--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="2049">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3010" uniqueCount="2049">
   <si>
     <t>Código</t>
   </si>
@@ -6543,7 +6543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F818"/>
+  <dimension ref="A1:F829"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.625" bestFit="1" customWidth="1"/>
@@ -16824,87 +16824,78 @@
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471">
-        <v>586177</v>
-      </c>
-      <c r="B471" t="s">
-        <v>817</v>
+        <v>59630</v>
       </c>
       <c r="C471" t="str">
         <f>VLOOKUP(A471,Hoja1!A:C,2,FALSE)</f>
-        <v>BRILL MATIC TABLETAS P/LAVAVAJILLAS X20 x12 un</v>
+        <v>AER CAR FRAGANCE COOL AQUA 5G. (4X15) x60 un</v>
       </c>
       <c r="D471">
         <f>VLOOKUP(A471,Hoja1!A:C,3,FALSE)</f>
-        <v>5379.66</v>
+        <v>2513.65</v>
       </c>
       <c r="E471">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F471" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472">
-        <v>57214</v>
-      </c>
-      <c r="B472" t="s">
-        <v>819</v>
+        <v>59628</v>
       </c>
       <c r="C472" t="str">
         <f>VLOOKUP(A472,Hoja1!A:C,2,FALSE)</f>
-        <v>BROSS LONDON BLUE EDT 100ML x3 un</v>
+        <v>AER CAR FRAGANCE MUSK AFTER MOSKE(4X15) x60 un</v>
       </c>
       <c r="D472">
         <f>VLOOKUP(A472,Hoja1!A:C,3,FALSE)</f>
-        <v>23970.18</v>
+        <v>2513.65</v>
       </c>
       <c r="E472">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F472" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473">
-        <v>57203</v>
-      </c>
-      <c r="B473" t="s">
-        <v>821</v>
+        <v>59629</v>
       </c>
       <c r="C473" t="str">
         <f>VLOOKUP(A473,Hoja1!A:C,2,FALSE)</f>
-        <v>BROSS LONDON CLASSIC EDT 100ML C/VAP x3 un</v>
+        <v>AER CAR FRAGANCE ROSE BLOSSOM 5G (4X15) x60 un</v>
       </c>
       <c r="D473">
         <f>VLOOKUP(A473,Hoja1!A:C,3,FALSE)</f>
-        <v>23970.18</v>
+        <v>2513.65</v>
       </c>
       <c r="E473">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F473" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474">
-        <v>57225</v>
+        <v>586177</v>
       </c>
       <c r="B474" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="C474" t="str">
         <f>VLOOKUP(A474,Hoja1!A:C,2,FALSE)</f>
-        <v>BROSS LONDON WARRIOR EDT 100ML C/VAP x3 un</v>
+        <v>BRILL MATIC TABLETAS P/LAVAVAJILLAS X20 x12 un</v>
       </c>
       <c r="D474">
         <f>VLOOKUP(A474,Hoja1!A:C,3,FALSE)</f>
-        <v>23970.18</v>
+        <v>5379.66</v>
       </c>
       <c r="E474">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F474" t="s">
         <v>6</v>
@@ -16912,21 +16903,21 @@
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475">
-        <v>7445</v>
+        <v>57214</v>
       </c>
       <c r="B475" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="C475" t="str">
         <f>VLOOKUP(A475,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA ADHESIVAS SILICONA-11MMX30CM-.17 x17 un</v>
+        <v>BROSS LONDON BLUE EDT 100ML x3 un</v>
       </c>
       <c r="D475">
         <f>VLOOKUP(A475,Hoja1!A:C,3,FALSE)</f>
-        <v>5597</v>
+        <v>23970.18</v>
       </c>
       <c r="E475">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F475" t="s">
         <v>6</v>
@@ -16934,21 +16925,21 @@
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476">
-        <v>7444</v>
+        <v>57203</v>
       </c>
       <c r="B476" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="C476" t="str">
         <f>VLOOKUP(A476,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA ADHESIVAS SILICONA-7MMX30CM-.42 x42 un</v>
+        <v>BROSS LONDON CLASSIC EDT 100ML C/VAP x3 un</v>
       </c>
       <c r="D476">
         <f>VLOOKUP(A476,Hoja1!A:C,3,FALSE)</f>
-        <v>5597</v>
+        <v>23970.18</v>
       </c>
       <c r="E476">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F476" t="s">
         <v>6</v>
@@ -16956,21 +16947,21 @@
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477">
-        <v>324</v>
+        <v>57225</v>
       </c>
       <c r="B477" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="C477" t="str">
         <f>VLOOKUP(A477,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA BOMBITAS DE AGUA 100 U (50) x1 un</v>
+        <v>BROSS LONDON WARRIOR EDT 100ML C/VAP x3 un</v>
       </c>
       <c r="D477">
         <f>VLOOKUP(A477,Hoja1!A:C,3,FALSE)</f>
-        <v>1730</v>
+        <v>23970.18</v>
       </c>
       <c r="E477">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F477" t="s">
         <v>6</v>
@@ -16978,18 +16969,18 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478">
-        <v>7061</v>
+        <v>7445</v>
       </c>
       <c r="B478" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="C478" t="str">
         <f>VLOOKUP(A478,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA CINTA AISLADORA AMARILLA 10MT(10 x10 un</v>
+        <v>CANDELA ADHESIVAS SILICONA-11MMX30CM-.17 x17 un</v>
       </c>
       <c r="D478">
         <f>VLOOKUP(A478,Hoja1!A:C,3,FALSE)</f>
-        <v>597</v>
+        <v>5597</v>
       </c>
       <c r="E478">
         <v>21</v>
@@ -17000,18 +16991,18 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479">
-        <v>7063</v>
+        <v>7444</v>
       </c>
       <c r="B479" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="C479" t="str">
         <f>VLOOKUP(A479,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA CINTA AISLADORA AZUL 10MT (10) x10 un</v>
+        <v>CANDELA ADHESIVAS SILICONA-7MMX30CM-.42 x42 un</v>
       </c>
       <c r="D479">
         <f>VLOOKUP(A479,Hoja1!A:C,3,FALSE)</f>
-        <v>597</v>
+        <v>5597</v>
       </c>
       <c r="E479">
         <v>21</v>
@@ -17022,18 +17013,18 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480">
-        <v>7069</v>
+        <v>324</v>
       </c>
       <c r="B480" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="C480" t="str">
         <f>VLOOKUP(A480,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA CINTA AISLADORA NEGRA 20MT(10) x10 un</v>
+        <v>CANDELA BOMBITAS DE AGUA 100 U (50) x1 un</v>
       </c>
       <c r="D480">
         <f>VLOOKUP(A480,Hoja1!A:C,3,FALSE)</f>
-        <v>1164</v>
+        <v>1730</v>
       </c>
       <c r="E480">
         <v>21</v>
@@ -17044,14 +17035,14 @@
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481">
-        <v>7059</v>
+        <v>7061</v>
       </c>
       <c r="B481" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="C481" t="str">
         <f>VLOOKUP(A481,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA CINTA AISLADORA NEGRA 10MT(10) x36 un</v>
+        <v>CANDELA CINTA AISLADORA AMARILLA 10MT(10 x10 un</v>
       </c>
       <c r="D481">
         <f>VLOOKUP(A481,Hoja1!A:C,3,FALSE)</f>
@@ -17066,14 +17057,14 @@
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482">
-        <v>7060</v>
+        <v>7063</v>
       </c>
       <c r="B482" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="C482" t="str">
         <f>VLOOKUP(A482,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA CINTA AISLADORA ROJA 10MTS.(10) x36 un</v>
+        <v>CANDELA CINTA AISLADORA AZUL 10MT (10) x10 un</v>
       </c>
       <c r="D482">
         <f>VLOOKUP(A482,Hoja1!A:C,3,FALSE)</f>
@@ -17088,18 +17079,18 @@
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483">
-        <v>7049</v>
+        <v>7069</v>
       </c>
       <c r="B483" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="C483" t="str">
         <f>VLOOKUP(A483,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA CINTA EMBALAR CONF.TRANS(6) x72 un</v>
+        <v>CANDELA CINTA AISLADORA NEGRA 20MT(10) x10 un</v>
       </c>
       <c r="D483">
         <f>VLOOKUP(A483,Hoja1!A:C,3,FALSE)</f>
-        <v>713</v>
+        <v>1164</v>
       </c>
       <c r="E483">
         <v>21</v>
@@ -17110,18 +17101,18 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484">
-        <v>7052</v>
+        <v>7059</v>
       </c>
       <c r="B484" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="C484" t="str">
         <f>VLOOKUP(A484,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA CINTA EMBALAR MARRON 41MTS (6) x36 un</v>
+        <v>CANDELA CINTA AISLADORA NEGRA 10MT(10) x36 un</v>
       </c>
       <c r="D484">
         <f>VLOOKUP(A484,Hoja1!A:C,3,FALSE)</f>
-        <v>1451</v>
+        <v>597</v>
       </c>
       <c r="E484">
         <v>21</v>
@@ -17132,18 +17123,18 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485">
-        <v>7051</v>
+        <v>7060</v>
       </c>
       <c r="B485" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="C485" t="str">
         <f>VLOOKUP(A485,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA CINTA EMBALAR TRANS. 10MT (6) x36 un</v>
+        <v>CANDELA CINTA AISLADORA ROJA 10MTS.(10) x36 un</v>
       </c>
       <c r="D485">
         <f>VLOOKUP(A485,Hoja1!A:C,3,FALSE)</f>
-        <v>2597</v>
+        <v>597</v>
       </c>
       <c r="E485">
         <v>21</v>
@@ -17154,18 +17145,18 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486">
-        <v>6883</v>
+        <v>7049</v>
       </c>
       <c r="B486" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="C486" t="str">
         <f>VLOOKUP(A486,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA CINTA EMBALAR TRANS. 42MT (6) x36 un</v>
+        <v>CANDELA CINTA EMBALAR CONF.TRANS(6) x72 un</v>
       </c>
       <c r="D486">
         <f>VLOOKUP(A486,Hoja1!A:C,3,FALSE)</f>
-        <v>1375</v>
+        <v>713</v>
       </c>
       <c r="E486">
         <v>21</v>
@@ -17176,18 +17167,18 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487">
-        <v>6503</v>
+        <v>7052</v>
       </c>
       <c r="B487" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="C487" t="str">
         <f>VLOOKUP(A487,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA ENCENDED. CLAS. GLOW CAJA X 20 U x20 un</v>
+        <v>CANDELA CINTA EMBALAR MARRON 41MTS (6) x36 un</v>
       </c>
       <c r="D487">
         <f>VLOOKUP(A487,Hoja1!A:C,3,FALSE)</f>
-        <v>627</v>
+        <v>1451</v>
       </c>
       <c r="E487">
         <v>21</v>
@@ -17198,18 +17189,18 @@
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488">
-        <v>1462</v>
+        <v>7051</v>
       </c>
       <c r="B488" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="C488" t="str">
         <f>VLOOKUP(A488,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA GLOBOS 9 FELIZ CUMPLEAÑOS X 50 U x1 un</v>
+        <v>CANDELA CINTA EMBALAR TRANS. 10MT (6) x36 un</v>
       </c>
       <c r="D488">
         <f>VLOOKUP(A488,Hoja1!A:C,3,FALSE)</f>
-        <v>4381</v>
+        <v>2597</v>
       </c>
       <c r="E488">
         <v>21</v>
@@ -17220,18 +17211,18 @@
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489">
-        <v>1461</v>
+        <v>6883</v>
       </c>
       <c r="B489" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="C489" t="str">
         <f>VLOOKUP(A489,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA GLOBOS 9 LISOS SURTIDOS X 50 U x1 un</v>
+        <v>CANDELA CINTA EMBALAR TRANS. 42MT (6) x36 un</v>
       </c>
       <c r="D489">
         <f>VLOOKUP(A489,Hoja1!A:C,3,FALSE)</f>
-        <v>3165</v>
+        <v>1375</v>
       </c>
       <c r="E489">
         <v>21</v>
@@ -17242,18 +17233,18 @@
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490">
-        <v>6483</v>
+        <v>6503</v>
       </c>
       <c r="B490" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="C490" t="str">
         <f>VLOOKUP(A490,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA HOGAR ENCENDED. CLAS. X 1U x12 un</v>
+        <v>CANDELA ENCENDED. CLAS. GLOW CAJA X 20 U x20 un</v>
       </c>
       <c r="D490">
         <f>VLOOKUP(A490,Hoja1!A:C,3,FALSE)</f>
-        <v>2939.01</v>
+        <v>627</v>
       </c>
       <c r="E490">
         <v>21</v>
@@ -17264,18 +17255,18 @@
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491">
-        <v>5860</v>
+        <v>1462</v>
       </c>
       <c r="B491" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="C491" t="str">
         <f>VLOOKUP(A491,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA HOGAR FLAMEADOR ENCENDEDOR. X 1 x1 un</v>
+        <v>CANDELA GLOBOS 9 FELIZ CUMPLEAÑOS X 50 U x1 un</v>
       </c>
       <c r="D491">
         <f>VLOOKUP(A491,Hoja1!A:C,3,FALSE)</f>
-        <v>6532</v>
+        <v>4381</v>
       </c>
       <c r="E491">
         <v>21</v>
@@ -17286,18 +17277,18 @@
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492">
-        <v>6796</v>
+        <v>1461</v>
       </c>
       <c r="B492" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="C492" t="str">
         <f>VLOOKUP(A492,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA LAMPARA LED 15W FRIA -120W x5 un</v>
+        <v>CANDELA GLOBOS 9 LISOS SURTIDOS X 50 U x1 un</v>
       </c>
       <c r="D492">
         <f>VLOOKUP(A492,Hoja1!A:C,3,FALSE)</f>
-        <v>1688</v>
+        <v>3165</v>
       </c>
       <c r="E492">
         <v>21</v>
@@ -17308,18 +17299,18 @@
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493">
-        <v>6516</v>
+        <v>6483</v>
       </c>
       <c r="B493" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="C493" t="str">
         <f>VLOOKUP(A493,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA LAMPARA LED 7W FRIA-50W x5 un</v>
+        <v>CANDELA HOGAR ENCENDED. CLAS. X 1U x12 un</v>
       </c>
       <c r="D493">
         <f>VLOOKUP(A493,Hoja1!A:C,3,FALSE)</f>
-        <v>1040</v>
+        <v>2939.01</v>
       </c>
       <c r="E493">
         <v>21</v>
@@ -17330,18 +17321,18 @@
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494">
-        <v>6518</v>
+        <v>5860</v>
       </c>
       <c r="B494" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="C494" t="str">
         <f>VLOOKUP(A494,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA LAMPARA LED 9W FRIA -75W x5 un</v>
+        <v>CANDELA HOGAR FLAMEADOR ENCENDEDOR. X 1 x1 un</v>
       </c>
       <c r="D494">
         <f>VLOOKUP(A494,Hoja1!A:C,3,FALSE)</f>
-        <v>1117</v>
+        <v>6532</v>
       </c>
       <c r="E494">
         <v>21</v>
@@ -17352,18 +17343,18 @@
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495">
-        <v>6520</v>
+        <v>6796</v>
       </c>
       <c r="B495" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="C495" t="str">
         <f>VLOOKUP(A495,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA LAMPARA LED CLASICA FRIA - 12W x5 un</v>
+        <v>CANDELA LAMPARA LED 15W FRIA -120W x5 un</v>
       </c>
       <c r="D495">
         <f>VLOOKUP(A495,Hoja1!A:C,3,FALSE)</f>
-        <v>1421</v>
+        <v>1688</v>
       </c>
       <c r="E495">
         <v>21</v>
@@ -17374,18 +17365,18 @@
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496">
-        <v>7442</v>
+        <v>6516</v>
       </c>
       <c r="B496" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="C496" t="str">
         <f>VLOOKUP(A496,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA PISTOLA ENCOLADORA 10W x1 un</v>
+        <v>CANDELA LAMPARA LED 7W FRIA-50W x5 un</v>
       </c>
       <c r="D496">
         <f>VLOOKUP(A496,Hoja1!A:C,3,FALSE)</f>
-        <v>3667</v>
+        <v>1040</v>
       </c>
       <c r="E496">
         <v>21</v>
@@ -17396,18 +17387,18 @@
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497">
-        <v>7443</v>
+        <v>6518</v>
       </c>
       <c r="B497" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="C497" t="str">
         <f>VLOOKUP(A497,Hoja1!A:C,2,FALSE)</f>
-        <v>CANDELA PISTOLA ENCOLADORA 40W x1 un</v>
+        <v>CANDELA LAMPARA LED 9W FRIA -75W x5 un</v>
       </c>
       <c r="D497">
         <f>VLOOKUP(A497,Hoja1!A:C,3,FALSE)</f>
-        <v>5018</v>
+        <v>1117</v>
       </c>
       <c r="E497">
         <v>21</v>
@@ -17418,21 +17409,21 @@
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498">
-        <v>2313</v>
+        <v>6520</v>
       </c>
       <c r="B498" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="C498" t="str">
         <f>VLOOKUP(A498,Hoja1!A:C,2,FALSE)</f>
-        <v>CARDON MAR DEO MEN 150ML x6 un</v>
+        <v>CANDELA LAMPARA LED CLASICA FRIA - 12W x5 un</v>
       </c>
       <c r="D498">
         <f>VLOOKUP(A498,Hoja1!A:C,3,FALSE)</f>
-        <v>4943.26</v>
+        <v>1421</v>
       </c>
       <c r="E498">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F498" t="s">
         <v>6</v>
@@ -17440,21 +17431,21 @@
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499">
-        <v>2302</v>
+        <v>7442</v>
       </c>
       <c r="B499" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="C499" t="str">
         <f>VLOOKUP(A499,Hoja1!A:C,2,FALSE)</f>
-        <v>CARDON MAR EAU MEN 100ML C/VAP x3 un</v>
+        <v>CANDELA PISTOLA ENCOLADORA 10W x1 un</v>
       </c>
       <c r="D499">
         <f>VLOOKUP(A499,Hoja1!A:C,3,FALSE)</f>
-        <v>29407.24</v>
+        <v>3667</v>
       </c>
       <c r="E499">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F499" t="s">
         <v>6</v>
@@ -17462,21 +17453,21 @@
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500">
-        <v>5614</v>
+        <v>7443</v>
       </c>
       <c r="B500" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="C500" t="str">
         <f>VLOOKUP(A500,Hoja1!A:C,2,FALSE)</f>
-        <v>CARDON SOÑADA DEO FEM 123ML x6 un</v>
+        <v>CANDELA PISTOLA ENCOLADORA 40W x1 un</v>
       </c>
       <c r="D500">
         <f>VLOOKUP(A500,Hoja1!A:C,3,FALSE)</f>
-        <v>4570.1899999999996</v>
+        <v>5018</v>
       </c>
       <c r="E500">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F500" t="s">
         <v>6</v>
@@ -17484,18 +17475,18 @@
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501">
-        <v>5603</v>
+        <v>2313</v>
       </c>
       <c r="B501" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="C501" t="str">
         <f>VLOOKUP(A501,Hoja1!A:C,2,FALSE)</f>
-        <v>CARDON SOÑADA EAU FEM 100ML C/VAP x3 un</v>
+        <v>CARDON MAR DEO MEN 150ML x6 un</v>
       </c>
       <c r="D501">
         <f>VLOOKUP(A501,Hoja1!A:C,3,FALSE)</f>
-        <v>27124.9</v>
+        <v>4943.26</v>
       </c>
       <c r="E501">
         <v>22</v>
@@ -17506,18 +17497,18 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502">
-        <v>2657</v>
+        <v>2302</v>
       </c>
       <c r="B502" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="C502" t="str">
         <f>VLOOKUP(A502,Hoja1!A:C,2,FALSE)</f>
-        <v>CARDON TIERRA DEO 150ML x6 un</v>
+        <v>CARDON MAR EAU MEN 100ML C/VAP x3 un</v>
       </c>
       <c r="D502">
         <f>VLOOKUP(A502,Hoja1!A:C,3,FALSE)</f>
-        <v>4943.26</v>
+        <v>29407.24</v>
       </c>
       <c r="E502">
         <v>22</v>
@@ -17528,18 +17519,18 @@
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503">
-        <v>2646</v>
+        <v>5614</v>
       </c>
       <c r="B503" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="C503" t="str">
         <f>VLOOKUP(A503,Hoja1!A:C,2,FALSE)</f>
-        <v>CARDON TIERRA EAU MEN 100ML C/VAP x3 un</v>
+        <v>CARDON SOÑADA DEO FEM 123ML x6 un</v>
       </c>
       <c r="D503">
         <f>VLOOKUP(A503,Hoja1!A:C,3,FALSE)</f>
-        <v>29407.24</v>
+        <v>4570.1899999999996</v>
       </c>
       <c r="E503">
         <v>22</v>
@@ -17550,18 +17541,18 @@
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504">
-        <v>5679</v>
+        <v>5603</v>
       </c>
       <c r="B504" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="C504" t="str">
         <f>VLOOKUP(A504,Hoja1!A:C,2,FALSE)</f>
-        <v>CARDON VIAJERA DEO FEM 123ML x6 un</v>
+        <v>CARDON SOÑADA EAU FEM 100ML C/VAP x3 un</v>
       </c>
       <c r="D504">
         <f>VLOOKUP(A504,Hoja1!A:C,3,FALSE)</f>
-        <v>4570.1899999999996</v>
+        <v>27124.9</v>
       </c>
       <c r="E504">
         <v>22</v>
@@ -17572,18 +17563,18 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505">
-        <v>5668</v>
+        <v>2657</v>
       </c>
       <c r="B505" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="C505" t="str">
         <f>VLOOKUP(A505,Hoja1!A:C,2,FALSE)</f>
-        <v>CARDON VIAJERA EAU FEM 100ML C/VAP x3 un</v>
+        <v>CARDON TIERRA DEO 150ML x6 un</v>
       </c>
       <c r="D505">
         <f>VLOOKUP(A505,Hoja1!A:C,3,FALSE)</f>
-        <v>27124.9</v>
+        <v>4943.26</v>
       </c>
       <c r="E505">
         <v>22</v>
@@ -17594,21 +17585,21 @@
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506">
-        <v>452112</v>
+        <v>2646</v>
       </c>
       <c r="B506" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="C506" t="str">
         <f>VLOOKUP(A506,Hoja1!A:C,2,FALSE)</f>
-        <v>CHANITA ROLLO DE COCINA 50 PAÑOS X3U(8) x8 un</v>
+        <v>CARDON TIERRA EAU MEN 100ML C/VAP x3 un</v>
       </c>
       <c r="D506">
         <f>VLOOKUP(A506,Hoja1!A:C,3,FALSE)</f>
-        <v>1331</v>
+        <v>29407.24</v>
       </c>
       <c r="E506">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F506" t="s">
         <v>6</v>
@@ -17616,21 +17607,21 @@
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507">
-        <v>3034</v>
+        <v>5679</v>
       </c>
       <c r="B507" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C507" t="str">
         <f>VLOOKUP(A507,Hoja1!A:C,2,FALSE)</f>
-        <v>CIEL DEO CLASICO 123ML x6 un</v>
+        <v>CARDON VIAJERA DEO FEM 123ML x6 un</v>
       </c>
       <c r="D507">
         <f>VLOOKUP(A507,Hoja1!A:C,3,FALSE)</f>
-        <v>4528.3900000000003</v>
+        <v>4570.1899999999996</v>
       </c>
       <c r="E507">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F507" t="s">
         <v>6</v>
@@ -17638,21 +17629,21 @@
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508">
-        <v>2423</v>
+        <v>5668</v>
       </c>
       <c r="B508" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="C508" t="str">
         <f>VLOOKUP(A508,Hoja1!A:C,2,FALSE)</f>
-        <v>CIEL DEO CRISTAL 123ML x6 un</v>
+        <v>CARDON VIAJERA EAU FEM 100ML C/VAP x3 un</v>
       </c>
       <c r="D508">
         <f>VLOOKUP(A508,Hoja1!A:C,3,FALSE)</f>
-        <v>4528.3900000000003</v>
+        <v>27124.9</v>
       </c>
       <c r="E508">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F508" t="s">
         <v>6</v>
@@ -17660,21 +17651,21 @@
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509">
-        <v>15425</v>
+        <v>452112</v>
       </c>
       <c r="B509" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="C509" t="str">
         <f>VLOOKUP(A509,Hoja1!A:C,2,FALSE)</f>
-        <v>CIEL DEO NOIR 123ML x6 un</v>
+        <v>CHANITA ROLLO DE COCINA 50 PAÑOS X3U(8) x8 un</v>
       </c>
       <c r="D509">
         <f>VLOOKUP(A509,Hoja1!A:C,3,FALSE)</f>
-        <v>4559.41</v>
+        <v>1331</v>
       </c>
       <c r="E509">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F509" t="s">
         <v>6</v>
@@ -17682,18 +17673,18 @@
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510">
-        <v>6445</v>
+        <v>3034</v>
       </c>
       <c r="B510" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C510" t="str">
         <f>VLOOKUP(A510,Hoja1!A:C,2,FALSE)</f>
-        <v>CIEL DEO NUIT 123ML x6 un</v>
+        <v>CIEL DEO CLASICO 123ML x6 un</v>
       </c>
       <c r="D510">
         <f>VLOOKUP(A510,Hoja1!A:C,3,FALSE)</f>
-        <v>4559.41</v>
+        <v>4528.3900000000003</v>
       </c>
       <c r="E510">
         <v>24</v>
@@ -17704,18 +17695,18 @@
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511">
-        <v>3023</v>
+        <v>2423</v>
       </c>
       <c r="B511" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="C511" t="str">
         <f>VLOOKUP(A511,Hoja1!A:C,2,FALSE)</f>
-        <v>CIEL EDT CLASICO 80ML C/VAP x3 un</v>
+        <v>CIEL DEO CRISTAL 123ML x6 un</v>
       </c>
       <c r="D511">
         <f>VLOOKUP(A511,Hoja1!A:C,3,FALSE)</f>
-        <v>17627.900000000001</v>
+        <v>4528.3900000000003</v>
       </c>
       <c r="E511">
         <v>24</v>
@@ -17726,18 +17717,18 @@
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512">
-        <v>2412</v>
+        <v>15425</v>
       </c>
       <c r="B512" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="C512" t="str">
         <f>VLOOKUP(A512,Hoja1!A:C,2,FALSE)</f>
-        <v>CIEL EDT CRISTAL 80ML C/VAP x3 un</v>
+        <v>CIEL DEO NOIR 123ML x6 un</v>
       </c>
       <c r="D512">
         <f>VLOOKUP(A512,Hoja1!A:C,3,FALSE)</f>
-        <v>21857.919999999998</v>
+        <v>4559.41</v>
       </c>
       <c r="E512">
         <v>24</v>
@@ -17748,18 +17739,18 @@
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513">
-        <v>15414</v>
+        <v>6445</v>
       </c>
       <c r="B513" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="C513" t="str">
         <f>VLOOKUP(A513,Hoja1!A:C,2,FALSE)</f>
-        <v>CIEL EDT NOIR 80ML C/VAP x3 un</v>
+        <v>CIEL DEO NUIT 123ML x6 un</v>
       </c>
       <c r="D513">
         <f>VLOOKUP(A513,Hoja1!A:C,3,FALSE)</f>
-        <v>21857.919999999998</v>
+        <v>4559.41</v>
       </c>
       <c r="E513">
         <v>24</v>
@@ -17770,14 +17761,14 @@
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514">
-        <v>6423</v>
+        <v>3023</v>
       </c>
       <c r="B514" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="C514" t="str">
         <f>VLOOKUP(A514,Hoja1!A:C,2,FALSE)</f>
-        <v>CIEL EDT NUIT 80ML C/VAP. x3 un</v>
+        <v>CIEL EDT CLASICO 80ML C/VAP x3 un</v>
       </c>
       <c r="D514">
         <f>VLOOKUP(A514,Hoja1!A:C,3,FALSE)</f>
@@ -17792,18 +17783,18 @@
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515">
-        <v>1547</v>
+        <v>2412</v>
       </c>
       <c r="B515" t="s">
-        <v>905</v>
-      </c>
-      <c r="C515" t="e">
+        <v>899</v>
+      </c>
+      <c r="C515" t="str">
         <f>VLOOKUP(A515,Hoja1!A:C,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D515" t="e">
+        <v>CIEL EDT CRISTAL 80ML C/VAP x3 un</v>
+      </c>
+      <c r="D515">
         <f>VLOOKUP(A515,Hoja1!A:C,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>21857.919999999998</v>
       </c>
       <c r="E515">
         <v>24</v>
@@ -17814,21 +17805,21 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516">
-        <v>16031</v>
+        <v>15414</v>
       </c>
       <c r="B516" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="C516" t="str">
         <f>VLOOKUP(A516,Hoja1!A:C,2,FALSE)</f>
-        <v>CLINSY AUTOBRILLO INCOLORO P/ CERAM. 900 x12 un</v>
+        <v>CIEL EDT NOIR 80ML C/VAP x3 un</v>
       </c>
       <c r="D516">
         <f>VLOOKUP(A516,Hoja1!A:C,3,FALSE)</f>
-        <v>5414.04</v>
+        <v>21857.919999999998</v>
       </c>
       <c r="E516">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F516" t="s">
         <v>6</v>
@@ -17836,21 +17827,21 @@
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517">
-        <v>16033</v>
+        <v>6423</v>
       </c>
       <c r="B517" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="C517" t="str">
         <f>VLOOKUP(A517,Hoja1!A:C,2,FALSE)</f>
-        <v>CLINSY AUTOBRILLO NEGRO P/ CERAM. 900ML. x12 un</v>
+        <v>CIEL EDT NUIT 80ML C/VAP. x3 un</v>
       </c>
       <c r="D517">
         <f>VLOOKUP(A517,Hoja1!A:C,3,FALSE)</f>
-        <v>5414.04</v>
+        <v>17627.900000000001</v>
       </c>
       <c r="E517">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F517" t="s">
         <v>6</v>
@@ -17858,21 +17849,21 @@
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518">
-        <v>16032</v>
+        <v>1547</v>
       </c>
       <c r="B518" t="s">
-        <v>910</v>
-      </c>
-      <c r="C518" t="str">
+        <v>905</v>
+      </c>
+      <c r="C518" t="e">
         <f>VLOOKUP(A518,Hoja1!A:C,2,FALSE)</f>
-        <v>CLINSY AUTOBRILLO ROJO P/ CERAM. 900ML x12 un</v>
-      </c>
-      <c r="D518">
+        <v>#N/A</v>
+      </c>
+      <c r="D518" t="e">
         <f>VLOOKUP(A518,Hoja1!A:C,3,FALSE)</f>
-        <v>5414.04</v>
+        <v>#N/A</v>
       </c>
       <c r="E518">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F518" t="s">
         <v>6</v>
@@ -17880,18 +17871,18 @@
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519">
-        <v>16121</v>
+        <v>16031</v>
       </c>
       <c r="B519" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="C519" t="str">
         <f>VLOOKUP(A519,Hoja1!A:C,2,FALSE)</f>
-        <v>CLINSY DESTAPACAÑERIAS 1LT x12 un</v>
+        <v>CLINSY AUTOBRILLO INCOLORO P/ CERAM. 900 x12 un</v>
       </c>
       <c r="D519">
         <f>VLOOKUP(A519,Hoja1!A:C,3,FALSE)</f>
-        <v>5644.6</v>
+        <v>5414.04</v>
       </c>
       <c r="E519">
         <v>25</v>
@@ -17902,18 +17893,18 @@
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520">
-        <v>16151</v>
+        <v>16033</v>
       </c>
       <c r="B520" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="C520" t="str">
         <f>VLOOKUP(A520,Hoja1!A:C,2,FALSE)</f>
-        <v>CLINSY SARROQUITOL  X 1LT x12 un</v>
+        <v>CLINSY AUTOBRILLO NEGRO P/ CERAM. 900ML. x12 un</v>
       </c>
       <c r="D520">
         <f>VLOOKUP(A520,Hoja1!A:C,3,FALSE)</f>
-        <v>6802.44</v>
+        <v>5414.04</v>
       </c>
       <c r="E520">
         <v>25</v>
@@ -17924,18 +17915,18 @@
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521">
-        <v>16111</v>
+        <v>16032</v>
       </c>
       <c r="B521" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="C521" t="str">
         <f>VLOOKUP(A521,Hoja1!A:C,2,FALSE)</f>
-        <v>CLINSY SELLADOR INCOLORO 900CC x12 un</v>
+        <v>CLINSY AUTOBRILLO ROJO P/ CERAM. 900ML x12 un</v>
       </c>
       <c r="D521">
         <f>VLOOKUP(A521,Hoja1!A:C,3,FALSE)</f>
-        <v>7961.29</v>
+        <v>5414.04</v>
       </c>
       <c r="E521">
         <v>25</v>
@@ -17946,18 +17937,18 @@
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522">
-        <v>16113</v>
+        <v>16121</v>
       </c>
       <c r="B522" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="C522" t="str">
         <f>VLOOKUP(A522,Hoja1!A:C,2,FALSE)</f>
-        <v>CLINSY SELLADOR NEGRO 900CC x12 un</v>
+        <v>CLINSY DESTAPACAÑERIAS 1LT x12 un</v>
       </c>
       <c r="D522">
         <f>VLOOKUP(A522,Hoja1!A:C,3,FALSE)</f>
-        <v>7961.29</v>
+        <v>5644.6</v>
       </c>
       <c r="E522">
         <v>25</v>
@@ -17968,18 +17959,18 @@
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523">
-        <v>16112</v>
+        <v>16151</v>
       </c>
       <c r="B523" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="C523" t="str">
         <f>VLOOKUP(A523,Hoja1!A:C,2,FALSE)</f>
-        <v>CLINSY SELLADOR ROJO 900CC x12 un</v>
+        <v>CLINSY SARROQUITOL  X 1LT x12 un</v>
       </c>
       <c r="D523">
         <f>VLOOKUP(A523,Hoja1!A:C,3,FALSE)</f>
-        <v>7961.29</v>
+        <v>6802.44</v>
       </c>
       <c r="E523">
         <v>25</v>
@@ -17990,21 +17981,21 @@
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524">
-        <v>550465</v>
+        <v>16111</v>
       </c>
       <c r="B524" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="C524" t="str">
         <f>VLOOKUP(A524,Hoja1!A:C,2,FALSE)</f>
-        <v>CLIPPER ENCENDEDOR REUSABLE GEOMETRIC 15 x15 un</v>
+        <v>CLINSY SELLADOR INCOLORO 900CC x12 un</v>
       </c>
       <c r="D524">
         <f>VLOOKUP(A524,Hoja1!A:C,3,FALSE)</f>
-        <v>523.69000000000005</v>
+        <v>7961.29</v>
       </c>
       <c r="E524">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F524" t="s">
         <v>6</v>
@@ -18012,21 +18003,21 @@
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525">
-        <v>58201</v>
+        <v>16113</v>
       </c>
       <c r="B525" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="C525" t="str">
         <f>VLOOKUP(A525,Hoja1!A:C,2,FALSE)</f>
-        <v>COLBERT CODE BOLD EAU 100ML C/VAP x3 un</v>
+        <v>CLINSY SELLADOR NEGRO 900CC x12 un</v>
       </c>
       <c r="D525">
         <f>VLOOKUP(A525,Hoja1!A:C,3,FALSE)</f>
-        <v>27212.68</v>
+        <v>7961.29</v>
       </c>
       <c r="E525">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F525" t="s">
         <v>6</v>
@@ -18034,21 +18025,21 @@
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526">
-        <v>19237</v>
+        <v>16112</v>
       </c>
       <c r="B526" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="C526" t="str">
         <f>VLOOKUP(A526,Hoja1!A:C,2,FALSE)</f>
-        <v>COLBERT DEO 150ML x6 un</v>
+        <v>CLINSY SELLADOR ROJO 900CC x12 un</v>
       </c>
       <c r="D526">
         <f>VLOOKUP(A526,Hoja1!A:C,3,FALSE)</f>
-        <v>4940.05</v>
+        <v>7961.29</v>
       </c>
       <c r="E526">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F526" t="s">
         <v>6</v>
@@ -18056,21 +18047,21 @@
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527">
-        <v>17465</v>
+        <v>550465</v>
       </c>
       <c r="B527" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="C527" t="str">
         <f>VLOOKUP(A527,Hoja1!A:C,2,FALSE)</f>
-        <v>COLBERT DEO NOIR 150ML x6 un</v>
+        <v>CLIPPER ENCENDEDOR REUSABLE GEOMETRIC 15 x15 un</v>
       </c>
       <c r="D527">
         <f>VLOOKUP(A527,Hoja1!A:C,3,FALSE)</f>
-        <v>4940.05</v>
+        <v>523.69000000000005</v>
       </c>
       <c r="E527">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F527" t="s">
         <v>6</v>
@@ -18078,18 +18069,18 @@
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528">
-        <v>17432</v>
+        <v>58201</v>
       </c>
       <c r="B528" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="C528" t="str">
         <f>VLOOKUP(A528,Hoja1!A:C,2,FALSE)</f>
-        <v>COLBERT EDP NOIR 60ML C/VAP x3 un</v>
+        <v>COLBERT CODE BOLD EAU 100ML C/VAP x3 un</v>
       </c>
       <c r="D528">
         <f>VLOOKUP(A528,Hoja1!A:C,3,FALSE)</f>
-        <v>12684.61</v>
+        <v>27212.68</v>
       </c>
       <c r="E528">
         <v>27</v>
@@ -18100,18 +18091,18 @@
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529">
-        <v>19204</v>
+        <v>19237</v>
       </c>
       <c r="B529" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="C529" t="str">
         <f>VLOOKUP(A529,Hoja1!A:C,2,FALSE)</f>
-        <v>COLBERT EDT 60ML C/VAP x3 un</v>
+        <v>COLBERT DEO 150ML x6 un</v>
       </c>
       <c r="D529">
         <f>VLOOKUP(A529,Hoja1!A:C,3,FALSE)</f>
-        <v>11192.32</v>
+        <v>4940.05</v>
       </c>
       <c r="E529">
         <v>27</v>
@@ -18122,21 +18113,21 @@
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530">
-        <v>4703</v>
+        <v>17465</v>
       </c>
       <c r="B530" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="C530" t="str">
         <f>VLOOKUP(A530,Hoja1!A:C,2,FALSE)</f>
-        <v>COQUETERIA FLOWER EDT 40ML C/VAP. x6 un</v>
+        <v>COLBERT DEO NOIR 150ML x6 un</v>
       </c>
       <c r="D530">
         <f>VLOOKUP(A530,Hoja1!A:C,3,FALSE)</f>
-        <v>7554.8</v>
+        <v>4940.05</v>
       </c>
       <c r="E530">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F530" t="s">
         <v>6</v>
@@ -18144,21 +18135,21 @@
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531">
-        <v>4747</v>
+        <v>17432</v>
       </c>
       <c r="B531" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="C531" t="str">
         <f>VLOOKUP(A531,Hoja1!A:C,2,FALSE)</f>
-        <v>COQUETERIA FLOWERS DEO 123ML x6 un</v>
+        <v>COLBERT EDP NOIR 60ML C/VAP x3 un</v>
       </c>
       <c r="D531">
         <f>VLOOKUP(A531,Hoja1!A:C,3,FALSE)</f>
-        <v>4106.41</v>
+        <v>12684.61</v>
       </c>
       <c r="E531">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F531" t="s">
         <v>6</v>
@@ -18166,21 +18157,21 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532">
-        <v>97361</v>
+        <v>19204</v>
       </c>
       <c r="B532" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="C532" t="str">
         <f>VLOOKUP(A532,Hoja1!A:C,2,FALSE)</f>
-        <v>CUPIDO JABON TOCADOR CREMAS 3X90GR. x20 un</v>
+        <v>COLBERT EDT 60ML C/VAP x3 un</v>
       </c>
       <c r="D532">
         <f>VLOOKUP(A532,Hoja1!A:C,3,FALSE)</f>
-        <v>1766.04</v>
+        <v>11192.32</v>
       </c>
       <c r="E532">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F532" t="s">
         <v>6</v>
@@ -18188,21 +18179,21 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533">
-        <v>9725</v>
+        <v>4703</v>
       </c>
       <c r="B533" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="C533" t="str">
         <f>VLOOKUP(A533,Hoja1!A:C,2,FALSE)</f>
-        <v>CUPIDO JABON TOCADOR TRICOLOR 3 X90GR. x20 un</v>
+        <v>COQUETERIA FLOWER EDT 40ML C/VAP. x6 un</v>
       </c>
       <c r="D533">
         <f>VLOOKUP(A533,Hoja1!A:C,3,FALSE)</f>
-        <v>1682.13</v>
+        <v>7554.8</v>
       </c>
       <c r="E533">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F533" t="s">
         <v>6</v>
@@ -18210,21 +18201,21 @@
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534">
-        <v>841022</v>
+        <v>4747</v>
       </c>
       <c r="B534" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="C534" t="str">
         <f>VLOOKUP(A534,Hoja1!A:C,2,FALSE)</f>
-        <v>DANUBIO APRESTO PLANCHA CON SILICONA x12 un</v>
+        <v>COQUETERIA FLOWERS DEO 123ML x6 un</v>
       </c>
       <c r="D534">
         <f>VLOOKUP(A534,Hoja1!A:C,3,FALSE)</f>
-        <v>3307.59</v>
+        <v>4106.41</v>
       </c>
       <c r="E534">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F534" t="s">
         <v>6</v>
@@ -18232,21 +18223,21 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535">
-        <v>841020</v>
+        <v>97361</v>
       </c>
       <c r="B535" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="C535" t="str">
         <f>VLOOKUP(A535,Hoja1!A:C,2,FALSE)</f>
-        <v>DANUBIO LUSTRAMUEBLES CLASICO 360 ML x12 un</v>
+        <v>CUPIDO JABON TOCADOR CREMAS 3X90GR. x20 un</v>
       </c>
       <c r="D535">
         <f>VLOOKUP(A535,Hoja1!A:C,3,FALSE)</f>
-        <v>3142.58</v>
+        <v>1766.04</v>
       </c>
       <c r="E535">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F535" t="s">
         <v>6</v>
@@ -18254,21 +18245,21 @@
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536">
-        <v>841027</v>
+        <v>9725</v>
       </c>
       <c r="B536" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="C536" t="str">
         <f>VLOOKUP(A536,Hoja1!A:C,2,FALSE)</f>
-        <v>DANUBIO LUSTRAMUEBLES LAVANDA 360 ML x12 un</v>
+        <v>CUPIDO JABON TOCADOR TRICOLOR 3 X90GR. x20 un</v>
       </c>
       <c r="D536">
         <f>VLOOKUP(A536,Hoja1!A:C,3,FALSE)</f>
-        <v>3142.58</v>
+        <v>1682.13</v>
       </c>
       <c r="E536">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F536" t="s">
         <v>6</v>
@@ -18276,21 +18267,21 @@
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537">
-        <v>1022005</v>
+        <v>841022</v>
       </c>
       <c r="B537" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="C537" t="str">
         <f>VLOOKUP(A537,Hoja1!A:C,2,FALSE)</f>
-        <v>DEPILORM CR DEP ROSTRO FLORAL 60GR (12) x12 un</v>
+        <v>DANUBIO APRESTO PLANCHA CON SILICONA x12 un</v>
       </c>
       <c r="D537">
         <f>VLOOKUP(A537,Hoja1!A:C,3,FALSE)</f>
-        <v>3850.22</v>
+        <v>3307.59</v>
       </c>
       <c r="E537">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F537" t="s">
         <v>6</v>
@@ -18298,21 +18289,21 @@
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538">
-        <v>1022004</v>
+        <v>841020</v>
       </c>
       <c r="B538" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="C538" t="str">
         <f>VLOOKUP(A538,Hoja1!A:C,2,FALSE)</f>
-        <v>DEPILORM CREMA DEP. ROSTRO ALOE VERA 60G x12 un</v>
+        <v>DANUBIO LUSTRAMUEBLES CLASICO 360 ML x12 un</v>
       </c>
       <c r="D538">
         <f>VLOOKUP(A538,Hoja1!A:C,3,FALSE)</f>
-        <v>3850.22</v>
+        <v>3142.58</v>
       </c>
       <c r="E538">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F538" t="s">
         <v>6</v>
@@ -18320,21 +18311,21 @@
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539">
-        <v>1022001</v>
+        <v>841027</v>
       </c>
       <c r="B539" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="C539" t="str">
         <f>VLOOKUP(A539,Hoja1!A:C,2,FALSE)</f>
-        <v>DEPILORM CREMA DEPILATORIA ROSTRO X30GR x12 un</v>
+        <v>DANUBIO LUSTRAMUEBLES LAVANDA 360 ML x12 un</v>
       </c>
       <c r="D539">
         <f>VLOOKUP(A539,Hoja1!A:C,3,FALSE)</f>
-        <v>3516.26</v>
+        <v>3142.58</v>
       </c>
       <c r="E539">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F539" t="s">
         <v>6</v>
@@ -18342,21 +18333,21 @@
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540">
-        <v>26633</v>
+        <v>1022005</v>
       </c>
       <c r="B540" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="C540" t="str">
         <f>VLOOKUP(A540,Hoja1!A:C,2,FALSE)</f>
-        <v>DESAFIO PALILLERO BLISTER X12 U x432 un</v>
+        <v>DEPILORM CR DEP ROSTRO FLORAL 60GR (12) x12 un</v>
       </c>
       <c r="D540">
         <f>VLOOKUP(A540,Hoja1!A:C,3,FALSE)</f>
-        <v>5893.03</v>
+        <v>3850.22</v>
       </c>
       <c r="E540">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F540" t="s">
         <v>6</v>
@@ -18364,21 +18355,21 @@
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541">
-        <v>232165</v>
+        <v>1022004</v>
       </c>
       <c r="B541" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="C541" t="str">
         <f>VLOOKUP(A541,Hoja1!A:C,2,FALSE)</f>
-        <v>DUC JABON TOCADOR ARMONIC 110GR-VIOLETA x72 un</v>
+        <v>DEPILORM CREMA DEP. ROSTRO ALOE VERA 60G x12 un</v>
       </c>
       <c r="D541">
         <f>VLOOKUP(A541,Hoja1!A:C,3,FALSE)</f>
-        <v>638</v>
+        <v>3850.22</v>
       </c>
       <c r="E541">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F541" t="s">
         <v>6</v>
@@ -18386,21 +18377,21 @@
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542">
-        <v>232167</v>
+        <v>1022001</v>
       </c>
       <c r="B542" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="C542" t="str">
         <f>VLOOKUP(A542,Hoja1!A:C,2,FALSE)</f>
-        <v>DUC JABON TOCADOR CITRUS 110GR-VERDE x72 un</v>
+        <v>DEPILORM CREMA DEPILATORIA ROSTRO X30GR x12 un</v>
       </c>
       <c r="D542">
         <f>VLOOKUP(A542,Hoja1!A:C,3,FALSE)</f>
-        <v>638</v>
+        <v>3516.26</v>
       </c>
       <c r="E542">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F542" t="s">
         <v>6</v>
@@ -18408,21 +18399,21 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543">
-        <v>232168</v>
+        <v>26633</v>
       </c>
       <c r="B543" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="C543" t="str">
         <f>VLOOKUP(A543,Hoja1!A:C,2,FALSE)</f>
-        <v>DUC JABON TOCADOR HIDRATANTE 110GR-AMAR x72 un</v>
+        <v>DESAFIO PALILLERO BLISTER X12 U x432 un</v>
       </c>
       <c r="D543">
         <f>VLOOKUP(A543,Hoja1!A:C,3,FALSE)</f>
-        <v>638</v>
+        <v>5893.03</v>
       </c>
       <c r="E543">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F543" t="s">
         <v>6</v>
@@ -18430,21 +18421,21 @@
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544">
-        <v>553898</v>
+        <v>232165</v>
       </c>
       <c r="B544" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="C544" t="str">
         <f>VLOOKUP(A544,Hoja1!A:C,2,FALSE)</f>
-        <v>EL PADRINO NAIPES POCKER (6) x1 un</v>
+        <v>DUC JABON TOCADOR ARMONIC 110GR-VIOLETA x72 un</v>
       </c>
       <c r="D544">
         <f>VLOOKUP(A544,Hoja1!A:C,3,FALSE)</f>
-        <v>4020.23</v>
+        <v>638</v>
       </c>
       <c r="E544">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F544" t="s">
         <v>6</v>
@@ -18452,21 +18443,21 @@
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545">
-        <v>841049</v>
+        <v>232167</v>
       </c>
       <c r="B545" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="C545" t="str">
         <f>VLOOKUP(A545,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO LUBRICANTE AEROSOL 230 G x12 un</v>
+        <v>DUC JABON TOCADOR CITRUS 110GR-VERDE x72 un</v>
       </c>
       <c r="D545">
         <f>VLOOKUP(A545,Hoja1!A:C,3,FALSE)</f>
-        <v>4572.04</v>
+        <v>638</v>
       </c>
       <c r="E545">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F545" t="s">
         <v>6</v>
@@ -18474,21 +18465,21 @@
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546">
-        <v>841001</v>
+        <v>232168</v>
       </c>
       <c r="B546" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="C546" t="str">
         <f>VLOOKUP(A546,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO MATA CUCARACHAS Y HORMIGAS 360 ML x12 un</v>
+        <v>DUC JABON TOCADOR HIDRATANTE 110GR-AMAR x72 un</v>
       </c>
       <c r="D546">
         <f>VLOOKUP(A546,Hoja1!A:C,3,FALSE)</f>
-        <v>3565.22</v>
+        <v>638</v>
       </c>
       <c r="E546">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F546" t="s">
         <v>6</v>
@@ -18496,21 +18487,21 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547">
-        <v>841010</v>
+        <v>553898</v>
       </c>
       <c r="B547" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="C547" t="str">
         <f>VLOOKUP(A547,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO MATA CUCARACHAS Y HORMIGAS S/OLOR x12 un</v>
+        <v>EL PADRINO NAIPES POCKER (6) x1 un</v>
       </c>
       <c r="D547">
         <f>VLOOKUP(A547,Hoja1!A:C,3,FALSE)</f>
-        <v>3991.73</v>
+        <v>4020.23</v>
       </c>
       <c r="E547">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F547" t="s">
         <v>6</v>
@@ -18518,18 +18509,18 @@
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548">
-        <v>841000</v>
+        <v>841049</v>
       </c>
       <c r="B548" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="C548" t="str">
         <f>VLOOKUP(A548,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO MATA MOSCAS Y MOSQUITOS 360 ML x12 un</v>
+        <v>ESCUDO LUBRICANTE AEROSOL 230 G x12 un</v>
       </c>
       <c r="D548">
         <f>VLOOKUP(A548,Hoja1!A:C,3,FALSE)</f>
-        <v>3308.79</v>
+        <v>4572.04</v>
       </c>
       <c r="E548">
         <v>35</v>
@@ -18540,18 +18531,18 @@
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549">
-        <v>841009</v>
+        <v>841001</v>
       </c>
       <c r="B549" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="C549" t="str">
         <f>VLOOKUP(A549,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO MATA MOSCAS/MOSQUITOS S/OLOR 360 x12 un</v>
+        <v>ESCUDO MATA CUCARACHAS Y HORMIGAS 360 ML x12 un</v>
       </c>
       <c r="D549">
         <f>VLOOKUP(A549,Hoja1!A:C,3,FALSE)</f>
-        <v>3802.62</v>
+        <v>3565.22</v>
       </c>
       <c r="E549">
         <v>35</v>
@@ -18562,18 +18553,18 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550">
-        <v>841032</v>
+        <v>841010</v>
       </c>
       <c r="B550" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C550" t="str">
         <f>VLOOKUP(A550,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO MATA POLILLAS/LARVAS 360 ML x12 un</v>
+        <v>ESCUDO MATA CUCARACHAS Y HORMIGAS S/OLOR x12 un</v>
       </c>
       <c r="D550">
         <f>VLOOKUP(A550,Hoja1!A:C,3,FALSE)</f>
-        <v>3602.38</v>
+        <v>3991.73</v>
       </c>
       <c r="E550">
         <v>35</v>
@@ -18584,18 +18575,18 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551">
-        <v>841002</v>
+        <v>841000</v>
       </c>
       <c r="B551" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="C551" t="str">
         <f>VLOOKUP(A551,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO MATA PULGAS /GARRAPATAS 360 ML x12 un</v>
+        <v>ESCUDO MATA MOSCAS Y MOSQUITOS 360 ML x12 un</v>
       </c>
       <c r="D551">
         <f>VLOOKUP(A551,Hoja1!A:C,3,FALSE)</f>
-        <v>3900</v>
+        <v>3308.79</v>
       </c>
       <c r="E551">
         <v>35</v>
@@ -18606,18 +18597,18 @@
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552">
-        <v>841011</v>
+        <v>841009</v>
       </c>
       <c r="B552" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="C552" t="str">
         <f>VLOOKUP(A552,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO MATAMOSQUITOS Y JEJENES x12 un</v>
+        <v>ESCUDO MATA MOSCAS/MOSQUITOS S/OLOR 360 x12 un</v>
       </c>
       <c r="D552">
         <f>VLOOKUP(A552,Hoja1!A:C,3,FALSE)</f>
-        <v>3656.15</v>
+        <v>3802.62</v>
       </c>
       <c r="E552">
         <v>35</v>
@@ -18628,18 +18619,18 @@
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553">
-        <v>841003</v>
+        <v>841032</v>
       </c>
       <c r="B553" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="C553" t="str">
         <f>VLOOKUP(A553,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO PARA EL  HOGAR Y JARDIN 360 ML x12 un</v>
+        <v>ESCUDO MATA POLILLAS/LARVAS 360 ML x12 un</v>
       </c>
       <c r="D553">
         <f>VLOOKUP(A553,Hoja1!A:C,3,FALSE)</f>
-        <v>4523.72</v>
+        <v>3602.38</v>
       </c>
       <c r="E553">
         <v>35</v>
@@ -18650,18 +18641,18 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554">
-        <v>841005</v>
+        <v>841002</v>
       </c>
       <c r="B554" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="C554" t="str">
         <f>VLOOKUP(A554,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO REPELENTE CREMA 200 ML x12 un</v>
+        <v>ESCUDO MATA PULGAS /GARRAPATAS 360 ML x12 un</v>
       </c>
       <c r="D554">
         <f>VLOOKUP(A554,Hoja1!A:C,3,FALSE)</f>
-        <v>3971.96</v>
+        <v>3900</v>
       </c>
       <c r="E554">
         <v>35</v>
@@ -18672,18 +18663,18 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555">
-        <v>841004</v>
+        <v>841011</v>
       </c>
       <c r="B555" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="C555" t="str">
         <f>VLOOKUP(A555,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO REPELENTE CREMA 60 ML x12 un</v>
+        <v>ESCUDO MATAMOSQUITOS Y JEJENES x12 un</v>
       </c>
       <c r="D555">
         <f>VLOOKUP(A555,Hoja1!A:C,3,FALSE)</f>
-        <v>2633.24</v>
+        <v>3656.15</v>
       </c>
       <c r="E555">
         <v>35</v>
@@ -18694,18 +18685,18 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556">
-        <v>841008</v>
+        <v>841003</v>
       </c>
       <c r="B556" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="C556" t="str">
         <f>VLOOKUP(A556,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO REPELENTE EXT. DURACION- VERDE 13 x12 un</v>
+        <v>ESCUDO PARA EL  HOGAR Y JARDIN 360 ML x12 un</v>
       </c>
       <c r="D556">
         <f>VLOOKUP(A556,Hoja1!A:C,3,FALSE)</f>
-        <v>5255.87</v>
+        <v>4523.72</v>
       </c>
       <c r="E556">
         <v>35</v>
@@ -18716,18 +18707,18 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557">
-        <v>841007</v>
+        <v>841005</v>
       </c>
       <c r="B557" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="C557" t="str">
         <f>VLOOKUP(A557,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO REPELENTE ORIGINAL- NARANJA 135 G x12 un</v>
+        <v>ESCUDO REPELENTE CREMA 200 ML x12 un</v>
       </c>
       <c r="D557">
         <f>VLOOKUP(A557,Hoja1!A:C,3,FALSE)</f>
-        <v>3527.62</v>
+        <v>3971.96</v>
       </c>
       <c r="E557">
         <v>35</v>
@@ -18738,18 +18729,18 @@
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558">
-        <v>841072</v>
+        <v>841004</v>
       </c>
       <c r="B558" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="C558" t="str">
         <f>VLOOKUP(A558,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO RG2 LIMPIATAPIZADOS 360 ML x12 un</v>
+        <v>ESCUDO REPELENTE CREMA 60 ML x12 un</v>
       </c>
       <c r="D558">
         <f>VLOOKUP(A558,Hoja1!A:C,3,FALSE)</f>
-        <v>3524.52</v>
+        <v>2633.24</v>
       </c>
       <c r="E558">
         <v>35</v>
@@ -18760,18 +18751,18 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559">
-        <v>841023</v>
+        <v>841008</v>
       </c>
       <c r="B559" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="C559" t="str">
         <f>VLOOKUP(A559,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO SILICONA MULTIUSO CUERO 400 ML x12 un</v>
+        <v>ESCUDO REPELENTE EXT. DURACION- VERDE 13 x12 un</v>
       </c>
       <c r="D559">
         <f>VLOOKUP(A559,Hoja1!A:C,3,FALSE)</f>
-        <v>5000.03</v>
+        <v>5255.87</v>
       </c>
       <c r="E559">
         <v>35</v>
@@ -18782,18 +18773,18 @@
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560">
-        <v>841024</v>
+        <v>841007</v>
       </c>
       <c r="B560" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="C560" t="str">
         <f>VLOOKUP(A560,Hoja1!A:C,2,FALSE)</f>
-        <v>ESCUDO SILICONA MULTIUSO LAVANDA 400 ML x12 un</v>
+        <v>ESCUDO REPELENTE ORIGINAL- NARANJA 135 G x12 un</v>
       </c>
       <c r="D560">
         <f>VLOOKUP(A560,Hoja1!A:C,3,FALSE)</f>
-        <v>5000.03</v>
+        <v>3527.62</v>
       </c>
       <c r="E560">
         <v>35</v>
@@ -18804,21 +18795,21 @@
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561">
-        <v>6644</v>
+        <v>841072</v>
       </c>
       <c r="B561" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="C561" t="str">
         <f>VLOOKUP(A561,Hoja1!A:C,2,FALSE)</f>
-        <v>FLOWER DEO ROSE 123ML x6 un</v>
+        <v>ESCUDO RG2 LIMPIATAPIZADOS 360 ML x12 un</v>
       </c>
       <c r="D561">
         <f>VLOOKUP(A561,Hoja1!A:C,3,FALSE)</f>
-        <v>4425.47</v>
+        <v>3524.52</v>
       </c>
       <c r="E561">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F561" t="s">
         <v>6</v>
@@ -18826,21 +18817,21 @@
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562">
-        <v>66851</v>
+        <v>841023</v>
       </c>
       <c r="B562" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="C562" t="str">
         <f>VLOOKUP(A562,Hoja1!A:C,2,FALSE)</f>
-        <v>FLOWER EAU ROSE 40ML C/VAP x3 un</v>
+        <v>ESCUDO SILICONA MULTIUSO CUERO 400 ML x12 un</v>
       </c>
       <c r="D562">
         <f>VLOOKUP(A562,Hoja1!A:C,3,FALSE)</f>
-        <v>10446.15</v>
+        <v>5000.03</v>
       </c>
       <c r="E562">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F562" t="s">
         <v>6</v>
@@ -18848,21 +18839,21 @@
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563">
-        <v>451068</v>
+        <v>841024</v>
       </c>
       <c r="B563" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="C563" t="str">
         <f>VLOOKUP(A563,Hoja1!A:C,2,FALSE)</f>
-        <v>GAMUZA PAPEL HIGIENICO S.HOJA 30MT(12) x12 un</v>
+        <v>ESCUDO SILICONA MULTIUSO LAVANDA 400 ML x12 un</v>
       </c>
       <c r="D563">
         <f>VLOOKUP(A563,Hoja1!A:C,3,FALSE)</f>
-        <v>1197.9000000000001</v>
+        <v>5000.03</v>
       </c>
       <c r="E563">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F563" t="s">
         <v>6</v>
@@ -18870,21 +18861,21 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564">
-        <v>451073</v>
+        <v>6644</v>
       </c>
       <c r="B564" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="C564" t="str">
         <f>VLOOKUP(A564,Hoja1!A:C,2,FALSE)</f>
-        <v>GAMUZA PAPEL HIGIENICO S.HOJA X80MT(12) x12 un</v>
+        <v>FLOWER DEO ROSE 123ML x6 un</v>
       </c>
       <c r="D564">
         <f>VLOOKUP(A564,Hoja1!A:C,3,FALSE)</f>
-        <v>2541</v>
+        <v>4425.47</v>
       </c>
       <c r="E564">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F564" t="s">
         <v>6</v>
@@ -18892,21 +18883,21 @@
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565">
-        <v>101827</v>
+        <v>66851</v>
       </c>
       <c r="B565" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="C565" t="str">
         <f>VLOOKUP(A565,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE DETERG. LIQUIDO ROPA BIO D/P 900 x15 un</v>
+        <v>FLOWER EAU ROSE 40ML C/VAP x3 un</v>
       </c>
       <c r="D565">
         <f>VLOOKUP(A565,Hoja1!A:C,3,FALSE)</f>
-        <v>3475</v>
+        <v>10446.15</v>
       </c>
       <c r="E565">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F565" t="s">
         <v>6</v>
@@ -18914,21 +18905,21 @@
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566">
-        <v>232131</v>
+        <v>451068</v>
       </c>
       <c r="B566" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C566" t="str">
         <f>VLOOKUP(A566,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE JABON BLANCO  ECONOMICO 120 GR x64 un</v>
+        <v>GAMUZA PAPEL HIGIENICO S.HOJA 30MT(12) x12 un</v>
       </c>
       <c r="D566">
         <f>VLOOKUP(A566,Hoja1!A:C,3,FALSE)</f>
-        <v>569</v>
+        <v>1197.9000000000001</v>
       </c>
       <c r="E566">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F566" t="s">
         <v>6</v>
@@ -18936,21 +18927,21 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567">
-        <v>101725</v>
+        <v>451073</v>
       </c>
       <c r="B567" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="C567" t="str">
         <f>VLOOKUP(A567,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE JABON BLANCO C/GLICERINA 150GR x72 un</v>
+        <v>GAMUZA PAPEL HIGIENICO S.HOJA X80MT(12) x12 un</v>
       </c>
       <c r="D567">
         <f>VLOOKUP(A567,Hoja1!A:C,3,FALSE)</f>
-        <v>913.01</v>
+        <v>2541</v>
       </c>
       <c r="E567">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F567" t="s">
         <v>6</v>
@@ -18958,18 +18949,18 @@
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568">
-        <v>101271</v>
+        <v>101827</v>
       </c>
       <c r="B568" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="C568" t="str">
         <f>VLOOKUP(A568,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE JABON BLANCO CLASICO 200GR x72 un</v>
+        <v>GIGANTE DETERG. LIQUIDO ROPA BIO D/P 900 x15 un</v>
       </c>
       <c r="D568">
         <f>VLOOKUP(A568,Hoja1!A:C,3,FALSE)</f>
-        <v>906</v>
+        <v>3475</v>
       </c>
       <c r="E568">
         <v>38</v>
@@ -18980,18 +18971,18 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569">
-        <v>10795</v>
+        <v>232131</v>
       </c>
       <c r="B569" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="C569" t="str">
         <f>VLOOKUP(A569,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE JABON BLANCO CLASICO 2 X200GR x36 un</v>
+        <v>GIGANTE JABON BLANCO  ECONOMICO 120 GR x64 un</v>
       </c>
       <c r="D569">
         <f>VLOOKUP(A569,Hoja1!A:C,3,FALSE)</f>
-        <v>1810.99</v>
+        <v>569</v>
       </c>
       <c r="E569">
         <v>38</v>
@@ -19002,18 +18993,18 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570">
-        <v>232317</v>
+        <v>101725</v>
       </c>
       <c r="B570" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="C570" t="str">
         <f>VLOOKUP(A570,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE JABON BLANCO PURO ECONOMICO 2U. x36 un</v>
+        <v>GIGANTE JABON BLANCO C/GLICERINA 150GR x72 un</v>
       </c>
       <c r="D570">
         <f>VLOOKUP(A570,Hoja1!A:C,3,FALSE)</f>
-        <v>1137</v>
+        <v>913.01</v>
       </c>
       <c r="E570">
         <v>38</v>
@@ -19024,18 +19015,18 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571">
-        <v>232316</v>
+        <v>101271</v>
       </c>
       <c r="B571" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="C571" t="str">
         <f>VLOOKUP(A571,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE JABON BLANCO PURO FRAG. INTENSA x36 un</v>
+        <v>GIGANTE JABON BLANCO CLASICO 200GR x72 un</v>
       </c>
       <c r="D571">
         <f>VLOOKUP(A571,Hoja1!A:C,3,FALSE)</f>
-        <v>1388</v>
+        <v>906</v>
       </c>
       <c r="E571">
         <v>38</v>
@@ -19046,18 +19037,18 @@
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572">
-        <v>101286</v>
+        <v>10795</v>
       </c>
       <c r="B572" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="C572" t="str">
         <f>VLOOKUP(A572,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE LAVAVAJILLAS ALOE VERA 750ML x15 un</v>
+        <v>GIGANTE JABON BLANCO CLASICO 2 X200GR x36 un</v>
       </c>
       <c r="D572">
         <f>VLOOKUP(A572,Hoja1!A:C,3,FALSE)</f>
-        <v>1648</v>
+        <v>1810.99</v>
       </c>
       <c r="E572">
         <v>38</v>
@@ -19068,18 +19059,18 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573">
-        <v>101855</v>
+        <v>232317</v>
       </c>
       <c r="B573" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="C573" t="str">
         <f>VLOOKUP(A573,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE LAVAVAJILLAS FRUTILLA ULTRA 273M x12 un</v>
+        <v>GIGANTE JABON BLANCO PURO ECONOMICO 2U. x36 un</v>
       </c>
       <c r="D573">
         <f>VLOOKUP(A573,Hoja1!A:C,3,FALSE)</f>
-        <v>1449</v>
+        <v>1137</v>
       </c>
       <c r="E573">
         <v>38</v>
@@ -19090,18 +19081,18 @@
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574">
-        <v>101859</v>
+        <v>232316</v>
       </c>
       <c r="B574" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="C574" t="str">
         <f>VLOOKUP(A574,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE LAVAVAJILLAS FRUTILLA ULTRA 545M x12 un</v>
+        <v>GIGANTE JABON BLANCO PURO FRAG. INTENSA x36 un</v>
       </c>
       <c r="D574">
         <f>VLOOKUP(A574,Hoja1!A:C,3,FALSE)</f>
-        <v>2180</v>
+        <v>1388</v>
       </c>
       <c r="E574">
         <v>38</v>
@@ -19112,14 +19103,14 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575">
-        <v>101285</v>
+        <v>101286</v>
       </c>
       <c r="B575" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="C575" t="str">
         <f>VLOOKUP(A575,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE LAVAVAJILLAS GLICERINA 750ML x15 un</v>
+        <v>GIGANTE LAVAVAJILLAS ALOE VERA 750ML x15 un</v>
       </c>
       <c r="D575">
         <f>VLOOKUP(A575,Hoja1!A:C,3,FALSE)</f>
@@ -19134,14 +19125,14 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576">
-        <v>101857</v>
+        <v>101855</v>
       </c>
       <c r="B576" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="C576" t="str">
         <f>VLOOKUP(A576,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE LAVAVAJILLAS KIWI ULTRA 273ML x12 un</v>
+        <v>GIGANTE LAVAVAJILLAS FRUTILLA ULTRA 273M x12 un</v>
       </c>
       <c r="D576">
         <f>VLOOKUP(A576,Hoja1!A:C,3,FALSE)</f>
@@ -19156,14 +19147,14 @@
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577">
-        <v>101861</v>
+        <v>101859</v>
       </c>
       <c r="B577" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="C577" t="str">
         <f>VLOOKUP(A577,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE LAVAVAJILLAS KIWI ULTRA 545ML x12 un</v>
+        <v>GIGANTE LAVAVAJILLAS FRUTILLA ULTRA 545M x12 un</v>
       </c>
       <c r="D577">
         <f>VLOOKUP(A577,Hoja1!A:C,3,FALSE)</f>
@@ -19178,14 +19169,14 @@
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578">
-        <v>101284</v>
+        <v>101285</v>
       </c>
       <c r="B578" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C578" t="str">
         <f>VLOOKUP(A578,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE LAVAVAJILLAS LIMON 750ML x15 un</v>
+        <v>GIGANTE LAVAVAJILLAS GLICERINA 750ML x15 un</v>
       </c>
       <c r="D578">
         <f>VLOOKUP(A578,Hoja1!A:C,3,FALSE)</f>
@@ -19200,14 +19191,14 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579">
-        <v>101856</v>
+        <v>101857</v>
       </c>
       <c r="B579" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="C579" t="str">
         <f>VLOOKUP(A579,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE LAVAVAJILLAS LIMON ULTRA 273ML x12 un</v>
+        <v>GIGANTE LAVAVAJILLAS KIWI ULTRA 273ML x12 un</v>
       </c>
       <c r="D579">
         <f>VLOOKUP(A579,Hoja1!A:C,3,FALSE)</f>
@@ -19222,14 +19213,14 @@
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580">
-        <v>101860</v>
+        <v>101861</v>
       </c>
       <c r="B580" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C580" t="str">
         <f>VLOOKUP(A580,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE LAVAVAJILLAS LIMON ULTRA 545ML x12 un</v>
+        <v>GIGANTE LAVAVAJILLAS KIWI ULTRA 545ML x12 un</v>
       </c>
       <c r="D580">
         <f>VLOOKUP(A580,Hoja1!A:C,3,FALSE)</f>
@@ -19244,18 +19235,18 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581">
-        <v>101987</v>
+        <v>101284</v>
       </c>
       <c r="B581" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="C581" t="str">
         <f>VLOOKUP(A581,Hoja1!A:C,2,FALSE)</f>
-        <v>GIGANTE QUITAMANCHAS BARRA X 75 GR x12 un</v>
+        <v>GIGANTE LAVAVAJILLAS LIMON 750ML x15 un</v>
       </c>
       <c r="D581">
         <f>VLOOKUP(A581,Hoja1!A:C,3,FALSE)</f>
-        <v>1069</v>
+        <v>1648</v>
       </c>
       <c r="E581">
         <v>38</v>
@@ -19266,21 +19257,21 @@
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582">
-        <v>582292</v>
+        <v>101856</v>
       </c>
       <c r="B582" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="C582" t="str">
         <f>VLOOKUP(A582,Hoja1!A:C,2,FALSE)</f>
-        <v>I LOVE BICARBONATO D/P X 100G x24 un</v>
+        <v>GIGANTE LAVAVAJILLAS LIMON ULTRA 273ML x12 un</v>
       </c>
       <c r="D582">
         <f>VLOOKUP(A582,Hoja1!A:C,3,FALSE)</f>
-        <v>1335.48</v>
+        <v>1449</v>
       </c>
       <c r="E582">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F582" t="s">
         <v>6</v>
@@ -19288,21 +19279,21 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583">
-        <v>582308</v>
+        <v>101860</v>
       </c>
       <c r="B583" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="C583" t="str">
         <f>VLOOKUP(A583,Hoja1!A:C,2,FALSE)</f>
-        <v>I LOVE BICARBONATO X500G x12 un</v>
+        <v>GIGANTE LAVAVAJILLAS LIMON ULTRA 545ML x12 un</v>
       </c>
       <c r="D583">
         <f>VLOOKUP(A583,Hoja1!A:C,3,FALSE)</f>
-        <v>5337.19</v>
+        <v>2180</v>
       </c>
       <c r="E583">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F583" t="s">
         <v>6</v>
@@ -19310,21 +19301,21 @@
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584">
-        <v>3450</v>
+        <v>101987</v>
       </c>
       <c r="B584" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="C584" t="str">
         <f>VLOOKUP(A584,Hoja1!A:C,2,FALSE)</f>
-        <v>IDEAL PALITOS BROCHET 25CM x50 un</v>
+        <v>GIGANTE QUITAMANCHAS BARRA X 75 GR x12 un</v>
       </c>
       <c r="D584">
         <f>VLOOKUP(A584,Hoja1!A:C,3,FALSE)</f>
-        <v>1972.22</v>
+        <v>1069</v>
       </c>
       <c r="E584">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F584" t="s">
         <v>6</v>
@@ -19332,21 +19323,21 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585">
-        <v>865</v>
+        <v>582292</v>
       </c>
       <c r="B585" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="C585" t="str">
         <f>VLOOKUP(A585,Hoja1!A:C,2,FALSE)</f>
-        <v>IDEAL TOALLITAS HUMEDAS ALOE VERA D/P x24 un</v>
+        <v>I LOVE BICARBONATO D/P X 100G x24 un</v>
       </c>
       <c r="D585">
         <f>VLOOKUP(A585,Hoja1!A:C,3,FALSE)</f>
-        <v>1839.36</v>
+        <v>1335.48</v>
       </c>
       <c r="E585">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F585" t="s">
         <v>6</v>
@@ -19354,21 +19345,21 @@
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586">
-        <v>864</v>
+        <v>582308</v>
       </c>
       <c r="B586" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="C586" t="str">
         <f>VLOOKUP(A586,Hoja1!A:C,2,FALSE)</f>
-        <v>IDEAL TOALLITAS HUMEDAS CLASICAS D/P x24 un</v>
+        <v>I LOVE BICARBONATO X500G x12 un</v>
       </c>
       <c r="D586">
         <f>VLOOKUP(A586,Hoja1!A:C,3,FALSE)</f>
-        <v>1839.36</v>
+        <v>5337.19</v>
       </c>
       <c r="E586">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F586" t="s">
         <v>6</v>
@@ -19376,21 +19367,21 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587">
-        <v>8504</v>
+        <v>3450</v>
       </c>
       <c r="B587" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="C587" t="str">
         <f>VLOOKUP(A587,Hoja1!A:C,2,FALSE)</f>
-        <v>J&amp;J COTONETES FLEXIBLES 75U x60 un</v>
+        <v>IDEAL PALITOS BROCHET 25CM x50 un</v>
       </c>
       <c r="D587">
         <f>VLOOKUP(A587,Hoja1!A:C,3,FALSE)</f>
-        <v>2463.56</v>
+        <v>1972.22</v>
       </c>
       <c r="E587">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F587" t="s">
         <v>6</v>
@@ -19398,21 +19389,21 @@
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588">
-        <v>101268</v>
+        <v>865</v>
       </c>
       <c r="B588" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="C588" t="str">
         <f>VLOOKUP(A588,Hoja1!A:C,2,FALSE)</f>
-        <v>KENIA JABON DE TOCADOR CREM 3 X90GR x35 un</v>
+        <v>IDEAL TOALLITAS HUMEDAS ALOE VERA D/P x24 un</v>
       </c>
       <c r="D588">
         <f>VLOOKUP(A588,Hoja1!A:C,3,FALSE)</f>
-        <v>1505</v>
+        <v>1839.36</v>
       </c>
       <c r="E588">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F588" t="s">
         <v>6</v>
@@ -19420,21 +19411,21 @@
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589">
-        <v>102062</v>
+        <v>864</v>
       </c>
       <c r="B589" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C589" t="str">
         <f>VLOOKUP(A589,Hoja1!A:C,2,FALSE)</f>
-        <v>KENIA JABON DE TOCADOR CREM 4X3 X 90GR x35 un</v>
+        <v>IDEAL TOALLITAS HUMEDAS CLASICAS D/P x24 un</v>
       </c>
       <c r="D589">
         <f>VLOOKUP(A589,Hoja1!A:C,3,FALSE)</f>
-        <v>1976</v>
+        <v>1839.36</v>
       </c>
       <c r="E589">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F589" t="s">
         <v>6</v>
@@ -19442,21 +19433,21 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590">
-        <v>232205</v>
+        <v>8504</v>
       </c>
       <c r="B590" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="C590" t="str">
         <f>VLOOKUP(A590,Hoja1!A:C,2,FALSE)</f>
-        <v>KENIA JABON DE TOCADOR CREM 90 GR x60 un</v>
+        <v>J&amp;J COTONETES FLEXIBLES 75U x60 un</v>
       </c>
       <c r="D590">
         <f>VLOOKUP(A590,Hoja1!A:C,3,FALSE)</f>
-        <v>479.99</v>
+        <v>2463.56</v>
       </c>
       <c r="E590">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F590" t="s">
         <v>6</v>
@@ -19464,14 +19455,14 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591">
-        <v>231266</v>
+        <v>101268</v>
       </c>
       <c r="B591" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="C591" t="str">
         <f>VLOOKUP(A591,Hoja1!A:C,2,FALSE)</f>
-        <v>KENIA JABON DE TOCADOR MIX- 3 X 90GR x135 un</v>
+        <v>KENIA JABON DE TOCADOR CREM 3 X90GR x35 un</v>
       </c>
       <c r="D591">
         <f>VLOOKUP(A591,Hoja1!A:C,3,FALSE)</f>
@@ -19486,18 +19477,18 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592">
-        <v>232162</v>
+        <v>102062</v>
       </c>
       <c r="B592" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C592" t="str">
         <f>VLOOKUP(A592,Hoja1!A:C,2,FALSE)</f>
-        <v>KENIA JABON TOCADOR COLOR MIX 3 X 80GR x32 un</v>
+        <v>KENIA JABON DE TOCADOR CREM 4X3 X 90GR x35 un</v>
       </c>
       <c r="D592">
         <f>VLOOKUP(A592,Hoja1!A:C,3,FALSE)</f>
-        <v>2109.9699999999998</v>
+        <v>1976</v>
       </c>
       <c r="E592">
         <v>42</v>
@@ -19508,18 +19499,18 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593">
-        <v>232132</v>
+        <v>232205</v>
       </c>
       <c r="B593" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="C593" t="str">
         <f>VLOOKUP(A593,Hoja1!A:C,2,FALSE)</f>
-        <v>KENIA JABON TOCADOR CREMOSO 3 X 80GR x32 un</v>
+        <v>KENIA JABON DE TOCADOR CREM 90 GR x60 un</v>
       </c>
       <c r="D593">
         <f>VLOOKUP(A593,Hoja1!A:C,3,FALSE)</f>
-        <v>1527</v>
+        <v>479.99</v>
       </c>
       <c r="E593">
         <v>42</v>
@@ -19530,21 +19521,21 @@
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594">
-        <v>59646</v>
+        <v>231266</v>
       </c>
       <c r="B594" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="C594" t="str">
         <f>VLOOKUP(A594,Hoja1!A:C,2,FALSE)</f>
-        <v>KEVIN ABSOLUTE DEO 150ML x6 un</v>
+        <v>KENIA JABON DE TOCADOR MIX- 3 X 90GR x135 un</v>
       </c>
       <c r="D594">
         <f>VLOOKUP(A594,Hoja1!A:C,3,FALSE)</f>
-        <v>4943.26</v>
+        <v>1505</v>
       </c>
       <c r="E594">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F594" t="s">
         <v>6</v>
@@ -19552,21 +19543,21 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595">
-        <v>59635</v>
+        <v>232162</v>
       </c>
       <c r="B595" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="C595" t="str">
         <f>VLOOKUP(A595,Hoja1!A:C,2,FALSE)</f>
-        <v>KEVIN ABSOLUTE EAU 100ML C/VAP x3 un</v>
+        <v>KENIA JABON TOCADOR COLOR MIX 3 X 80GR x32 un</v>
       </c>
       <c r="D595">
         <f>VLOOKUP(A595,Hoja1!A:C,3,FALSE)</f>
-        <v>28968.32</v>
+        <v>2109.9699999999998</v>
       </c>
       <c r="E595">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F595" t="s">
         <v>6</v>
@@ -19574,21 +19565,21 @@
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596">
-        <v>3723</v>
+        <v>232132</v>
       </c>
       <c r="B596" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="C596" t="str">
         <f>VLOOKUP(A596,Hoja1!A:C,2,FALSE)</f>
-        <v>KEVIN DEO 150ML x6 un</v>
+        <v>KENIA JABON TOCADOR CREMOSO 3 X 80GR x32 un</v>
       </c>
       <c r="D596">
         <f>VLOOKUP(A596,Hoja1!A:C,3,FALSE)</f>
-        <v>4940.05</v>
+        <v>1527</v>
       </c>
       <c r="E596">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F596" t="s">
         <v>6</v>
@@ -19596,18 +19587,18 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597">
-        <v>3712</v>
+        <v>59646</v>
       </c>
       <c r="B597" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="C597" t="str">
         <f>VLOOKUP(A597,Hoja1!A:C,2,FALSE)</f>
-        <v>KEVIN EDT 100ML C/VAP x3 un</v>
+        <v>KEVIN ABSOLUTE DEO 150ML x6 un</v>
       </c>
       <c r="D597">
         <f>VLOOKUP(A597,Hoja1!A:C,3,FALSE)</f>
-        <v>20102.259999999998</v>
+        <v>4943.26</v>
       </c>
       <c r="E597">
         <v>43</v>
@@ -19618,18 +19609,18 @@
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598">
-        <v>3701</v>
+        <v>59635</v>
       </c>
       <c r="B598" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="C598" t="str">
         <f>VLOOKUP(A598,Hoja1!A:C,2,FALSE)</f>
-        <v>KEVIN EDT CLASICO 60ML C/VAP x3 un</v>
+        <v>KEVIN ABSOLUTE EAU 100ML C/VAP x3 un</v>
       </c>
       <c r="D598">
         <f>VLOOKUP(A598,Hoja1!A:C,3,FALSE)</f>
-        <v>15713.12</v>
+        <v>28968.32</v>
       </c>
       <c r="E598">
         <v>43</v>
@@ -19640,18 +19631,18 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599">
-        <v>6724</v>
+        <v>3723</v>
       </c>
       <c r="B599" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="C599" t="str">
         <f>VLOOKUP(A599,Hoja1!A:C,2,FALSE)</f>
-        <v>KEVIN FREEDOM DEO 150ML x6 un</v>
+        <v>KEVIN DEO 150ML x6 un</v>
       </c>
       <c r="D599">
         <f>VLOOKUP(A599,Hoja1!A:C,3,FALSE)</f>
-        <v>4943.26</v>
+        <v>4940.05</v>
       </c>
       <c r="E599">
         <v>43</v>
@@ -19662,18 +19653,18 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600">
-        <v>25332</v>
+        <v>3712</v>
       </c>
       <c r="B600" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="C600" t="str">
         <f>VLOOKUP(A600,Hoja1!A:C,2,FALSE)</f>
-        <v>KEVIN PLATINUM EAU 50ML C/VAP x3 un</v>
+        <v>KEVIN EDT 100ML C/VAP x3 un</v>
       </c>
       <c r="D600">
         <f>VLOOKUP(A600,Hoja1!A:C,3,FALSE)</f>
-        <v>22823.54</v>
+        <v>20102.259999999998</v>
       </c>
       <c r="E600">
         <v>43</v>
@@ -19684,21 +19675,21 @@
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601">
-        <v>40023</v>
+        <v>3701</v>
       </c>
       <c r="B601" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="C601" t="str">
         <f>VLOOKUP(A601,Hoja1!A:C,2,FALSE)</f>
-        <v>LAS PEPAS MITO DEO 123ML x6 un</v>
+        <v>KEVIN EDT CLASICO 60ML C/VAP x3 un</v>
       </c>
       <c r="D601">
         <f>VLOOKUP(A601,Hoja1!A:C,3,FALSE)</f>
-        <v>4756.74</v>
+        <v>15713.12</v>
       </c>
       <c r="E601">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F601" t="s">
         <v>6</v>
@@ -19706,21 +19697,21 @@
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602">
-        <v>40012</v>
+        <v>6724</v>
       </c>
       <c r="B602" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="C602" t="str">
         <f>VLOOKUP(A602,Hoja1!A:C,2,FALSE)</f>
-        <v>LAS PEPAS MITO EAU 100ML C/VAP x3 un</v>
+        <v>KEVIN FREEDOM DEO 150ML x6 un</v>
       </c>
       <c r="D602">
         <f>VLOOKUP(A602,Hoja1!A:C,3,FALSE)</f>
-        <v>35903.18</v>
+        <v>4943.26</v>
       </c>
       <c r="E602">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F602" t="s">
         <v>6</v>
@@ -19728,21 +19719,21 @@
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603">
-        <v>40078</v>
+        <v>25332</v>
       </c>
       <c r="B603" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="C603" t="str">
         <f>VLOOKUP(A603,Hoja1!A:C,2,FALSE)</f>
-        <v>LAS PEPAS NINFA DEO 123ML x6 un</v>
+        <v>KEVIN PLATINUM EAU 50ML C/VAP x3 un</v>
       </c>
       <c r="D603">
         <f>VLOOKUP(A603,Hoja1!A:C,3,FALSE)</f>
-        <v>4756.74</v>
+        <v>22823.54</v>
       </c>
       <c r="E603">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F603" t="s">
         <v>6</v>
@@ -19750,87 +19741,78 @@
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604">
-        <v>40067</v>
-      </c>
-      <c r="B604" t="s">
-        <v>1080</v>
+        <v>22824</v>
       </c>
       <c r="C604" t="str">
         <f>VLOOKUP(A604,Hoja1!A:C,2,FALSE)</f>
-        <v>LAS PEPAS NINFA EAU 100ML C/VAP x3 un</v>
+        <v>KEVIN DUBAI DESODORANTE X150ML (6) x6 un</v>
       </c>
       <c r="D604">
         <f>VLOOKUP(A604,Hoja1!A:C,3,FALSE)</f>
-        <v>35903.18</v>
+        <v>4943.26</v>
       </c>
       <c r="E604">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F604" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605">
-        <v>451230</v>
-      </c>
-      <c r="B605" t="s">
-        <v>1082</v>
+        <v>22813</v>
       </c>
       <c r="C605" t="str">
         <f>VLOOKUP(A605,Hoja1!A:C,2,FALSE)</f>
-        <v>LISS PLUS MEGA ROLLO BLANCO X200PAÑOS(15 x15 un</v>
+        <v>KEVIN DUBAI EAU DE PARFUM X100ML (3) x3 un</v>
       </c>
       <c r="D605">
         <f>VLOOKUP(A605,Hoja1!A:C,3,FALSE)</f>
-        <v>1331</v>
+        <v>44505</v>
       </c>
       <c r="E605">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F605" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606">
-        <v>451220</v>
-      </c>
-      <c r="B606" t="s">
-        <v>1084</v>
+        <v>22802</v>
       </c>
       <c r="C606" t="str">
         <f>VLOOKUP(A606,Hoja1!A:C,2,FALSE)</f>
-        <v>LISS PLUS MEGA ROLLO DECO X200PAÑOS(15) x15 un</v>
+        <v>KEVIN DUBAI EAU DE PARFUM X60ML (3) x3 un</v>
       </c>
       <c r="D606">
         <f>VLOOKUP(A606,Hoja1!A:C,3,FALSE)</f>
-        <v>1331</v>
+        <v>34945.449999999997</v>
       </c>
       <c r="E606">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F606" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607">
-        <v>84400</v>
+        <v>40023</v>
       </c>
       <c r="B607" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="C607" t="str">
         <f>VLOOKUP(A607,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR  DEEP BLUE DEO MEN 170 ML x12 un</v>
+        <v>LAS PEPAS MITO DEO 123ML x6 un</v>
       </c>
       <c r="D607">
         <f>VLOOKUP(A607,Hoja1!A:C,3,FALSE)</f>
-        <v>3836.91</v>
+        <v>4756.74</v>
       </c>
       <c r="E607">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F607" t="s">
         <v>6</v>
@@ -19838,21 +19820,21 @@
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608">
-        <v>84100</v>
+        <v>40012</v>
       </c>
       <c r="B608" t="s">
-        <v>1088</v>
+        <v>1076</v>
       </c>
       <c r="C608" t="str">
         <f>VLOOKUP(A608,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR A.P. EQUAL UNISEX 97G x12 un</v>
+        <v>LAS PEPAS MITO EAU 100ML C/VAP x3 un</v>
       </c>
       <c r="D608">
         <f>VLOOKUP(A608,Hoja1!A:C,3,FALSE)</f>
-        <v>3719.54</v>
+        <v>35903.18</v>
       </c>
       <c r="E608">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F608" t="s">
         <v>6</v>
@@ -19860,21 +19842,21 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609">
-        <v>84101</v>
+        <v>40078</v>
       </c>
       <c r="B609" t="s">
-        <v>1090</v>
+        <v>1078</v>
       </c>
       <c r="C609" t="str">
         <f>VLOOKUP(A609,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR A.P. UNISEX NEUTRAL 97G x12 un</v>
+        <v>LAS PEPAS NINFA DEO 123ML x6 un</v>
       </c>
       <c r="D609">
         <f>VLOOKUP(A609,Hoja1!A:C,3,FALSE)</f>
-        <v>3719.54</v>
+        <v>4756.74</v>
       </c>
       <c r="E609">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F609" t="s">
         <v>6</v>
@@ -19882,21 +19864,21 @@
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610">
-        <v>84102</v>
+        <v>40067</v>
       </c>
       <c r="B610" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="C610" t="str">
         <f>VLOOKUP(A610,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR A.P. UNISEX PLURAL 97G x12 un</v>
+        <v>LAS PEPAS NINFA EAU 100ML C/VAP x3 un</v>
       </c>
       <c r="D610">
         <f>VLOOKUP(A610,Hoja1!A:C,3,FALSE)</f>
-        <v>3719.54</v>
+        <v>35903.18</v>
       </c>
       <c r="E610">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F610" t="s">
         <v>6</v>
@@ -19904,21 +19886,21 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611">
-        <v>84401</v>
+        <v>451230</v>
       </c>
       <c r="B611" t="s">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="C611" t="str">
         <f>VLOOKUP(A611,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR DEMON DEO MEN 170 ML x12 un</v>
+        <v>LISS PLUS MEGA ROLLO BLANCO X200PAÑOS(15 x15 un</v>
       </c>
       <c r="D611">
         <f>VLOOKUP(A611,Hoja1!A:C,3,FALSE)</f>
-        <v>3836.91</v>
+        <v>1331</v>
       </c>
       <c r="E611">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F611" t="s">
         <v>6</v>
@@ -19926,21 +19908,21 @@
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612">
-        <v>84277</v>
+        <v>451220</v>
       </c>
       <c r="B612" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
       <c r="C612" t="str">
         <f>VLOOKUP(A612,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR DEO PINO 220ML x12 un</v>
+        <v>LISS PLUS MEGA ROLLO DECO X200PAÑOS(15) x15 un</v>
       </c>
       <c r="D612">
         <f>VLOOKUP(A612,Hoja1!A:C,3,FALSE)</f>
-        <v>4318.58</v>
+        <v>1331</v>
       </c>
       <c r="E612">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F612" t="s">
         <v>6</v>
@@ -19948,18 +19930,18 @@
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613">
-        <v>84280</v>
+        <v>84400</v>
       </c>
       <c r="B613" t="s">
-        <v>1098</v>
+        <v>1086</v>
       </c>
       <c r="C613" t="str">
         <f>VLOOKUP(A613,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR ESPUMA DE AFEITAR 220 ML x12 un</v>
+        <v>MAC GREGOR  DEEP BLUE DEO MEN 170 ML x12 un</v>
       </c>
       <c r="D613">
         <f>VLOOKUP(A613,Hoja1!A:C,3,FALSE)</f>
-        <v>3872</v>
+        <v>3836.91</v>
       </c>
       <c r="E613">
         <v>46</v>
@@ -19970,18 +19952,18 @@
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614">
-        <v>84405</v>
+        <v>84100</v>
       </c>
       <c r="B614" t="s">
-        <v>1100</v>
+        <v>1088</v>
       </c>
       <c r="C614" t="str">
         <f>VLOOKUP(A614,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR LOVELY DEO FEM. 170 ML x12 un</v>
+        <v>MAC GREGOR A.P. EQUAL UNISEX 97G x12 un</v>
       </c>
       <c r="D614">
         <f>VLOOKUP(A614,Hoja1!A:C,3,FALSE)</f>
-        <v>3836.91</v>
+        <v>3719.54</v>
       </c>
       <c r="E614">
         <v>46</v>
@@ -19992,18 +19974,18 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615">
-        <v>84403</v>
+        <v>84101</v>
       </c>
       <c r="B615" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
       <c r="C615" t="str">
         <f>VLOOKUP(A615,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR STRONGER DEO MEN 170 ML x12 un</v>
+        <v>MAC GREGOR A.P. UNISEX NEUTRAL 97G x12 un</v>
       </c>
       <c r="D615">
         <f>VLOOKUP(A615,Hoja1!A:C,3,FALSE)</f>
-        <v>3836.91</v>
+        <v>3719.54</v>
       </c>
       <c r="E615">
         <v>46</v>
@@ -20014,97 +19996,109 @@
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616">
-        <v>34711</v>
+        <v>84102</v>
+      </c>
+      <c r="B616" t="s">
+        <v>1092</v>
       </c>
       <c r="C616" t="str">
         <f>VLOOKUP(A616,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR BINARY EDP 100ML x12 un</v>
+        <v>MAC GREGOR A.P. UNISEX PLURAL 97G x12 un</v>
       </c>
       <c r="D616">
         <f>VLOOKUP(A616,Hoja1!A:C,3,FALSE)</f>
-        <v>30436.15</v>
+        <v>3719.54</v>
       </c>
       <c r="E616">
         <v>46</v>
       </c>
       <c r="F616" t="s">
-        <v>2048</v>
+        <v>6</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617">
-        <v>20025</v>
+        <v>84401</v>
+      </c>
+      <c r="B617" t="s">
+        <v>1094</v>
       </c>
       <c r="C617" t="str">
         <f>VLOOKUP(A617,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR LOVELY EDP 100ML x12 un</v>
+        <v>MAC GREGOR DEMON DEO MEN 170 ML x12 un</v>
       </c>
       <c r="D617">
         <f>VLOOKUP(A617,Hoja1!A:C,3,FALSE)</f>
-        <v>30436.15</v>
+        <v>3836.91</v>
       </c>
       <c r="E617">
         <v>46</v>
       </c>
       <c r="F617" t="s">
-        <v>2048</v>
+        <v>6</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618">
-        <v>20056</v>
+        <v>84277</v>
+      </c>
+      <c r="B618" t="s">
+        <v>1096</v>
       </c>
       <c r="C618" t="str">
         <f>VLOOKUP(A618,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR LOVELY PURE EDP 100ML x12 un</v>
+        <v>MAC GREGOR DEO PINO 220ML x12 un</v>
       </c>
       <c r="D618">
         <f>VLOOKUP(A618,Hoja1!A:C,3,FALSE)</f>
-        <v>30436.15</v>
+        <v>4318.58</v>
       </c>
       <c r="E618">
         <v>46</v>
       </c>
       <c r="F618" t="s">
-        <v>2048</v>
+        <v>6</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619">
-        <v>20018</v>
+        <v>84280</v>
+      </c>
+      <c r="B619" t="s">
+        <v>1098</v>
       </c>
       <c r="C619" t="str">
         <f>VLOOKUP(A619,Hoja1!A:C,2,FALSE)</f>
-        <v>MAC GREGOR STRONGER EDP x12 un</v>
+        <v>MAC GREGOR ESPUMA DE AFEITAR 220 ML x12 un</v>
       </c>
       <c r="D619">
         <f>VLOOKUP(A619,Hoja1!A:C,3,FALSE)</f>
-        <v>30436.15</v>
+        <v>3872</v>
       </c>
       <c r="E619">
         <v>46</v>
       </c>
       <c r="F619" t="s">
-        <v>2048</v>
+        <v>6</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620">
-        <v>59534</v>
+        <v>84405</v>
       </c>
       <c r="B620" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="C620" t="str">
         <f>VLOOKUP(A620,Hoja1!A:C,2,FALSE)</f>
-        <v>MUJERCITAS DEO 123ML x6 un</v>
+        <v>MAC GREGOR LOVELY DEO FEM. 170 ML x12 un</v>
       </c>
       <c r="D620">
         <f>VLOOKUP(A620,Hoja1!A:C,3,FALSE)</f>
-        <v>4106.41</v>
+        <v>3836.91</v>
       </c>
       <c r="E620">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F620" t="s">
         <v>6</v>
@@ -20112,21 +20106,21 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621">
-        <v>59523</v>
+        <v>84403</v>
       </c>
       <c r="B621" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="C621" t="str">
         <f>VLOOKUP(A621,Hoja1!A:C,2,FALSE)</f>
-        <v>MUJERCITAS EDT 40ML C/VAP. x6 un</v>
+        <v>MAC GREGOR STRONGER DEO MEN 170 ML x12 un</v>
       </c>
       <c r="D621">
         <f>VLOOKUP(A621,Hoja1!A:C,3,FALSE)</f>
-        <v>7648.08</v>
+        <v>3836.91</v>
       </c>
       <c r="E621">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F621" t="s">
         <v>6</v>
@@ -20134,106 +20128,94 @@
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622">
-        <v>59512</v>
-      </c>
-      <c r="B622" t="s">
-        <v>1108</v>
+        <v>34711</v>
       </c>
       <c r="C622" t="str">
         <f>VLOOKUP(A622,Hoja1!A:C,2,FALSE)</f>
-        <v>MUJERCITAS EDT 80ML C/VAP x6 un</v>
+        <v>MAC GREGOR BINARY EDP 100ML x12 un</v>
       </c>
       <c r="D622">
         <f>VLOOKUP(A622,Hoja1!A:C,3,FALSE)</f>
-        <v>9326.92</v>
+        <v>30436.15</v>
       </c>
       <c r="E622">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F622" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623">
-        <v>9115</v>
-      </c>
-      <c r="B623" t="s">
-        <v>1110</v>
+        <v>20025</v>
       </c>
       <c r="C623" t="str">
         <f>VLOOKUP(A623,Hoja1!A:C,2,FALSE)</f>
-        <v>MUJERCITAS JULIE DEO 123ML x6 un</v>
+        <v>MAC GREGOR LOVELY EDP 100ML x12 un</v>
       </c>
       <c r="D623">
         <f>VLOOKUP(A623,Hoja1!A:C,3,FALSE)</f>
-        <v>4106.41</v>
+        <v>30436.15</v>
       </c>
       <c r="E623">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F623" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624">
-        <v>9104</v>
-      </c>
-      <c r="B624" t="s">
-        <v>1112</v>
+        <v>20056</v>
       </c>
       <c r="C624" t="str">
         <f>VLOOKUP(A624,Hoja1!A:C,2,FALSE)</f>
-        <v>MUJERCITAS JULIE EDT 50ML C/VAP x3 un</v>
+        <v>MAC GREGOR LOVELY PURE EDP 100ML x12 un</v>
       </c>
       <c r="D624">
         <f>VLOOKUP(A624,Hoja1!A:C,3,FALSE)</f>
-        <v>14270.18</v>
+        <v>30436.15</v>
       </c>
       <c r="E624">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F624" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625">
-        <v>62313</v>
-      </c>
-      <c r="B625" t="s">
-        <v>1114</v>
+        <v>20018</v>
       </c>
       <c r="C625" t="str">
         <f>VLOOKUP(A625,Hoja1!A:C,2,FALSE)</f>
-        <v>MUJERCITAS LATA FUNNY EDT 40ML + DEO x3 un</v>
+        <v>MAC GREGOR STRONGER EDP x12 un</v>
       </c>
       <c r="D625">
         <f>VLOOKUP(A625,Hoja1!A:C,3,FALSE)</f>
-        <v>15718.96</v>
+        <v>30436.15</v>
       </c>
       <c r="E625">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F625" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626">
-        <v>62302</v>
+        <v>59534</v>
       </c>
       <c r="B626" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="C626" t="str">
         <f>VLOOKUP(A626,Hoja1!A:C,2,FALSE)</f>
-        <v>MUJERCITAS LATA SUNNY EDT 40ML + DEO x3 un</v>
+        <v>MUJERCITAS DEO 123ML x6 un</v>
       </c>
       <c r="D626">
         <f>VLOOKUP(A626,Hoja1!A:C,3,FALSE)</f>
-        <v>15718.96</v>
+        <v>4106.41</v>
       </c>
       <c r="E626">
         <v>47</v>
@@ -20244,18 +20226,18 @@
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627">
-        <v>9013</v>
+        <v>59523</v>
       </c>
       <c r="B627" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="C627" t="str">
         <f>VLOOKUP(A627,Hoja1!A:C,2,FALSE)</f>
-        <v>MUJERCITAS SOPHIE DEO 123ML x6 un</v>
+        <v>MUJERCITAS EDT 40ML C/VAP. x6 un</v>
       </c>
       <c r="D627">
         <f>VLOOKUP(A627,Hoja1!A:C,3,FALSE)</f>
-        <v>4106.41</v>
+        <v>7648.08</v>
       </c>
       <c r="E627">
         <v>47</v>
@@ -20266,18 +20248,18 @@
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628">
-        <v>9002</v>
+        <v>59512</v>
       </c>
       <c r="B628" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="C628" t="str">
         <f>VLOOKUP(A628,Hoja1!A:C,2,FALSE)</f>
-        <v>MUJERCITAS SOPHIE EDT 50ML C/VAP x3 un</v>
+        <v>MUJERCITAS EDT 80ML C/VAP x6 un</v>
       </c>
       <c r="D628">
         <f>VLOOKUP(A628,Hoja1!A:C,3,FALSE)</f>
-        <v>14270.18</v>
+        <v>9326.92</v>
       </c>
       <c r="E628">
         <v>47</v>
@@ -20288,21 +20270,21 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629">
-        <v>581059</v>
+        <v>9115</v>
       </c>
       <c r="B629" t="s">
-        <v>1122</v>
+        <v>1110</v>
       </c>
       <c r="C629" t="str">
         <f>VLOOKUP(A629,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX DESENGRASANTE PARA COCINA x36 un</v>
+        <v>MUJERCITAS JULIE DEO 123ML x6 un</v>
       </c>
       <c r="D629">
         <f>VLOOKUP(A629,Hoja1!A:C,3,FALSE)</f>
-        <v>1029.69</v>
+        <v>4106.41</v>
       </c>
       <c r="E629">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F629" t="s">
         <v>6</v>
@@ -20310,21 +20292,21 @@
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630">
-        <v>582315</v>
+        <v>9104</v>
       </c>
       <c r="B630" t="s">
-        <v>1124</v>
+        <v>1112</v>
       </c>
       <c r="C630" t="str">
         <f>VLOOKUP(A630,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX JAB. LIQ CONCENTRADO C/BICARBON x12 un</v>
+        <v>MUJERCITAS JULIE EDT 50ML C/VAP x3 un</v>
       </c>
       <c r="D630">
         <f>VLOOKUP(A630,Hoja1!A:C,3,FALSE)</f>
-        <v>2240.58</v>
+        <v>14270.18</v>
       </c>
       <c r="E630">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F630" t="s">
         <v>6</v>
@@ -20332,21 +20314,21 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631">
-        <v>585019</v>
+        <v>62313</v>
       </c>
       <c r="B631" t="s">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="C631" t="str">
         <f>VLOOKUP(A631,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX JAB. LIQ. CON SUAVIZANTE X200ML x12 un</v>
+        <v>MUJERCITAS LATA FUNNY EDT 40ML + DEO x3 un</v>
       </c>
       <c r="D631">
         <f>VLOOKUP(A631,Hoja1!A:C,3,FALSE)</f>
-        <v>2134.88</v>
+        <v>15718.96</v>
       </c>
       <c r="E631">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F631" t="s">
         <v>6</v>
@@ -20354,21 +20336,21 @@
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632">
-        <v>586351</v>
+        <v>62302</v>
       </c>
       <c r="B632" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="C632" t="str">
         <f>VLOOKUP(A632,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX JAB. LIQ. CLASICO X200ML x12 un</v>
+        <v>MUJERCITAS LATA SUNNY EDT 40ML + DEO x3 un</v>
       </c>
       <c r="D632">
         <f>VLOOKUP(A632,Hoja1!A:C,3,FALSE)</f>
-        <v>1922.52</v>
+        <v>15718.96</v>
       </c>
       <c r="E632">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F632" t="s">
         <v>6</v>
@@ -20376,21 +20358,21 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633">
-        <v>583039</v>
+        <v>9013</v>
       </c>
       <c r="B633" t="s">
-        <v>1130</v>
+        <v>1118</v>
       </c>
       <c r="C633" t="str">
         <f>VLOOKUP(A633,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX LIMPIADOR BAÑO  X100ML x36 un</v>
+        <v>MUJERCITAS SOPHIE DEO 123ML x6 un</v>
       </c>
       <c r="D633">
         <f>VLOOKUP(A633,Hoja1!A:C,3,FALSE)</f>
-        <v>1029.69</v>
+        <v>4106.41</v>
       </c>
       <c r="E633">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F633" t="s">
         <v>6</v>
@@ -20398,21 +20380,21 @@
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634">
-        <v>583022</v>
+        <v>9002</v>
       </c>
       <c r="B634" t="s">
-        <v>1132</v>
+        <v>1120</v>
       </c>
       <c r="C634" t="str">
         <f>VLOOKUP(A634,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX LIMPIADOR DE VIDRIOS X100ML x36 un</v>
+        <v>MUJERCITAS SOPHIE EDT 50ML C/VAP x3 un</v>
       </c>
       <c r="D634">
         <f>VLOOKUP(A634,Hoja1!A:C,3,FALSE)</f>
-        <v>1029.69</v>
+        <v>14270.18</v>
       </c>
       <c r="E634">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F634" t="s">
         <v>6</v>
@@ -20420,18 +20402,18 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635">
-        <v>581097</v>
+        <v>581059</v>
       </c>
       <c r="B635" t="s">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="C635" t="str">
         <f>VLOOKUP(A635,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX LIMP.DESO.LIMON 150ML x15 un</v>
+        <v>MULTIMAX DESENGRASANTE PARA COCINA x36 un</v>
       </c>
       <c r="D635">
         <f>VLOOKUP(A635,Hoja1!A:C,3,FALSE)</f>
-        <v>2216.04</v>
+        <v>1029.69</v>
       </c>
       <c r="E635">
         <v>48</v>
@@ -20442,18 +20424,18 @@
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A636">
-        <v>581066</v>
+        <v>582315</v>
       </c>
       <c r="B636" t="s">
-        <v>1136</v>
+        <v>1124</v>
       </c>
       <c r="C636" t="str">
         <f>VLOOKUP(A636,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX LIMP.DESO.CHERRY 150ML x15 un</v>
+        <v>MULTIMAX JAB. LIQ CONCENTRADO C/BICARBON x12 un</v>
       </c>
       <c r="D636">
         <f>VLOOKUP(A636,Hoja1!A:C,3,FALSE)</f>
-        <v>2216.04</v>
+        <v>2240.58</v>
       </c>
       <c r="E636">
         <v>48</v>
@@ -20464,18 +20446,18 @@
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637">
-        <v>581738</v>
+        <v>585019</v>
       </c>
       <c r="B637" t="s">
-        <v>1138</v>
+        <v>1126</v>
       </c>
       <c r="C637" t="str">
         <f>VLOOKUP(A637,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX LIMP.DESO.CITRONELA 150ML x15 un</v>
+        <v>MULTIMAX JAB. LIQ. CON SUAVIZANTE X200ML x12 un</v>
       </c>
       <c r="D637">
         <f>VLOOKUP(A637,Hoja1!A:C,3,FALSE)</f>
-        <v>2216.04</v>
+        <v>2134.88</v>
       </c>
       <c r="E637">
         <v>48</v>
@@ -20486,18 +20468,18 @@
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638">
-        <v>581332</v>
+        <v>586351</v>
       </c>
       <c r="B638" t="s">
-        <v>1140</v>
+        <v>1128</v>
       </c>
       <c r="C638" t="str">
         <f>VLOOKUP(A638,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX LIMP. DESO.COCO VAIN 150ML x15 un</v>
+        <v>MULTIMAX JAB. LIQ. CLASICO X200ML x12 un</v>
       </c>
       <c r="D638">
         <f>VLOOKUP(A638,Hoja1!A:C,3,FALSE)</f>
-        <v>2216.04</v>
+        <v>1922.52</v>
       </c>
       <c r="E638">
         <v>48</v>
@@ -20508,18 +20490,18 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639">
-        <v>581103</v>
+        <v>583039</v>
       </c>
       <c r="B639" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="C639" t="str">
         <f>VLOOKUP(A639,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX LIMP.DESO.LAVANDA 150ML x15 un</v>
+        <v>MULTIMAX LIMPIADOR BAÑO  X100ML x36 un</v>
       </c>
       <c r="D639">
         <f>VLOOKUP(A639,Hoja1!A:C,3,FALSE)</f>
-        <v>554.01</v>
+        <v>1029.69</v>
       </c>
       <c r="E639">
         <v>48</v>
@@ -20530,18 +20512,18 @@
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640">
-        <v>581073</v>
+        <v>583022</v>
       </c>
       <c r="B640" t="s">
-        <v>1144</v>
+        <v>1132</v>
       </c>
       <c r="C640" t="str">
         <f>VLOOKUP(A640,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX LIMP.DESO.MARINA 150ML x15 un</v>
+        <v>MULTIMAX LIMPIADOR DE VIDRIOS X100ML x36 un</v>
       </c>
       <c r="D640">
         <f>VLOOKUP(A640,Hoja1!A:C,3,FALSE)</f>
-        <v>554.01</v>
+        <v>1029.69</v>
       </c>
       <c r="E640">
         <v>48</v>
@@ -20552,14 +20534,14 @@
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641">
-        <v>581080</v>
+        <v>581097</v>
       </c>
       <c r="B641" t="s">
-        <v>1146</v>
+        <v>1134</v>
       </c>
       <c r="C641" t="str">
         <f>VLOOKUP(A641,Hoja1!A:C,2,FALSE)</f>
-        <v>MULTIMAX LIMP.DESO.PINO 150ML x15 un</v>
+        <v>MULTIMAX LIMP.DESO.LIMON 150ML x15 un</v>
       </c>
       <c r="D641">
         <f>VLOOKUP(A641,Hoja1!A:C,3,FALSE)</f>
@@ -20574,21 +20556,21 @@
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642">
-        <v>17335</v>
+        <v>581066</v>
       </c>
       <c r="B642" t="s">
-        <v>1148</v>
+        <v>1136</v>
       </c>
       <c r="C642" t="str">
         <f>VLOOKUP(A642,Hoja1!A:C,2,FALSE)</f>
-        <v>PACO DEO 150ML x6 un</v>
+        <v>MULTIMAX LIMP.DESO.CHERRY 150ML x15 un</v>
       </c>
       <c r="D642">
         <f>VLOOKUP(A642,Hoja1!A:C,3,FALSE)</f>
-        <v>4168.17</v>
+        <v>2216.04</v>
       </c>
       <c r="E642">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F642" t="s">
         <v>6</v>
@@ -20596,21 +20578,21 @@
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643">
-        <v>12723</v>
+        <v>581738</v>
       </c>
       <c r="B643" t="s">
-        <v>1150</v>
+        <v>1138</v>
       </c>
       <c r="C643" t="str">
         <f>VLOOKUP(A643,Hoja1!A:C,2,FALSE)</f>
-        <v>PACO DEO SURF 150CC x6 un</v>
+        <v>MULTIMAX LIMP.DESO.CITRONELA 150ML x15 un</v>
       </c>
       <c r="D643">
         <f>VLOOKUP(A643,Hoja1!A:C,3,FALSE)</f>
-        <v>4168.17</v>
+        <v>2216.04</v>
       </c>
       <c r="E643">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F643" t="s">
         <v>6</v>
@@ -20618,21 +20600,21 @@
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644">
-        <v>17313</v>
+        <v>581332</v>
       </c>
       <c r="B644" t="s">
-        <v>1152</v>
+        <v>1140</v>
       </c>
       <c r="C644" t="str">
         <f>VLOOKUP(A644,Hoja1!A:C,2,FALSE)</f>
-        <v>PACO EDT 60ML C/VAP. x6 un</v>
+        <v>MULTIMAX LIMP. DESO.COCO VAIN 150ML x15 un</v>
       </c>
       <c r="D644">
         <f>VLOOKUP(A644,Hoja1!A:C,3,FALSE)</f>
-        <v>7648.08</v>
+        <v>2216.04</v>
       </c>
       <c r="E644">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F644" t="s">
         <v>6</v>
@@ -20640,21 +20622,21 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645">
-        <v>17302</v>
+        <v>581103</v>
       </c>
       <c r="B645" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="C645" t="str">
         <f>VLOOKUP(A645,Hoja1!A:C,2,FALSE)</f>
-        <v>PACO EDT 90ML C/VAP x6 un</v>
+        <v>MULTIMAX LIMP.DESO.LAVANDA 150ML x15 un</v>
       </c>
       <c r="D645">
         <f>VLOOKUP(A645,Hoja1!A:C,3,FALSE)</f>
-        <v>8300.9599999999991</v>
+        <v>554.01</v>
       </c>
       <c r="E645">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F645" t="s">
         <v>6</v>
@@ -20662,21 +20644,21 @@
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646">
-        <v>12735</v>
+        <v>581073</v>
       </c>
       <c r="B646" t="s">
-        <v>1156</v>
+        <v>1144</v>
       </c>
       <c r="C646" t="str">
         <f>VLOOKUP(A646,Hoja1!A:C,2,FALSE)</f>
-        <v>PACO SURF EAU DE TOILETTE C/VAP.  60ML 7 x3 un</v>
+        <v>MULTIMAX LIMP.DESO.MARINA 150ML x15 un</v>
       </c>
       <c r="D646">
         <f>VLOOKUP(A646,Hoja1!A:C,3,FALSE)</f>
-        <v>11751.92</v>
+        <v>554.01</v>
       </c>
       <c r="E646">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F646" t="s">
         <v>6</v>
@@ -20684,21 +20666,21 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647">
-        <v>5737</v>
+        <v>581080</v>
       </c>
       <c r="B647" t="s">
-        <v>1158</v>
+        <v>1146</v>
       </c>
       <c r="C647" t="str">
         <f>VLOOKUP(A647,Hoja1!A:C,2,FALSE)</f>
-        <v>PALOMA HERRERA COMBO (EDP 60ML+DEO 123ML x1 un</v>
+        <v>MULTIMAX LIMP.DESO.PINO 150ML x15 un</v>
       </c>
       <c r="D647">
         <f>VLOOKUP(A647,Hoja1!A:C,3,FALSE)</f>
-        <v>37214.42</v>
+        <v>2216.04</v>
       </c>
       <c r="E647">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F647" t="s">
         <v>6</v>
@@ -20706,21 +20688,21 @@
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648">
-        <v>5726</v>
+        <v>17335</v>
       </c>
       <c r="B648" t="s">
-        <v>1160</v>
+        <v>1148</v>
       </c>
       <c r="C648" t="str">
         <f>VLOOKUP(A648,Hoja1!A:C,2,FALSE)</f>
-        <v>PALOMA HERRERA DEO 123ML x6 un</v>
+        <v>PACO DEO 150ML x6 un</v>
       </c>
       <c r="D648">
         <f>VLOOKUP(A648,Hoja1!A:C,3,FALSE)</f>
-        <v>4756.74</v>
+        <v>4168.17</v>
       </c>
       <c r="E648">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F648" t="s">
         <v>6</v>
@@ -20728,21 +20710,21 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649">
-        <v>5704</v>
+        <v>12723</v>
       </c>
       <c r="B649" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
       <c r="C649" t="str">
         <f>VLOOKUP(A649,Hoja1!A:C,2,FALSE)</f>
-        <v>PALOMA HERRERA EAU 100ML C/VAP x3 un</v>
+        <v>PACO DEO SURF 150CC x6 un</v>
       </c>
       <c r="D649">
         <f>VLOOKUP(A649,Hoja1!A:C,3,FALSE)</f>
-        <v>35025.339999999997</v>
+        <v>4168.17</v>
       </c>
       <c r="E649">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F649" t="s">
         <v>6</v>
@@ -20750,21 +20732,21 @@
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650">
-        <v>5715</v>
+        <v>17313</v>
       </c>
       <c r="B650" t="s">
-        <v>1164</v>
+        <v>1152</v>
       </c>
       <c r="C650" t="str">
         <f>VLOOKUP(A650,Hoja1!A:C,2,FALSE)</f>
-        <v>PALOMA HERRERA EAU 60ML x3 un</v>
+        <v>PACO EDT 60ML C/VAP. x6 un</v>
       </c>
       <c r="D650">
         <f>VLOOKUP(A650,Hoja1!A:C,3,FALSE)</f>
-        <v>28529.42</v>
+        <v>7648.08</v>
       </c>
       <c r="E650">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F650" t="s">
         <v>6</v>
@@ -20772,21 +20754,21 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651">
-        <v>10613</v>
+        <v>17302</v>
       </c>
       <c r="B651" t="s">
-        <v>1166</v>
+        <v>1154</v>
       </c>
       <c r="C651" t="str">
         <f>VLOOKUP(A651,Hoja1!A:C,2,FALSE)</f>
-        <v>PALOMA HERRERA FANTASY EAU DE PARFUM C/V x3 un</v>
+        <v>PACO EDT 90ML C/VAP x6 un</v>
       </c>
       <c r="D651">
         <f>VLOOKUP(A651,Hoja1!A:C,3,FALSE)</f>
-        <v>28529.42</v>
+        <v>8300.9599999999991</v>
       </c>
       <c r="E651">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F651" t="s">
         <v>6</v>
@@ -20794,21 +20776,21 @@
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652">
-        <v>18627</v>
+        <v>12735</v>
       </c>
       <c r="B652" t="s">
-        <v>1168</v>
+        <v>1156</v>
       </c>
       <c r="C652" t="str">
         <f>VLOOKUP(A652,Hoja1!A:C,2,FALSE)</f>
-        <v>PALOMA PASSION DEO 123ML x6 un</v>
+        <v>PACO SURF EAU DE TOILETTE C/VAP.  60ML 7 x3 un</v>
       </c>
       <c r="D652">
         <f>VLOOKUP(A652,Hoja1!A:C,3,FALSE)</f>
-        <v>4756.74</v>
+        <v>11751.92</v>
       </c>
       <c r="E652">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F652" t="s">
         <v>6</v>
@@ -20816,18 +20798,18 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653">
-        <v>18605</v>
+        <v>5737</v>
       </c>
       <c r="B653" t="s">
-        <v>1170</v>
+        <v>1158</v>
       </c>
       <c r="C653" t="str">
         <f>VLOOKUP(A653,Hoja1!A:C,2,FALSE)</f>
-        <v>PALOMA PASSION EAU 100ML C/VAP x3 un</v>
+        <v>PALOMA HERRERA COMBO (EDP 60ML+DEO 123ML x1 un</v>
       </c>
       <c r="D653">
         <f>VLOOKUP(A653,Hoja1!A:C,3,FALSE)</f>
-        <v>35025.339999999997</v>
+        <v>37214.42</v>
       </c>
       <c r="E653">
         <v>50</v>
@@ -20838,18 +20820,18 @@
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654">
-        <v>18616</v>
+        <v>5726</v>
       </c>
       <c r="B654" t="s">
-        <v>1172</v>
+        <v>1160</v>
       </c>
       <c r="C654" t="str">
         <f>VLOOKUP(A654,Hoja1!A:C,2,FALSE)</f>
-        <v>PALOMA PASSION EAU 60ML C/VAP x3 un</v>
+        <v>PALOMA HERRERA DEO 123ML x6 un</v>
       </c>
       <c r="D654">
         <f>VLOOKUP(A654,Hoja1!A:C,3,FALSE)</f>
-        <v>28529.42</v>
+        <v>4756.74</v>
       </c>
       <c r="E654">
         <v>50</v>
@@ -20860,18 +20842,18 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A655">
-        <v>18638</v>
+        <v>5704</v>
       </c>
       <c r="B655" t="s">
-        <v>1174</v>
+        <v>1162</v>
       </c>
       <c r="C655" t="str">
         <f>VLOOKUP(A655,Hoja1!A:C,2,FALSE)</f>
-        <v>PALOMA PASSION EST.COMB.(EDP 60ML + DEO x1 un</v>
+        <v>PALOMA HERRERA EAU 100ML C/VAP x3 un</v>
       </c>
       <c r="D655">
         <f>VLOOKUP(A655,Hoja1!A:C,3,FALSE)</f>
-        <v>37214.42</v>
+        <v>35025.339999999997</v>
       </c>
       <c r="E655">
         <v>50</v>
@@ -20882,21 +20864,21 @@
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656">
-        <v>60048</v>
+        <v>5715</v>
       </c>
       <c r="B656" t="s">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="C656" t="str">
         <f>VLOOKUP(A656,Hoja1!A:C,2,FALSE)</f>
-        <v>PATITO ESPONJA ACERO ULTRA 12 U x12 un</v>
+        <v>PALOMA HERRERA EAU 60ML x3 un</v>
       </c>
       <c r="D656">
         <f>VLOOKUP(A656,Hoja1!A:C,3,FALSE)</f>
-        <v>1095</v>
+        <v>28529.42</v>
       </c>
       <c r="E656">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F656" t="s">
         <v>6</v>
@@ -20904,21 +20886,21 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657">
-        <v>60046</v>
+        <v>10613</v>
       </c>
       <c r="B657" t="s">
-        <v>1178</v>
+        <v>1166</v>
       </c>
       <c r="C657" t="str">
         <f>VLOOKUP(A657,Hoja1!A:C,2,FALSE)</f>
-        <v>PATITO ESPONJA DORADA 12 U x12 un</v>
+        <v>PALOMA HERRERA FANTASY EAU DE PARFUM C/V x3 un</v>
       </c>
       <c r="D657">
         <f>VLOOKUP(A657,Hoja1!A:C,3,FALSE)</f>
-        <v>1537.99</v>
+        <v>28529.42</v>
       </c>
       <c r="E657">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F657" t="s">
         <v>6</v>
@@ -20926,21 +20908,21 @@
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A658">
-        <v>60047</v>
+        <v>18627</v>
       </c>
       <c r="B658" t="s">
-        <v>1180</v>
+        <v>1168</v>
       </c>
       <c r="C658" t="str">
         <f>VLOOKUP(A658,Hoja1!A:C,2,FALSE)</f>
-        <v>PATITO ESPONJA DORADA ECO  12 U x12 un</v>
+        <v>PALOMA PASSION DEO 123ML x6 un</v>
       </c>
       <c r="D658">
         <f>VLOOKUP(A658,Hoja1!A:C,3,FALSE)</f>
-        <v>1404</v>
+        <v>4756.74</v>
       </c>
       <c r="E658">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F658" t="s">
         <v>6</v>
@@ -20948,21 +20930,21 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659">
-        <v>60045</v>
+        <v>18605</v>
       </c>
       <c r="B659" t="s">
-        <v>1182</v>
+        <v>1170</v>
       </c>
       <c r="C659" t="str">
         <f>VLOOKUP(A659,Hoja1!A:C,2,FALSE)</f>
-        <v>PATITO ESPONJA SALVAUÑAS 1 U x12 un</v>
+        <v>PALOMA PASSION EAU 100ML C/VAP x3 un</v>
       </c>
       <c r="D659">
         <f>VLOOKUP(A659,Hoja1!A:C,3,FALSE)</f>
-        <v>1097</v>
+        <v>35025.339999999997</v>
       </c>
       <c r="E659">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F659" t="s">
         <v>6</v>
@@ -20970,21 +20952,21 @@
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660">
-        <v>60050</v>
+        <v>18616</v>
       </c>
       <c r="B660" t="s">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="C660" t="str">
         <f>VLOOKUP(A660,Hoja1!A:C,2,FALSE)</f>
-        <v>PATITO GUANTE CHICO 6 U x6 un</v>
+        <v>PALOMA PASSION EAU 60ML C/VAP x3 un</v>
       </c>
       <c r="D660">
         <f>VLOOKUP(A660,Hoja1!A:C,3,FALSE)</f>
-        <v>2423</v>
+        <v>28529.42</v>
       </c>
       <c r="E660">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F660" t="s">
         <v>6</v>
@@ -20992,21 +20974,21 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661">
-        <v>60056</v>
+        <v>18638</v>
       </c>
       <c r="B661" t="s">
-        <v>1186</v>
+        <v>1174</v>
       </c>
       <c r="C661" t="str">
         <f>VLOOKUP(A661,Hoja1!A:C,2,FALSE)</f>
-        <v>PATITO GUANTE EXTRA GRANDE 6 U x6 un</v>
+        <v>PALOMA PASSION EST.COMB.(EDP 60ML + DEO x1 un</v>
       </c>
       <c r="D661">
         <f>VLOOKUP(A661,Hoja1!A:C,3,FALSE)</f>
-        <v>2423</v>
+        <v>37214.42</v>
       </c>
       <c r="E661">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F661" t="s">
         <v>6</v>
@@ -21014,18 +20996,18 @@
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662">
-        <v>60052</v>
+        <v>60048</v>
       </c>
       <c r="B662" t="s">
-        <v>1188</v>
+        <v>1176</v>
       </c>
       <c r="C662" t="str">
         <f>VLOOKUP(A662,Hoja1!A:C,2,FALSE)</f>
-        <v>PATITO GUANTE GRANDE 6 U x6 un</v>
+        <v>PATITO ESPONJA ACERO ULTRA 12 U x12 un</v>
       </c>
       <c r="D662">
         <f>VLOOKUP(A662,Hoja1!A:C,3,FALSE)</f>
-        <v>2423</v>
+        <v>1095</v>
       </c>
       <c r="E662">
         <v>51</v>
@@ -21036,18 +21018,18 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663">
-        <v>60051</v>
+        <v>60046</v>
       </c>
       <c r="B663" t="s">
-        <v>1190</v>
+        <v>1178</v>
       </c>
       <c r="C663" t="str">
         <f>VLOOKUP(A663,Hoja1!A:C,2,FALSE)</f>
-        <v>PATITO GUANTE MEDIANO 6 U x6 un</v>
+        <v>PATITO ESPONJA DORADA 12 U x12 un</v>
       </c>
       <c r="D663">
         <f>VLOOKUP(A663,Hoja1!A:C,3,FALSE)</f>
-        <v>2423</v>
+        <v>1537.99</v>
       </c>
       <c r="E663">
         <v>51</v>
@@ -21058,18 +21040,18 @@
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664">
-        <v>60042</v>
+        <v>60047</v>
       </c>
       <c r="B664" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="C664" t="str">
         <f>VLOOKUP(A664,Hoja1!A:C,2,FALSE)</f>
-        <v>PATITO MOP ALGODON 1 U x12 un</v>
+        <v>PATITO ESPONJA DORADA ECO  12 U x12 un</v>
       </c>
       <c r="D664">
         <f>VLOOKUP(A664,Hoja1!A:C,3,FALSE)</f>
-        <v>5162.01</v>
+        <v>1404</v>
       </c>
       <c r="E664">
         <v>51</v>
@@ -21080,18 +21062,18 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665">
-        <v>60043</v>
+        <v>60045</v>
       </c>
       <c r="B665" t="s">
-        <v>1194</v>
+        <v>1182</v>
       </c>
       <c r="C665" t="str">
         <f>VLOOKUP(A665,Hoja1!A:C,2,FALSE)</f>
-        <v>PATITO PAÑO ALGODON PISO 1 U x60 un</v>
+        <v>PATITO ESPONJA SALVAUÑAS 1 U x12 un</v>
       </c>
       <c r="D665">
         <f>VLOOKUP(A665,Hoja1!A:C,3,FALSE)</f>
-        <v>1723</v>
+        <v>1097</v>
       </c>
       <c r="E665">
         <v>51</v>
@@ -21102,18 +21084,18 @@
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666">
-        <v>60070</v>
+        <v>60050</v>
       </c>
       <c r="B666" t="s">
-        <v>1196</v>
+        <v>1184</v>
       </c>
       <c r="C666" t="str">
         <f>VLOOKUP(A666,Hoja1!A:C,2,FALSE)</f>
-        <v>PATITO PAÑO MULTIUSO 2 U x30 un</v>
+        <v>PATITO GUANTE CHICO 6 U x6 un</v>
       </c>
       <c r="D666">
         <f>VLOOKUP(A666,Hoja1!A:C,3,FALSE)</f>
-        <v>2723</v>
+        <v>2423</v>
       </c>
       <c r="E666">
         <v>51</v>
@@ -21124,21 +21106,21 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667">
-        <v>67831</v>
+        <v>60056</v>
       </c>
       <c r="B667" t="s">
-        <v>1198</v>
+        <v>1186</v>
       </c>
       <c r="C667" t="str">
         <f>VLOOKUP(A667,Hoja1!A:C,2,FALSE)</f>
-        <v>PAULA CACHEN DANVERS ESTUCHE(EDT 60ML+DE x1 un</v>
+        <v>PATITO GUANTE EXTRA GRANDE 6 U x6 un</v>
       </c>
       <c r="D667">
         <f>VLOOKUP(A667,Hoja1!A:C,3,FALSE)</f>
-        <v>111643.25</v>
+        <v>2423</v>
       </c>
       <c r="E667">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F667" t="s">
         <v>6</v>
@@ -21146,21 +21128,21 @@
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668">
-        <v>84325</v>
+        <v>60052</v>
       </c>
       <c r="B668" t="s">
-        <v>1200</v>
+        <v>1188</v>
       </c>
       <c r="C668" t="str">
         <f>VLOOKUP(A668,Hoja1!A:C,2,FALSE)</f>
-        <v>PAULA CAHEN D ANVERS DEO ALMA 123ML x6 un</v>
+        <v>PATITO GUANTE GRANDE 6 U x6 un</v>
       </c>
       <c r="D668">
         <f>VLOOKUP(A668,Hoja1!A:C,3,FALSE)</f>
-        <v>4756.74</v>
+        <v>2423</v>
       </c>
       <c r="E668">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F668" t="s">
         <v>6</v>
@@ -21168,21 +21150,21 @@
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669">
-        <v>4559</v>
+        <v>60051</v>
       </c>
       <c r="B669" t="s">
-        <v>1202</v>
+        <v>1190</v>
       </c>
       <c r="C669" t="str">
         <f>VLOOKUP(A669,Hoja1!A:C,2,FALSE)</f>
-        <v>PAULA CAHEN D ANVERS DEO CLASICO 123ML x6 un</v>
+        <v>PATITO GUANTE MEDIANO 6 U x6 un</v>
       </c>
       <c r="D669">
         <f>VLOOKUP(A669,Hoja1!A:C,3,FALSE)</f>
-        <v>4756.74</v>
+        <v>2423</v>
       </c>
       <c r="E669">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F669" t="s">
         <v>6</v>
@@ -21190,21 +21172,21 @@
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670">
-        <v>84303</v>
+        <v>60042</v>
       </c>
       <c r="B670" t="s">
-        <v>1204</v>
+        <v>1192</v>
       </c>
       <c r="C670" t="str">
         <f>VLOOKUP(A670,Hoja1!A:C,2,FALSE)</f>
-        <v>PAULA CAHEN D ANVERS EDT ALMA 60ML x3 un</v>
+        <v>PATITO MOP ALGODON 1 U x12 un</v>
       </c>
       <c r="D670">
         <f>VLOOKUP(A670,Hoja1!A:C,3,FALSE)</f>
-        <v>28880.55</v>
+        <v>5162.01</v>
       </c>
       <c r="E670">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F670" t="s">
         <v>6</v>
@@ -21212,21 +21194,21 @@
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671">
-        <v>4541</v>
+        <v>60043</v>
       </c>
       <c r="B671" t="s">
-        <v>1206</v>
+        <v>1194</v>
       </c>
       <c r="C671" t="str">
         <f>VLOOKUP(A671,Hoja1!A:C,2,FALSE)</f>
-        <v>PAULA CAHEN D ANVERS EDT CLASICO 100ML x6 un</v>
+        <v>PATITO PAÑO ALGODON PISO 1 U x60 un</v>
       </c>
       <c r="D671">
         <f>VLOOKUP(A671,Hoja1!A:C,3,FALSE)</f>
-        <v>35903.18</v>
+        <v>1723</v>
       </c>
       <c r="E671">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F671" t="s">
         <v>6</v>
@@ -21234,21 +21216,21 @@
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672">
-        <v>4534</v>
+        <v>60070</v>
       </c>
       <c r="B672" t="s">
-        <v>1208</v>
+        <v>1196</v>
       </c>
       <c r="C672" t="str">
         <f>VLOOKUP(A672,Hoja1!A:C,2,FALSE)</f>
-        <v>PAULA CAHEN D ANVERS EDT CLASICO 60ML x3 un</v>
+        <v>PATITO PAÑO MULTIUSO 2 U x30 un</v>
       </c>
       <c r="D672">
         <f>VLOOKUP(A672,Hoja1!A:C,3,FALSE)</f>
-        <v>28880.55</v>
+        <v>2723</v>
       </c>
       <c r="E672">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F672" t="s">
         <v>6</v>
@@ -21256,18 +21238,18 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673">
-        <v>31113</v>
+        <v>67831</v>
       </c>
       <c r="B673" t="s">
-        <v>1210</v>
+        <v>1198</v>
       </c>
       <c r="C673" t="str">
         <f>VLOOKUP(A673,Hoja1!A:C,2,FALSE)</f>
-        <v>PAULA CAHEN DANVERS ALEGRIA 100ML C/VAP x3 un</v>
+        <v>PAULA CACHEN DANVERS ESTUCHE(EDT 60ML+DE x1 un</v>
       </c>
       <c r="D673">
         <f>VLOOKUP(A673,Hoja1!A:C,3,FALSE)</f>
-        <v>35903.18</v>
+        <v>111643.25</v>
       </c>
       <c r="E673">
         <v>52</v>
@@ -21278,18 +21260,18 @@
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674">
-        <v>31102</v>
+        <v>84325</v>
       </c>
       <c r="B674" t="s">
-        <v>1212</v>
+        <v>1200</v>
       </c>
       <c r="C674" t="str">
         <f>VLOOKUP(A674,Hoja1!A:C,2,FALSE)</f>
-        <v>PAULA CAHEN DANVERS ALEGRIA 60ML C/VAP x3 un</v>
+        <v>PAULA CAHEN D ANVERS DEO ALMA 123ML x6 un</v>
       </c>
       <c r="D674">
         <f>VLOOKUP(A674,Hoja1!A:C,3,FALSE)</f>
-        <v>28880.55</v>
+        <v>4756.74</v>
       </c>
       <c r="E674">
         <v>52</v>
@@ -21300,14 +21282,14 @@
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675">
-        <v>31124</v>
+        <v>4559</v>
       </c>
       <c r="B675" t="s">
-        <v>1214</v>
+        <v>1202</v>
       </c>
       <c r="C675" t="str">
         <f>VLOOKUP(A675,Hoja1!A:C,2,FALSE)</f>
-        <v>PAULA CAHEN DANVERS ALEGRIA DEO 123ML x6 un</v>
+        <v>PAULA CAHEN D ANVERS DEO CLASICO 123ML x6 un</v>
       </c>
       <c r="D675">
         <f>VLOOKUP(A675,Hoja1!A:C,3,FALSE)</f>
@@ -21322,21 +21304,21 @@
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676">
-        <v>5009</v>
+        <v>84303</v>
       </c>
       <c r="B676" t="s">
-        <v>1216</v>
+        <v>1204</v>
       </c>
       <c r="C676" t="str">
         <f>VLOOKUP(A676,Hoja1!A:C,2,FALSE)</f>
-        <v>PIBES COLONIA 95ML C/VAP. x6 un</v>
+        <v>PAULA CAHEN D ANVERS EDT ALMA 60ML x3 un</v>
       </c>
       <c r="D676">
         <f>VLOOKUP(A676,Hoja1!A:C,3,FALSE)</f>
-        <v>8300.9599999999991</v>
+        <v>28880.55</v>
       </c>
       <c r="E676">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F676" t="s">
         <v>6</v>
@@ -21344,21 +21326,21 @@
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677">
-        <v>57142</v>
+        <v>4541</v>
       </c>
       <c r="B677" t="s">
-        <v>1218</v>
+        <v>1206</v>
       </c>
       <c r="C677" t="str">
         <f>VLOOKUP(A677,Hoja1!A:C,2,FALSE)</f>
-        <v>PINO COLBERT EDT 60ML C/VAP x3 un</v>
+        <v>PAULA CAHEN D ANVERS EDT CLASICO 100ML x6 un</v>
       </c>
       <c r="D677">
         <f>VLOOKUP(A677,Hoja1!A:C,3,FALSE)</f>
-        <v>10725.96</v>
+        <v>35903.18</v>
       </c>
       <c r="E677">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F677" t="s">
         <v>6</v>
@@ -21366,21 +21348,21 @@
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678">
-        <v>57153</v>
+        <v>4534</v>
       </c>
       <c r="B678" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="C678" t="str">
         <f>VLOOKUP(A678,Hoja1!A:C,2,FALSE)</f>
-        <v>PINO DEO COLBERT 150ML x6 un</v>
+        <v>PAULA CAHEN D ANVERS EDT CLASICO 60ML x3 un</v>
       </c>
       <c r="D678">
         <f>VLOOKUP(A678,Hoja1!A:C,3,FALSE)</f>
-        <v>4940.05</v>
+        <v>28880.55</v>
       </c>
       <c r="E678">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F678" t="s">
         <v>6</v>
@@ -21388,21 +21370,21 @@
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679">
-        <v>10135</v>
+        <v>31113</v>
       </c>
       <c r="B679" t="s">
-        <v>1222</v>
+        <v>1210</v>
       </c>
       <c r="C679" t="str">
         <f>VLOOKUP(A679,Hoja1!A:C,2,FALSE)</f>
-        <v>PRO CEPILLO DOBLE ACCION PROFILE X2U. x12 un</v>
+        <v>PAULA CAHEN DANVERS ALEGRIA 100ML C/VAP x3 un</v>
       </c>
       <c r="D679">
         <f>VLOOKUP(A679,Hoja1!A:C,3,FALSE)</f>
-        <v>7902</v>
+        <v>35903.18</v>
       </c>
       <c r="E679">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F679" t="s">
         <v>6</v>
@@ -21410,21 +21392,21 @@
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680">
-        <v>600106</v>
+        <v>31102</v>
       </c>
       <c r="B680" t="s">
-        <v>1223</v>
+        <v>1212</v>
       </c>
       <c r="C680" t="str">
         <f>VLOOKUP(A680,Hoja1!A:C,2,FALSE)</f>
-        <v>PRO CEPILLO DOBLE ACCION  X 1U x12 un</v>
+        <v>PAULA CAHEN DANVERS ALEGRIA 60ML C/VAP x3 un</v>
       </c>
       <c r="D680">
         <f>VLOOKUP(A680,Hoja1!A:C,3,FALSE)</f>
-        <v>3607</v>
+        <v>28880.55</v>
       </c>
       <c r="E680">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F680" t="s">
         <v>6</v>
@@ -21432,21 +21414,21 @@
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681">
-        <v>600107</v>
+        <v>31124</v>
       </c>
       <c r="B681" t="s">
-        <v>1224</v>
+        <v>1214</v>
       </c>
       <c r="C681" t="str">
         <f>VLOOKUP(A681,Hoja1!A:C,2,FALSE)</f>
-        <v>PRO CEPILLO PLUS CUIDADO DE ENCIAS X 3U x12 un</v>
+        <v>PAULA CAHEN DANVERS ALEGRIA DEO 123ML x6 un</v>
       </c>
       <c r="D681">
         <f>VLOOKUP(A681,Hoja1!A:C,3,FALSE)</f>
-        <v>10194</v>
+        <v>4756.74</v>
       </c>
       <c r="E681">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F681" t="s">
         <v>6</v>
@@ -21454,109 +21436,97 @@
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682">
-        <v>582377</v>
-      </c>
-      <c r="B682" t="s">
-        <v>1225</v>
+        <v>45471</v>
       </c>
       <c r="C682" t="str">
         <f>VLOOKUP(A682,Hoja1!A:C,2,FALSE)</f>
-        <v>PURIFIC AIR ANTIHUMEDAD PINO 300G x18 un</v>
+        <v>PAULA CAHEN DANVERS BODY MIST X120ML x6 un</v>
       </c>
       <c r="D682">
         <f>VLOOKUP(A682,Hoja1!A:C,3,FALSE)</f>
-        <v>7783.99</v>
+        <v>15294.12</v>
       </c>
       <c r="E682">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F682" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683">
-        <v>4100</v>
-      </c>
-      <c r="B683" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C683" t="e">
+        <v>92639</v>
+      </c>
+      <c r="C683" t="str">
         <f>VLOOKUP(A683,Hoja1!A:C,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D683" t="e">
+        <v>CARO CUORE BODY MIST AMORE X120ML x6 un</v>
+      </c>
+      <c r="D683">
         <f>VLOOKUP(A683,Hoja1!A:C,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>15294.12</v>
       </c>
       <c r="E683">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F683" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684">
-        <v>756</v>
-      </c>
-      <c r="B684" t="s">
-        <v>1228</v>
+        <v>61556</v>
       </c>
       <c r="C684" t="str">
         <f>VLOOKUP(A684,Hoja1!A:C,2,FALSE)</f>
-        <v>Q-SOFT FAMILY HISOPOS ESTUCHE X 75U x48 un</v>
+        <v>CARO CUORE BODY MIST COURE X120ML x6 un</v>
       </c>
       <c r="D684">
         <f>VLOOKUP(A684,Hoja1!A:C,3,FALSE)</f>
-        <v>2032.76</v>
+        <v>15294.12</v>
       </c>
       <c r="E684">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F684" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685">
-        <v>755</v>
-      </c>
-      <c r="B685" t="s">
-        <v>1230</v>
+        <v>65951</v>
       </c>
       <c r="C685" t="str">
         <f>VLOOKUP(A685,Hoja1!A:C,2,FALSE)</f>
-        <v>Q-SOFT FAMILY HISOPOS POTE  X 100 U x24 un</v>
+        <v>CARO CUORE BODY MIST X120ML x6 un</v>
       </c>
       <c r="D685">
         <f>VLOOKUP(A685,Hoja1!A:C,3,FALSE)</f>
-        <v>2214.41</v>
+        <v>15294.12</v>
       </c>
       <c r="E685">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F685" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686">
-        <v>4175</v>
+        <v>5009</v>
       </c>
       <c r="B686" t="s">
-        <v>1232</v>
-      </c>
-      <c r="C686" t="e">
+        <v>1216</v>
+      </c>
+      <c r="C686" t="str">
         <f>VLOOKUP(A686,Hoja1!A:C,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D686" t="e">
+        <v>PIBES COLONIA 95ML C/VAP. x6 un</v>
+      </c>
+      <c r="D686">
         <f>VLOOKUP(A686,Hoja1!A:C,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>8300.9599999999991</v>
       </c>
       <c r="E686">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F686" t="s">
         <v>6</v>
@@ -21564,21 +21534,21 @@
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A687">
-        <v>4125</v>
+        <v>57142</v>
       </c>
       <c r="B687" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C687" t="e">
+        <v>1218</v>
+      </c>
+      <c r="C687" t="str">
         <f>VLOOKUP(A687,Hoja1!A:C,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D687" t="e">
+        <v>PINO COLBERT EDT 60ML C/VAP x3 un</v>
+      </c>
+      <c r="D687">
         <f>VLOOKUP(A687,Hoja1!A:C,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>10725.96</v>
       </c>
       <c r="E687">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F687" t="s">
         <v>6</v>
@@ -21586,21 +21556,21 @@
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A688">
-        <v>757</v>
+        <v>57153</v>
       </c>
       <c r="B688" t="s">
-        <v>1234</v>
+        <v>1220</v>
       </c>
       <c r="C688" t="str">
         <f>VLOOKUP(A688,Hoja1!A:C,2,FALSE)</f>
-        <v>Q-SOFT FAMILY HISOPOS X150U x18 un</v>
+        <v>PINO DEO COLBERT 150ML x6 un</v>
       </c>
       <c r="D688">
         <f>VLOOKUP(A688,Hoja1!A:C,3,FALSE)</f>
-        <v>2468</v>
+        <v>4940.05</v>
       </c>
       <c r="E688">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F688" t="s">
         <v>6</v>
@@ -21608,21 +21578,21 @@
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A689">
-        <v>56293</v>
+        <v>10135</v>
       </c>
       <c r="B689" t="s">
-        <v>1236</v>
+        <v>1222</v>
       </c>
       <c r="C689" t="str">
         <f>VLOOKUP(A689,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY FIJADOR ANTIFRIZZ NEW 180ML x12 un</v>
+        <v>PRO CEPILLO DOBLE ACCION PROFILE X2U. x12 un</v>
       </c>
       <c r="D689">
         <f>VLOOKUP(A689,Hoja1!A:C,3,FALSE)</f>
-        <v>5072.82</v>
+        <v>7902</v>
       </c>
       <c r="E689">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F689" t="s">
         <v>6</v>
@@ -21630,21 +21600,21 @@
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A690">
-        <v>41474</v>
+        <v>600106</v>
       </c>
       <c r="B690" t="s">
-        <v>1238</v>
+        <v>1223</v>
       </c>
       <c r="C690" t="str">
         <f>VLOOKUP(A690,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY FIJADOR ANTIFRIZZ NEW 390ML x12 un</v>
+        <v>PRO CEPILLO DOBLE ACCION  X 1U x12 un</v>
       </c>
       <c r="D690">
         <f>VLOOKUP(A690,Hoja1!A:C,3,FALSE)</f>
-        <v>7326.57</v>
+        <v>3607</v>
       </c>
       <c r="E690">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F690" t="s">
         <v>6</v>
@@ -21652,21 +21622,21 @@
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A691">
-        <v>56291</v>
+        <v>600107</v>
       </c>
       <c r="B691" t="s">
-        <v>1240</v>
+        <v>1224</v>
       </c>
       <c r="C691" t="str">
         <f>VLOOKUP(A691,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY FIJADOR EXTRA FUERTE NEW 180 ML x12 un</v>
+        <v>PRO CEPILLO PLUS CUIDADO DE ENCIAS X 3U x12 un</v>
       </c>
       <c r="D691">
         <f>VLOOKUP(A691,Hoja1!A:C,3,FALSE)</f>
-        <v>5072.82</v>
+        <v>10194</v>
       </c>
       <c r="E691">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F691" t="s">
         <v>6</v>
@@ -21674,21 +21644,21 @@
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A692">
-        <v>41472</v>
+        <v>582377</v>
       </c>
       <c r="B692" t="s">
-        <v>1242</v>
+        <v>1225</v>
       </c>
       <c r="C692" t="str">
         <f>VLOOKUP(A692,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY FIJADOR EXTRA FUERTE NEW 390 ML x12 un</v>
+        <v>PURIFIC AIR ANTIHUMEDAD PINO 300G x18 un</v>
       </c>
       <c r="D692">
         <f>VLOOKUP(A692,Hoja1!A:C,3,FALSE)</f>
-        <v>7326.57</v>
+        <v>7783.99</v>
       </c>
       <c r="E692">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F692" t="s">
         <v>6</v>
@@ -21696,21 +21666,21 @@
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A693">
-        <v>56292</v>
+        <v>4100</v>
       </c>
       <c r="B693" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C693" t="str">
+        <v>1227</v>
+      </c>
+      <c r="C693" t="e">
         <f>VLOOKUP(A693,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY FIJADOR FUERTE NEW 180 ML x12 un</v>
-      </c>
-      <c r="D693">
+        <v>#N/A</v>
+      </c>
+      <c r="D693" t="e">
         <f>VLOOKUP(A693,Hoja1!A:C,3,FALSE)</f>
-        <v>5072.82</v>
+        <v>#N/A</v>
       </c>
       <c r="E693">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F693" t="s">
         <v>6</v>
@@ -21718,21 +21688,21 @@
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A694">
-        <v>41473</v>
+        <v>756</v>
       </c>
       <c r="B694" t="s">
-        <v>1246</v>
+        <v>1228</v>
       </c>
       <c r="C694" t="str">
         <f>VLOOKUP(A694,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY FIJADOR FUERTE NEW 390 ML x12 un</v>
+        <v>Q-SOFT FAMILY HISOPOS ESTUCHE X 75U x48 un</v>
       </c>
       <c r="D694">
         <f>VLOOKUP(A694,Hoja1!A:C,3,FALSE)</f>
-        <v>7326.57</v>
+        <v>2032.76</v>
       </c>
       <c r="E694">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F694" t="s">
         <v>6</v>
@@ -21740,21 +21710,21 @@
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A695">
-        <v>41264</v>
+        <v>755</v>
       </c>
       <c r="B695" t="s">
-        <v>1248</v>
+        <v>1230</v>
       </c>
       <c r="C695" t="str">
         <f>VLOOKUP(A695,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY GEL EXTRA FUERTE CON ALOE 150G x12 un</v>
+        <v>Q-SOFT FAMILY HISOPOS POTE  X 100 U x24 un</v>
       </c>
       <c r="D695">
         <f>VLOOKUP(A695,Hoja1!A:C,3,FALSE)</f>
-        <v>2579.4899999999998</v>
+        <v>2214.41</v>
       </c>
       <c r="E695">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F695" t="s">
         <v>6</v>
@@ -21762,21 +21732,21 @@
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A696">
-        <v>41263</v>
+        <v>4175</v>
       </c>
       <c r="B696" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C696" t="str">
+        <v>1232</v>
+      </c>
+      <c r="C696" t="e">
         <f>VLOOKUP(A696,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY GEL FIJADOR CAPILAR FUERTE 150ML x12 un</v>
-      </c>
-      <c r="D696">
+        <v>#N/A</v>
+      </c>
+      <c r="D696" t="e">
         <f>VLOOKUP(A696,Hoja1!A:C,3,FALSE)</f>
-        <v>2579.4899999999998</v>
+        <v>#N/A</v>
       </c>
       <c r="E696">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F696" t="s">
         <v>6</v>
@@ -21784,10 +21754,10 @@
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A697">
-        <v>24568</v>
+        <v>4125</v>
       </c>
       <c r="B697" t="s">
-        <v>1252</v>
+        <v>1233</v>
       </c>
       <c r="C697" t="e">
         <f>VLOOKUP(A697,Hoja1!A:C,2,FALSE)</f>
@@ -21798,7 +21768,7 @@
         <v>#N/A</v>
       </c>
       <c r="E697">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F697" t="s">
         <v>6</v>
@@ -21806,21 +21776,21 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A698">
-        <v>41261</v>
+        <v>757</v>
       </c>
       <c r="B698" t="s">
-        <v>1253</v>
+        <v>1234</v>
       </c>
       <c r="C698" t="str">
         <f>VLOOKUP(A698,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY GEL FIJADOR CAPILAR NORMAL 150ML x12 un</v>
+        <v>Q-SOFT FAMILY HISOPOS X150U x18 un</v>
       </c>
       <c r="D698">
         <f>VLOOKUP(A698,Hoja1!A:C,3,FALSE)</f>
-        <v>2579.4899999999998</v>
+        <v>2468</v>
       </c>
       <c r="E698">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F698" t="s">
         <v>6</v>
@@ -21828,18 +21798,18 @@
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A699">
-        <v>41262</v>
+        <v>56293</v>
       </c>
       <c r="B699" t="s">
-        <v>1255</v>
+        <v>1236</v>
       </c>
       <c r="C699" t="str">
         <f>VLOOKUP(A699,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY GEL HUMEDO CON ALOE 150G x12 un</v>
+        <v>ROBY FIJADOR ANTIFRIZZ NEW 180ML x12 un</v>
       </c>
       <c r="D699">
         <f>VLOOKUP(A699,Hoja1!A:C,3,FALSE)</f>
-        <v>2579.4899999999998</v>
+        <v>5072.82</v>
       </c>
       <c r="E699">
         <v>58</v>
@@ -21850,18 +21820,18 @@
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A700">
-        <v>56282</v>
+        <v>41474</v>
       </c>
       <c r="B700" t="s">
-        <v>1257</v>
+        <v>1238</v>
       </c>
       <c r="C700" t="str">
         <f>VLOOKUP(A700,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY GEL SPORTMAXIMA FIJACION X150G x12 un</v>
+        <v>ROBY FIJADOR ANTIFRIZZ NEW 390ML x12 un</v>
       </c>
       <c r="D700">
         <f>VLOOKUP(A700,Hoja1!A:C,3,FALSE)</f>
-        <v>2798.58</v>
+        <v>7326.57</v>
       </c>
       <c r="E700">
         <v>58</v>
@@ -21872,18 +21842,18 @@
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A701">
-        <v>41478</v>
+        <v>56291</v>
       </c>
       <c r="B701" t="s">
-        <v>1259</v>
+        <v>1240</v>
       </c>
       <c r="C701" t="str">
         <f>VLOOKUP(A701,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY MOUSSE CAPILAR 190ML x12 un</v>
+        <v>ROBY FIJADOR EXTRA FUERTE NEW 180 ML x12 un</v>
       </c>
       <c r="D701">
         <f>VLOOKUP(A701,Hoja1!A:C,3,FALSE)</f>
-        <v>7285.69</v>
+        <v>5072.82</v>
       </c>
       <c r="E701">
         <v>58</v>
@@ -21894,18 +21864,18 @@
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A702">
-        <v>31233</v>
+        <v>41472</v>
       </c>
       <c r="B702" t="s">
-        <v>1261</v>
+        <v>1242</v>
       </c>
       <c r="C702" t="str">
         <f>VLOOKUP(A702,Hoja1!A:C,2,FALSE)</f>
-        <v>ROBY PROTECTOR TERMICO 190 ML x12 un</v>
+        <v>ROBY FIJADOR EXTRA FUERTE NEW 390 ML x12 un</v>
       </c>
       <c r="D702">
         <f>VLOOKUP(A702,Hoja1!A:C,3,FALSE)</f>
-        <v>9047.23</v>
+        <v>7326.57</v>
       </c>
       <c r="E702">
         <v>58</v>
@@ -21916,21 +21886,21 @@
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A703">
-        <v>103026</v>
+        <v>56292</v>
       </c>
       <c r="B703" t="s">
-        <v>1263</v>
+        <v>1244</v>
       </c>
       <c r="C703" t="str">
         <f>VLOOKUP(A703,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS AEROSOL  BUBBLEGUM 185 G x12 un</v>
+        <v>ROBY FIJADOR FUERTE NEW 180 ML x12 un</v>
       </c>
       <c r="D703">
         <f>VLOOKUP(A703,Hoja1!A:C,3,FALSE)</f>
-        <v>5606.24</v>
+        <v>5072.82</v>
       </c>
       <c r="E703">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F703" t="s">
         <v>6</v>
@@ -21938,21 +21908,21 @@
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A704">
-        <v>103201</v>
+        <v>41473</v>
       </c>
       <c r="B704" t="s">
-        <v>1265</v>
+        <v>1246</v>
       </c>
       <c r="C704" t="str">
         <f>VLOOKUP(A704,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS DIFUSOR AMOUR 125ML x12 un</v>
+        <v>ROBY FIJADOR FUERTE NEW 390 ML x12 un</v>
       </c>
       <c r="D704">
         <f>VLOOKUP(A704,Hoja1!A:C,3,FALSE)</f>
-        <v>5490.02</v>
+        <v>7326.57</v>
       </c>
       <c r="E704">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F704" t="s">
         <v>6</v>
@@ -21960,21 +21930,21 @@
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A705">
-        <v>103301</v>
+        <v>41264</v>
       </c>
       <c r="B705" t="s">
-        <v>1267</v>
+        <v>1248</v>
       </c>
       <c r="C705" t="str">
         <f>VLOOKUP(A705,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS HOME SPRAY BREEZE 500ML x6 un</v>
+        <v>ROBY GEL EXTRA FUERTE CON ALOE 150G x12 un</v>
       </c>
       <c r="D705">
         <f>VLOOKUP(A705,Hoja1!A:C,3,FALSE)</f>
-        <v>7749.89</v>
+        <v>2579.4899999999998</v>
       </c>
       <c r="E705">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F705" t="s">
         <v>6</v>
@@ -21982,21 +21952,21 @@
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A706">
-        <v>103101</v>
+        <v>41263</v>
       </c>
       <c r="B706" t="s">
-        <v>1269</v>
+        <v>1250</v>
       </c>
       <c r="C706" t="str">
         <f>VLOOKUP(A706,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS TEXTIL NIGHT EMPIRE 250ML x12 un</v>
+        <v>ROBY GEL FIJADOR CAPILAR FUERTE 150ML x12 un</v>
       </c>
       <c r="D706">
         <f>VLOOKUP(A706,Hoja1!A:C,3,FALSE)</f>
-        <v>3873.74</v>
+        <v>2579.4899999999998</v>
       </c>
       <c r="E706">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F706" t="s">
         <v>6</v>
@@ -22004,21 +21974,21 @@
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A707">
-        <v>103401</v>
+        <v>24568</v>
       </c>
       <c r="B707" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C707" t="str">
+        <v>1252</v>
+      </c>
+      <c r="C707" t="e">
         <f>VLOOKUP(A707,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS TOUCH REP. AGUA MARINA 9G x12 un</v>
-      </c>
-      <c r="D707">
+        <v>#N/A</v>
+      </c>
+      <c r="D707" t="e">
         <f>VLOOKUP(A707,Hoja1!A:C,3,FALSE)</f>
-        <v>3001.91</v>
+        <v>#N/A</v>
       </c>
       <c r="E707">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F707" t="s">
         <v>6</v>
@@ -22026,21 +21996,21 @@
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A708">
-        <v>103402</v>
+        <v>41261</v>
       </c>
       <c r="B708" t="s">
-        <v>1273</v>
+        <v>1253</v>
       </c>
       <c r="C708" t="str">
         <f>VLOOKUP(A708,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS TOUCH REP. FRUTOS ROJOS 9G x12 un</v>
+        <v>ROBY GEL FIJADOR CAPILAR NORMAL 150ML x12 un</v>
       </c>
       <c r="D708">
         <f>VLOOKUP(A708,Hoja1!A:C,3,FALSE)</f>
-        <v>3001.91</v>
+        <v>2579.4899999999998</v>
       </c>
       <c r="E708">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F708" t="s">
         <v>6</v>
@@ -22048,21 +22018,21 @@
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A709">
-        <v>103404</v>
+        <v>41262</v>
       </c>
       <c r="B709" t="s">
-        <v>1275</v>
+        <v>1255</v>
       </c>
       <c r="C709" t="str">
         <f>VLOOKUP(A709,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS TOUCH REP. PETALOS FLORAL 9G x12 un</v>
+        <v>ROBY GEL HUMEDO CON ALOE 150G x12 un</v>
       </c>
       <c r="D709">
         <f>VLOOKUP(A709,Hoja1!A:C,3,FALSE)</f>
-        <v>3001.91</v>
+        <v>2579.4899999999998</v>
       </c>
       <c r="E709">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F709" t="s">
         <v>6</v>
@@ -22070,21 +22040,21 @@
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A710">
-        <v>103403</v>
+        <v>56282</v>
       </c>
       <c r="B710" t="s">
-        <v>1277</v>
+        <v>1257</v>
       </c>
       <c r="C710" t="str">
         <f>VLOOKUP(A710,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS TOUCH REP. MIX CITRICO 9G x12 un</v>
+        <v>ROBY GEL SPORTMAXIMA FIJACION X150G x12 un</v>
       </c>
       <c r="D710">
         <f>VLOOKUP(A710,Hoja1!A:C,3,FALSE)</f>
-        <v>3001.91</v>
+        <v>2798.58</v>
       </c>
       <c r="E710">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F710" t="s">
         <v>6</v>
@@ -22092,21 +22062,21 @@
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A711">
-        <v>103501</v>
+        <v>41478</v>
       </c>
       <c r="B711" t="s">
-        <v>1279</v>
+        <v>1259</v>
       </c>
       <c r="C711" t="str">
         <f>VLOOKUP(A711,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS TOUCH REP.+ DISP. CITRICO ARENA x12 un</v>
+        <v>ROBY MOUSSE CAPILAR 190ML x12 un</v>
       </c>
       <c r="D711">
         <f>VLOOKUP(A711,Hoja1!A:C,3,FALSE)</f>
-        <v>4831.5200000000004</v>
+        <v>7285.69</v>
       </c>
       <c r="E711">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F711" t="s">
         <v>6</v>
@@ -22114,21 +22084,21 @@
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A712">
-        <v>103502</v>
+        <v>31233</v>
       </c>
       <c r="B712" t="s">
-        <v>1281</v>
+        <v>1261</v>
       </c>
       <c r="C712" t="str">
         <f>VLOOKUP(A712,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS TOUCH REP.+ DISP. F.ROJOS x12 un</v>
+        <v>ROBY PROTECTOR TERMICO 190 ML x12 un</v>
       </c>
       <c r="D712">
         <f>VLOOKUP(A712,Hoja1!A:C,3,FALSE)</f>
-        <v>4831.5200000000004</v>
+        <v>9047.23</v>
       </c>
       <c r="E712">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F712" t="s">
         <v>6</v>
@@ -22136,18 +22106,18 @@
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A713">
-        <v>103504</v>
+        <v>103026</v>
       </c>
       <c r="B713" t="s">
-        <v>1283</v>
+        <v>1263</v>
       </c>
       <c r="C713" t="str">
         <f>VLOOKUP(A713,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS TOUCH REP.+ DISP. PETALOS ROSA x12 un</v>
+        <v>SAPHIRUS AEROSOL  BUBBLEGUM 185 G x12 un</v>
       </c>
       <c r="D713">
         <f>VLOOKUP(A713,Hoja1!A:C,3,FALSE)</f>
-        <v>4831.5200000000004</v>
+        <v>5606.24</v>
       </c>
       <c r="E713">
         <v>59</v>
@@ -22158,18 +22128,18 @@
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A714">
-        <v>103503</v>
+        <v>103201</v>
       </c>
       <c r="B714" t="s">
-        <v>1285</v>
+        <v>1265</v>
       </c>
       <c r="C714" t="str">
         <f>VLOOKUP(A714,Hoja1!A:C,2,FALSE)</f>
-        <v>SAPHIRUS TOUCH REP.+DISP. MARINA CELESTE x12 un</v>
+        <v>SAPHIRUS DIFUSOR AMOUR 125ML x12 un</v>
       </c>
       <c r="D714">
         <f>VLOOKUP(A714,Hoja1!A:C,3,FALSE)</f>
-        <v>4831.5200000000004</v>
+        <v>5490.02</v>
       </c>
       <c r="E714">
         <v>59</v>
@@ -22180,21 +22150,21 @@
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A715">
-        <v>36003</v>
+        <v>103301</v>
       </c>
       <c r="B715" t="s">
-        <v>1287</v>
+        <v>1267</v>
       </c>
       <c r="C715" t="str">
         <f>VLOOKUP(A715,Hoja1!A:C,2,FALSE)</f>
-        <v>SENS NATURAL GROSELLAS ROSAS EDT 100 ML x3 un</v>
+        <v>SAPHIRUS HOME SPRAY BREEZE 500ML x6 un</v>
       </c>
       <c r="D715">
         <f>VLOOKUP(A715,Hoja1!A:C,3,FALSE)</f>
-        <v>19769.740000000002</v>
+        <v>7749.89</v>
       </c>
       <c r="E715">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F715" t="s">
         <v>6</v>
@@ -22202,21 +22172,21 @@
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A716">
-        <v>36025</v>
+        <v>103101</v>
       </c>
       <c r="B716" t="s">
-        <v>1289</v>
+        <v>1269</v>
       </c>
       <c r="C716" t="str">
         <f>VLOOKUP(A716,Hoja1!A:C,2,FALSE)</f>
-        <v>SENS NATURAL MAGNOLIA PERA EDT 100ML x3 un</v>
+        <v>SAPHIRUS TEXTIL NIGHT EMPIRE 250ML x12 un</v>
       </c>
       <c r="D716">
         <f>VLOOKUP(A716,Hoja1!A:C,3,FALSE)</f>
-        <v>19769.740000000002</v>
+        <v>3873.74</v>
       </c>
       <c r="E716">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F716" t="s">
         <v>6</v>
@@ -22224,21 +22194,21 @@
     </row>
     <row r="717" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A717">
-        <v>36036</v>
+        <v>103401</v>
       </c>
       <c r="B717" t="s">
-        <v>1291</v>
+        <v>1271</v>
       </c>
       <c r="C717" t="str">
         <f>VLOOKUP(A717,Hoja1!A:C,2,FALSE)</f>
-        <v>SENS NATURAL NEROLI LIMA EDT 100ML x3 un</v>
+        <v>SAPHIRUS TOUCH REP. AGUA MARINA 9G x12 un</v>
       </c>
       <c r="D717">
         <f>VLOOKUP(A717,Hoja1!A:C,3,FALSE)</f>
-        <v>19769.740000000002</v>
+        <v>3001.91</v>
       </c>
       <c r="E717">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F717" t="s">
         <v>6</v>
@@ -22246,21 +22216,21 @@
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A718">
-        <v>36014</v>
+        <v>103402</v>
       </c>
       <c r="B718" t="s">
-        <v>1293</v>
+        <v>1273</v>
       </c>
       <c r="C718" t="str">
         <f>VLOOKUP(A718,Hoja1!A:C,2,FALSE)</f>
-        <v>SENS NATURAL VAINILLA CLASSIS EDT 100ML x3 un</v>
+        <v>SAPHIRUS TOUCH REP. FRUTOS ROJOS 9G x12 un</v>
       </c>
       <c r="D718">
         <f>VLOOKUP(A718,Hoja1!A:C,3,FALSE)</f>
-        <v>19769.740000000002</v>
+        <v>3001.91</v>
       </c>
       <c r="E718">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F718" t="s">
         <v>6</v>
@@ -22268,21 +22238,21 @@
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A719">
-        <v>36047</v>
+        <v>103404</v>
       </c>
       <c r="B719" t="s">
-        <v>1295</v>
+        <v>1275</v>
       </c>
       <c r="C719" t="str">
         <f>VLOOKUP(A719,Hoja1!A:C,2,FALSE)</f>
-        <v>SENS NATURAL VERBENA NARANJA EDT 100ML x3 un</v>
+        <v>SAPHIRUS TOUCH REP. PETALOS FLORAL 9G x12 un</v>
       </c>
       <c r="D719">
         <f>VLOOKUP(A719,Hoja1!A:C,3,FALSE)</f>
-        <v>19769.740000000002</v>
+        <v>3001.91</v>
       </c>
       <c r="E719">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F719" t="s">
         <v>6</v>
@@ -22290,21 +22260,21 @@
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A720">
-        <v>36082</v>
+        <v>103403</v>
       </c>
       <c r="B720" t="s">
-        <v>1297</v>
+        <v>1277</v>
       </c>
       <c r="C720" t="str">
         <f>VLOOKUP(A720,Hoja1!A:C,2,FALSE)</f>
-        <v>SENS NECESER VERBENA NARANJA EAU X 100M x3 un</v>
+        <v>SAPHIRUS TOUCH REP. MIX CITRICO 9G x12 un</v>
       </c>
       <c r="D720">
         <f>VLOOKUP(A720,Hoja1!A:C,3,FALSE)</f>
-        <v>27589.75</v>
+        <v>3001.91</v>
       </c>
       <c r="E720">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F720" t="s">
         <v>6</v>
@@ -22312,21 +22282,21 @@
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A721">
-        <v>841131</v>
+        <v>103501</v>
       </c>
       <c r="B721" t="s">
-        <v>1299</v>
+        <v>1279</v>
       </c>
       <c r="C721" t="str">
         <f>VLOOKUP(A721,Hoja1!A:C,2,FALSE)</f>
-        <v>SMELL FRESH DESINFECT. LAVANDA 360 ML x12 un</v>
+        <v>SAPHIRUS TOUCH REP.+ DISP. CITRICO ARENA x12 un</v>
       </c>
       <c r="D721">
         <f>VLOOKUP(A721,Hoja1!A:C,3,FALSE)</f>
-        <v>4866.83</v>
+        <v>4831.5200000000004</v>
       </c>
       <c r="E721">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F721" t="s">
         <v>6</v>
@@ -22334,21 +22304,21 @@
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A722">
-        <v>841130</v>
+        <v>103502</v>
       </c>
       <c r="B722" t="s">
-        <v>1301</v>
+        <v>1281</v>
       </c>
       <c r="C722" t="str">
         <f>VLOOKUP(A722,Hoja1!A:C,2,FALSE)</f>
-        <v>SMELL FRESH DESINFECT. ORIGINAL 360 ML x12 un</v>
+        <v>SAPHIRUS TOUCH REP.+ DISP. F.ROJOS x12 un</v>
       </c>
       <c r="D722">
         <f>VLOOKUP(A722,Hoja1!A:C,3,FALSE)</f>
-        <v>4866.83</v>
+        <v>4831.5200000000004</v>
       </c>
       <c r="E722">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F722" t="s">
         <v>6</v>
@@ -22356,21 +22326,21 @@
     </row>
     <row r="723" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A723">
-        <v>84235</v>
+        <v>103504</v>
       </c>
       <c r="B723" t="s">
-        <v>1303</v>
+        <v>1283</v>
       </c>
       <c r="C723" t="str">
         <f>VLOOKUP(A723,Hoja1!A:C,2,FALSE)</f>
-        <v>SMELL FRESH DIFUSOR AURA x12 un</v>
+        <v>SAPHIRUS TOUCH REP.+ DISP. PETALOS ROSA x12 un</v>
       </c>
       <c r="D723">
         <f>VLOOKUP(A723,Hoja1!A:C,3,FALSE)</f>
-        <v>4082.58</v>
+        <v>4831.5200000000004</v>
       </c>
       <c r="E723">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F723" t="s">
         <v>6</v>
@@ -22378,21 +22348,21 @@
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A724">
-        <v>84236</v>
+        <v>103503</v>
       </c>
       <c r="B724" t="s">
-        <v>1305</v>
+        <v>1285</v>
       </c>
       <c r="C724" t="str">
         <f>VLOOKUP(A724,Hoja1!A:C,2,FALSE)</f>
-        <v>SMELL FRESH DIFUSOR CHER x12 un</v>
+        <v>SAPHIRUS TOUCH REP.+DISP. MARINA CELESTE x12 un</v>
       </c>
       <c r="D724">
         <f>VLOOKUP(A724,Hoja1!A:C,3,FALSE)</f>
-        <v>4082.58</v>
+        <v>4831.5200000000004</v>
       </c>
       <c r="E724">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F724" t="s">
         <v>6</v>
@@ -22400,21 +22370,21 @@
     </row>
     <row r="725" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A725">
-        <v>84237</v>
+        <v>36003</v>
       </c>
       <c r="B725" t="s">
-        <v>1307</v>
+        <v>1287</v>
       </c>
       <c r="C725" t="str">
         <f>VLOOKUP(A725,Hoja1!A:C,2,FALSE)</f>
-        <v>SMELL FRESH DIFUSOR ESSENCE x12 un</v>
+        <v>SENS NATURAL GROSELLAS ROSAS EDT 100 ML x3 un</v>
       </c>
       <c r="D725">
         <f>VLOOKUP(A725,Hoja1!A:C,3,FALSE)</f>
-        <v>4082.58</v>
+        <v>19769.740000000002</v>
       </c>
       <c r="E725">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F725" t="s">
         <v>6</v>
@@ -22422,21 +22392,21 @@
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A726">
-        <v>84238</v>
+        <v>36025</v>
       </c>
       <c r="B726" t="s">
-        <v>1309</v>
+        <v>1289</v>
       </c>
       <c r="C726" t="str">
         <f>VLOOKUP(A726,Hoja1!A:C,2,FALSE)</f>
-        <v>SMELL FRESH DIFUSOR NEW YORK x12 un</v>
+        <v>SENS NATURAL MAGNOLIA PERA EDT 100ML x3 un</v>
       </c>
       <c r="D726">
         <f>VLOOKUP(A726,Hoja1!A:C,3,FALSE)</f>
-        <v>4082.58</v>
+        <v>19769.740000000002</v>
       </c>
       <c r="E726">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F726" t="s">
         <v>6</v>
@@ -22444,21 +22414,21 @@
     </row>
     <row r="727" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A727">
-        <v>84239</v>
+        <v>36036</v>
       </c>
       <c r="B727" t="s">
-        <v>1311</v>
+        <v>1291</v>
       </c>
       <c r="C727" t="str">
         <f>VLOOKUP(A727,Hoja1!A:C,2,FALSE)</f>
-        <v>SMELL FRESH DIFUSOR YASMIN x12 un</v>
+        <v>SENS NATURAL NEROLI LIMA EDT 100ML x3 un</v>
       </c>
       <c r="D727">
         <f>VLOOKUP(A727,Hoja1!A:C,3,FALSE)</f>
-        <v>4082.58</v>
+        <v>19769.740000000002</v>
       </c>
       <c r="E727">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F727" t="s">
         <v>6</v>
@@ -22466,21 +22436,21 @@
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A728">
-        <v>841075</v>
+        <v>36014</v>
       </c>
       <c r="B728" t="s">
-        <v>1313</v>
+        <v>1293</v>
       </c>
       <c r="C728" t="str">
         <f>VLOOKUP(A728,Hoja1!A:C,2,FALSE)</f>
-        <v>SMELL FRESH LIMPIAHORNOS 360 ML x12 un</v>
+        <v>SENS NATURAL VAINILLA CLASSIS EDT 100ML x3 un</v>
       </c>
       <c r="D728">
         <f>VLOOKUP(A728,Hoja1!A:C,3,FALSE)</f>
-        <v>3413.27</v>
+        <v>19769.740000000002</v>
       </c>
       <c r="E728">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F728" t="s">
         <v>6</v>
@@ -22488,21 +22458,21 @@
     </row>
     <row r="729" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A729">
-        <v>84241</v>
+        <v>36047</v>
       </c>
       <c r="B729" t="s">
-        <v>1315</v>
+        <v>1295</v>
       </c>
       <c r="C729" t="str">
         <f>VLOOKUP(A729,Hoja1!A:C,2,FALSE)</f>
-        <v>SMELL FRESH NEUTRALIZADOR DE OLORES LAV x12 un</v>
+        <v>SENS NATURAL VERBENA NARANJA EDT 100ML x3 un</v>
       </c>
       <c r="D729">
         <f>VLOOKUP(A729,Hoja1!A:C,3,FALSE)</f>
-        <v>5203</v>
+        <v>19769.740000000002</v>
       </c>
       <c r="E729">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F729" t="s">
         <v>6</v>
@@ -22510,21 +22480,21 @@
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A730">
-        <v>84240</v>
+        <v>36082</v>
       </c>
       <c r="B730" t="s">
-        <v>1317</v>
+        <v>1297</v>
       </c>
       <c r="C730" t="str">
         <f>VLOOKUP(A730,Hoja1!A:C,2,FALSE)</f>
-        <v>SMELL FRESH NEUTRALIZADOR DE OLORES MAR. x12 un</v>
+        <v>SENS NECESER VERBENA NARANJA EAU X 100M x3 un</v>
       </c>
       <c r="D730">
         <f>VLOOKUP(A730,Hoja1!A:C,3,FALSE)</f>
-        <v>5203</v>
+        <v>27589.75</v>
       </c>
       <c r="E730">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F730" t="s">
         <v>6</v>
@@ -22532,21 +22502,21 @@
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A731">
-        <v>201440</v>
+        <v>841131</v>
       </c>
       <c r="B731" t="s">
-        <v>1319</v>
+        <v>1299</v>
       </c>
       <c r="C731" t="str">
         <f>VLOOKUP(A731,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET TOALLA MEDIUM X10U CELES x12 un</v>
+        <v>SMELL FRESH DESINFECT. LAVANDA 360 ML x12 un</v>
       </c>
       <c r="D731">
         <f>VLOOKUP(A731,Hoja1!A:C,3,FALSE)</f>
-        <v>10198.93</v>
+        <v>4866.83</v>
       </c>
       <c r="E731">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F731" t="s">
         <v>6</v>
@@ -22554,21 +22524,21 @@
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A732">
-        <v>200371</v>
+        <v>841130</v>
       </c>
       <c r="B732" t="s">
-        <v>1321</v>
+        <v>1301</v>
       </c>
       <c r="C732" t="str">
         <f>VLOOKUP(A732,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET TOALLA MAXI NOCTURNAX10 x12 un</v>
+        <v>SMELL FRESH DESINFECT. ORIGINAL 360 ML x12 un</v>
       </c>
       <c r="D732">
         <f>VLOOKUP(A732,Hoja1!A:C,3,FALSE)</f>
-        <v>15073.93</v>
+        <v>4866.83</v>
       </c>
       <c r="E732">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F732" t="s">
         <v>6</v>
@@ -22576,21 +22546,21 @@
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A733">
-        <v>46782</v>
+        <v>84235</v>
       </c>
       <c r="B733" t="s">
-        <v>1322</v>
+        <v>1303</v>
       </c>
       <c r="C733" t="str">
         <f>VLOOKUP(A733,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET TOALLA MEDIUM X30U CELEST x8 un</v>
+        <v>SMELL FRESH DIFUSOR AURA x12 un</v>
       </c>
       <c r="D733">
         <f>VLOOKUP(A733,Hoja1!A:C,3,FALSE)</f>
-        <v>27535.919999999998</v>
+        <v>4082.58</v>
       </c>
       <c r="E733">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F733" t="s">
         <v>6</v>
@@ -22598,21 +22568,21 @@
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A734">
-        <v>106115</v>
+        <v>84236</v>
       </c>
       <c r="B734" t="s">
-        <v>1324</v>
+        <v>1305</v>
       </c>
       <c r="C734" t="str">
         <f>VLOOKUP(A734,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PD NATURAL CARE SIN ALAS  X 15 x15 un</v>
+        <v>SMELL FRESH DIFUSOR CHER x12 un</v>
       </c>
       <c r="D734">
         <f>VLOOKUP(A734,Hoja1!A:C,3,FALSE)</f>
-        <v>2771.3</v>
+        <v>4082.58</v>
       </c>
       <c r="E734">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F734" t="s">
         <v>6</v>
@@ -22620,21 +22590,21 @@
     </row>
     <row r="735" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A735">
-        <v>46786</v>
+        <v>84237</v>
       </c>
       <c r="B735" t="s">
-        <v>1326</v>
+        <v>1307</v>
       </c>
       <c r="C735" t="str">
         <f>VLOOKUP(A735,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET PD LARGOS C/ALAS X50 x6 un</v>
+        <v>SMELL FRESH DIFUSOR ESSENCE x12 un</v>
       </c>
       <c r="D735">
         <f>VLOOKUP(A735,Hoja1!A:C,3,FALSE)</f>
-        <v>12270.1</v>
+        <v>4082.58</v>
       </c>
       <c r="E735">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F735" t="s">
         <v>6</v>
@@ -22642,21 +22612,21 @@
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A736">
-        <v>106103</v>
+        <v>84238</v>
       </c>
       <c r="B736" t="s">
-        <v>1328</v>
+        <v>1309</v>
       </c>
       <c r="C736" t="str">
         <f>VLOOKUP(A736,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET PD LARGOS S/ALAS X 15 x36 un</v>
+        <v>SMELL FRESH DIFUSOR NEW YORK x12 un</v>
       </c>
       <c r="D736">
         <f>VLOOKUP(A736,Hoja1!A:C,3,FALSE)</f>
-        <v>3599.07</v>
+        <v>4082.58</v>
       </c>
       <c r="E736">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F736" t="s">
         <v>6</v>
@@ -22664,21 +22634,21 @@
     </row>
     <row r="737" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A737">
-        <v>106104</v>
+        <v>84239</v>
       </c>
       <c r="B737" t="s">
-        <v>1330</v>
+        <v>1311</v>
       </c>
       <c r="C737" t="str">
         <f>VLOOKUP(A737,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET PD LARGOS S/ALAS X 50 x12 un</v>
+        <v>SMELL FRESH DIFUSOR YASMIN x12 un</v>
       </c>
       <c r="D737">
         <f>VLOOKUP(A737,Hoja1!A:C,3,FALSE)</f>
-        <v>11705.54</v>
+        <v>4082.58</v>
       </c>
       <c r="E737">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F737" t="s">
         <v>6</v>
@@ -22686,21 +22656,21 @@
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A738">
-        <v>106216</v>
+        <v>841075</v>
       </c>
       <c r="B738" t="s">
-        <v>1332</v>
+        <v>1313</v>
       </c>
       <c r="C738" t="str">
         <f>VLOOKUP(A738,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PD NATURAL CARE S/ALAS 80 X 60U x12 un</v>
+        <v>SMELL FRESH LIMPIAHORNOS 360 ML x12 un</v>
       </c>
       <c r="D738">
         <f>VLOOKUP(A738,Hoja1!A:C,3,FALSE)</f>
-        <v>11085.19</v>
+        <v>3413.27</v>
       </c>
       <c r="E738">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F738" t="s">
         <v>6</v>
@@ -22708,21 +22678,21 @@
     </row>
     <row r="739" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A739">
-        <v>106116</v>
+        <v>84241</v>
       </c>
       <c r="B739" t="s">
-        <v>1334</v>
+        <v>1315</v>
       </c>
       <c r="C739" t="str">
         <f>VLOOKUP(A739,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PD NATURAL CARE SIN ALAS X 50 x12 un</v>
+        <v>SMELL FRESH NEUTRALIZADOR DE OLORES LAV x12 un</v>
       </c>
       <c r="D739">
         <f>VLOOKUP(A739,Hoja1!A:C,3,FALSE)</f>
-        <v>9013.2900000000009</v>
+        <v>5203</v>
       </c>
       <c r="E739">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F739" t="s">
         <v>6</v>
@@ -22730,21 +22700,21 @@
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A740">
-        <v>200372</v>
+        <v>84240</v>
       </c>
       <c r="B740" t="s">
-        <v>1336</v>
+        <v>1317</v>
       </c>
       <c r="C740" t="str">
         <f>VLOOKUP(A740,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET TOALLA MAXI NOCTURNA X30 x8 un</v>
+        <v>SMELL FRESH NEUTRALIZADOR DE OLORES MAR. x12 un</v>
       </c>
       <c r="D740">
         <f>VLOOKUP(A740,Hoja1!A:C,3,FALSE)</f>
-        <v>40697.19</v>
+        <v>5203</v>
       </c>
       <c r="E740">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F740" t="s">
         <v>6</v>
@@ -22752,18 +22722,18 @@
     </row>
     <row r="741" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A741">
-        <v>201418</v>
+        <v>201440</v>
       </c>
       <c r="B741" t="s">
-        <v>1338</v>
+        <v>1319</v>
       </c>
       <c r="C741" t="str">
         <f>VLOOKUP(A741,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET TOALLA MAXI X10U AMARILLO x12 un</v>
+        <v>TENA DISCREET TOALLA MEDIUM X10U CELES x12 un</v>
       </c>
       <c r="D741">
         <f>VLOOKUP(A741,Hoja1!A:C,3,FALSE)</f>
-        <v>13107.75</v>
+        <v>10198.93</v>
       </c>
       <c r="E741">
         <v>62</v>
@@ -22774,18 +22744,18 @@
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A742">
-        <v>200057</v>
+        <v>200371</v>
       </c>
       <c r="B742" t="s">
-        <v>1340</v>
+        <v>1321</v>
       </c>
       <c r="C742" t="str">
         <f>VLOOKUP(A742,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET TOALLA MINI X10U LILA x12 un</v>
+        <v>TENA DISCREET TOALLA MAXI NOCTURNAX10 x12 un</v>
       </c>
       <c r="D742">
         <f>VLOOKUP(A742,Hoja1!A:C,3,FALSE)</f>
-        <v>8316.2000000000007</v>
+        <v>15073.93</v>
       </c>
       <c r="E742">
         <v>62</v>
@@ -22796,18 +22766,18 @@
     </row>
     <row r="743" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A743">
-        <v>110271</v>
+        <v>46782</v>
       </c>
       <c r="B743" t="s">
-        <v>1342</v>
+        <v>1322</v>
       </c>
       <c r="C743" t="str">
         <f>VLOOKUP(A743,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA TOALLA NATURAL CARE C/ALAS x16 un</v>
+        <v>TENA DISCREET TOALLA MEDIUM X30U CELEST x8 un</v>
       </c>
       <c r="D743">
         <f>VLOOKUP(A743,Hoja1!A:C,3,FALSE)</f>
-        <v>6952.36</v>
+        <v>27535.919999999998</v>
       </c>
       <c r="E743">
         <v>62</v>
@@ -22818,18 +22788,18 @@
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A744">
-        <v>130134</v>
+        <v>106115</v>
       </c>
       <c r="B744" t="s">
-        <v>1344</v>
+        <v>1324</v>
       </c>
       <c r="C744" t="str">
         <f>VLOOKUP(A744,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET PD EXTRALARGOS S/ALAS X15 x12 un</v>
+        <v>TENA PD NATURAL CARE SIN ALAS  X 15 x15 un</v>
       </c>
       <c r="D744">
         <f>VLOOKUP(A744,Hoja1!A:C,3,FALSE)</f>
-        <v>4149.88</v>
+        <v>2771.3</v>
       </c>
       <c r="E744">
         <v>62</v>
@@ -22840,18 +22810,18 @@
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A745">
-        <v>130135</v>
+        <v>46786</v>
       </c>
       <c r="B745" t="s">
-        <v>1346</v>
+        <v>1326</v>
       </c>
       <c r="C745" t="str">
         <f>VLOOKUP(A745,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET PD EXTRALARGOS S/ALAS X50 x6 un</v>
+        <v>TENA DISCREET PD LARGOS C/ALAS X50 x6 un</v>
       </c>
       <c r="D745">
         <f>VLOOKUP(A745,Hoja1!A:C,3,FALSE)</f>
-        <v>13497.11</v>
+        <v>12270.1</v>
       </c>
       <c r="E745">
         <v>62</v>
@@ -22862,18 +22832,18 @@
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A746">
-        <v>110270</v>
+        <v>106103</v>
       </c>
       <c r="B746" t="s">
-        <v>1348</v>
+        <v>1328</v>
       </c>
       <c r="C746" t="str">
         <f>VLOOKUP(A746,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA TOALLA NATURAL CARE C/ALAS X8U x18 un</v>
+        <v>TENA DISCREET PD LARGOS S/ALAS X 15 x36 un</v>
       </c>
       <c r="D746">
         <f>VLOOKUP(A746,Hoja1!A:C,3,FALSE)</f>
-        <v>3659.14</v>
+        <v>3599.07</v>
       </c>
       <c r="E746">
         <v>62</v>
@@ -22884,18 +22854,18 @@
     </row>
     <row r="747" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A747">
-        <v>46101</v>
+        <v>106104</v>
       </c>
       <c r="B747" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C747" t="e">
+        <v>1330</v>
+      </c>
+      <c r="C747" t="str">
         <f>VLOOKUP(A747,Hoja1!A:C,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D747" t="e">
+        <v>TENA DISCREET PD LARGOS S/ALAS X 50 x12 un</v>
+      </c>
+      <c r="D747">
         <f>VLOOKUP(A747,Hoja1!A:C,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>11705.54</v>
       </c>
       <c r="E747">
         <v>62</v>
@@ -22906,18 +22876,18 @@
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A748">
-        <v>200652</v>
+        <v>106216</v>
       </c>
       <c r="B748" t="s">
-        <v>1351</v>
+        <v>1332</v>
       </c>
       <c r="C748" t="str">
         <f>VLOOKUP(A748,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PANTS NOCTURNO LARGE X8 x6 un</v>
+        <v>TENA PD NATURAL CARE S/ALAS 80 X 60U x12 un</v>
       </c>
       <c r="D748">
         <f>VLOOKUP(A748,Hoja1!A:C,3,FALSE)</f>
-        <v>30136.959999999999</v>
+        <v>11085.19</v>
       </c>
       <c r="E748">
         <v>62</v>
@@ -22928,18 +22898,18 @@
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A749">
-        <v>200849</v>
+        <v>106116</v>
       </c>
       <c r="B749" t="s">
-        <v>1353</v>
+        <v>1334</v>
       </c>
       <c r="C749" t="str">
         <f>VLOOKUP(A749,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PANTS CLASICO LARGE X 8 U x8 un</v>
+        <v>TENA PD NATURAL CARE SIN ALAS X 50 x12 un</v>
       </c>
       <c r="D749">
         <f>VLOOKUP(A749,Hoja1!A:C,3,FALSE)</f>
-        <v>19154.830000000002</v>
+        <v>9013.2900000000009</v>
       </c>
       <c r="E749">
         <v>62</v>
@@ -22950,18 +22920,18 @@
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A750">
-        <v>200847</v>
+        <v>200372</v>
       </c>
       <c r="B750" t="s">
-        <v>1355</v>
+        <v>1336</v>
       </c>
       <c r="C750" t="str">
         <f>VLOOKUP(A750,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PANTS CLASICO MEDIUM X 8 U x8 un</v>
+        <v>TENA DISCREET TOALLA MAXI NOCTURNA X30 x8 un</v>
       </c>
       <c r="D750">
         <f>VLOOKUP(A750,Hoja1!A:C,3,FALSE)</f>
-        <v>19154.830000000002</v>
+        <v>40697.19</v>
       </c>
       <c r="E750">
         <v>62</v>
@@ -22972,18 +22942,18 @@
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A751">
-        <v>200848</v>
+        <v>201418</v>
       </c>
       <c r="B751" t="s">
-        <v>1357</v>
+        <v>1338</v>
       </c>
       <c r="C751" t="str">
         <f>VLOOKUP(A751,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PANTS CLASICO MEDIUM X 16U x4 un</v>
+        <v>TENA DISCREET TOALLA MAXI X10U AMARILLO x12 un</v>
       </c>
       <c r="D751">
         <f>VLOOKUP(A751,Hoja1!A:C,3,FALSE)</f>
-        <v>36394.25</v>
+        <v>13107.75</v>
       </c>
       <c r="E751">
         <v>62</v>
@@ -22994,18 +22964,18 @@
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A752">
-        <v>200651</v>
+        <v>200057</v>
       </c>
       <c r="B752" t="s">
-        <v>1359</v>
+        <v>1340</v>
       </c>
       <c r="C752" t="str">
         <f>VLOOKUP(A752,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PANTS NOCTURNO MEDIUM X 8 x6 un</v>
+        <v>TENA DISCREET TOALLA MINI X10U LILA x12 un</v>
       </c>
       <c r="D752">
         <f>VLOOKUP(A752,Hoja1!A:C,3,FALSE)</f>
-        <v>30136.959999999999</v>
+        <v>8316.2000000000007</v>
       </c>
       <c r="E752">
         <v>62</v>
@@ -23016,18 +22986,18 @@
     </row>
     <row r="753" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A753">
-        <v>200073</v>
+        <v>110271</v>
       </c>
       <c r="B753" t="s">
-        <v>1361</v>
+        <v>1342</v>
       </c>
       <c r="C753" t="str">
         <f>VLOOKUP(A753,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PANTS ULTRA LARGE X 16U x4 un</v>
+        <v>TENA TOALLA NATURAL CARE C/ALAS x16 un</v>
       </c>
       <c r="D753">
         <f>VLOOKUP(A753,Hoja1!A:C,3,FALSE)</f>
-        <v>46584.67</v>
+        <v>6952.36</v>
       </c>
       <c r="E753">
         <v>62</v>
@@ -23038,18 +23008,18 @@
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A754">
-        <v>200845</v>
+        <v>130134</v>
       </c>
       <c r="B754" t="s">
-        <v>1363</v>
+        <v>1344</v>
       </c>
       <c r="C754" t="str">
         <f>VLOOKUP(A754,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PANTS ULTRA LARGE X 8 U x8 un</v>
+        <v>TENA DISCREET PD EXTRALARGOS S/ALAS X15 x12 un</v>
       </c>
       <c r="D754">
         <f>VLOOKUP(A754,Hoja1!A:C,3,FALSE)</f>
-        <v>25539.77</v>
+        <v>4149.88</v>
       </c>
       <c r="E754">
         <v>62</v>
@@ -23060,18 +23030,18 @@
     </row>
     <row r="755" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A755">
-        <v>200072</v>
+        <v>130135</v>
       </c>
       <c r="B755" t="s">
-        <v>1365</v>
+        <v>1346</v>
       </c>
       <c r="C755" t="str">
         <f>VLOOKUP(A755,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PANTS ULTRA MEDIUM X 16U x4 un</v>
+        <v>TENA DISCREET PD EXTRALARGOS S/ALAS X50 x6 un</v>
       </c>
       <c r="D755">
         <f>VLOOKUP(A755,Hoja1!A:C,3,FALSE)</f>
-        <v>46584.67</v>
+        <v>13497.11</v>
       </c>
       <c r="E755">
         <v>62</v>
@@ -23082,18 +23052,18 @@
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A756">
-        <v>200846</v>
+        <v>110270</v>
       </c>
       <c r="B756" t="s">
-        <v>1367</v>
+        <v>1348</v>
       </c>
       <c r="C756" t="str">
         <f>VLOOKUP(A756,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PANTS ULTRA MEDIUM X 8 U x8 un</v>
+        <v>TENA TOALLA NATURAL CARE C/ALAS X8U x18 un</v>
       </c>
       <c r="D756">
         <f>VLOOKUP(A756,Hoja1!A:C,3,FALSE)</f>
-        <v>25539.77</v>
+        <v>3659.14</v>
       </c>
       <c r="E756">
         <v>62</v>
@@ -23104,18 +23074,18 @@
     </row>
     <row r="757" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A757">
-        <v>200850</v>
+        <v>46101</v>
       </c>
       <c r="B757" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C757" t="str">
+        <v>1350</v>
+      </c>
+      <c r="C757" t="e">
         <f>VLOOKUP(A757,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA PANTS CLASICO LARGE X 16U x4 un</v>
-      </c>
-      <c r="D757">
+        <v>#N/A</v>
+      </c>
+      <c r="D757" t="e">
         <f>VLOOKUP(A757,Hoja1!A:C,3,FALSE)</f>
-        <v>36394.25</v>
+        <v>#N/A</v>
       </c>
       <c r="E757">
         <v>62</v>
@@ -23126,21 +23096,21 @@
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A758">
-        <v>7825</v>
+        <v>200652</v>
       </c>
       <c r="B758" t="s">
-        <v>1373</v>
+        <v>1351</v>
       </c>
       <c r="C758" t="str">
         <f>VLOOKUP(A758,Hoja1!A:C,2,FALSE)</f>
-        <v>VALERIA BY- VALERIA MAZA DEO X 123 ML x6 un</v>
+        <v>TENA PANTS NOCTURNO LARGE X8 x6 un</v>
       </c>
       <c r="D758">
         <f>VLOOKUP(A758,Hoja1!A:C,3,FALSE)</f>
-        <v>4756.74</v>
+        <v>30136.959999999999</v>
       </c>
       <c r="E758">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F758" t="s">
         <v>6</v>
@@ -23148,21 +23118,21 @@
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A759">
-        <v>7814</v>
+        <v>200849</v>
       </c>
       <c r="B759" t="s">
-        <v>1375</v>
+        <v>1353</v>
       </c>
       <c r="C759" t="str">
         <f>VLOOKUP(A759,Hoja1!A:C,2,FALSE)</f>
-        <v>VALERIA BY- VALERIA MAZA EAU X 100 ML x3 un</v>
+        <v>TENA PANTS CLASICO LARGE X 8 U x8 un</v>
       </c>
       <c r="D759">
         <f>VLOOKUP(A759,Hoja1!A:C,3,FALSE)</f>
-        <v>33094.120000000003</v>
+        <v>19154.830000000002</v>
       </c>
       <c r="E759">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F759" t="s">
         <v>6</v>
@@ -23170,21 +23140,21 @@
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A760">
-        <v>7803</v>
+        <v>200847</v>
       </c>
       <c r="B760" t="s">
-        <v>1377</v>
+        <v>1355</v>
       </c>
       <c r="C760" t="str">
         <f>VLOOKUP(A760,Hoja1!A:C,2,FALSE)</f>
-        <v>VALERIA BY- VALERIA MAZA EAU X 60 ML x3 un</v>
+        <v>TENA PANTS CLASICO MEDIUM X 8 U x8 un</v>
       </c>
       <c r="D760">
         <f>VLOOKUP(A760,Hoja1!A:C,3,FALSE)</f>
-        <v>27563.8</v>
+        <v>19154.830000000002</v>
       </c>
       <c r="E760">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F760" t="s">
         <v>6</v>
@@ -23192,21 +23162,21 @@
     </row>
     <row r="761" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A761">
-        <v>60040</v>
+        <v>200848</v>
       </c>
       <c r="B761" t="s">
-        <v>1379</v>
+        <v>1357</v>
       </c>
       <c r="C761" t="str">
         <f>VLOOKUP(A761,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA CABO METALICO ROJO 1 U x12 un</v>
+        <v>TENA PANTS CLASICO MEDIUM X 16U x4 un</v>
       </c>
       <c r="D761">
         <f>VLOOKUP(A761,Hoja1!A:C,3,FALSE)</f>
-        <v>4104.01</v>
+        <v>36394.25</v>
       </c>
       <c r="E761">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F761" t="s">
         <v>6</v>
@@ -23214,21 +23184,21 @@
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A762">
-        <v>60064</v>
+        <v>200651</v>
       </c>
       <c r="B762" t="s">
-        <v>1381</v>
+        <v>1359</v>
       </c>
       <c r="C762" t="str">
         <f>VLOOKUP(A762,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA EASY WRING MOP+CUBO C/ PEDAL x1 un</v>
+        <v>TENA PANTS NOCTURNO MEDIUM X 8 x6 un</v>
       </c>
       <c r="D762">
         <f>VLOOKUP(A762,Hoja1!A:C,3,FALSE)</f>
-        <v>102352</v>
+        <v>30136.959999999999</v>
       </c>
       <c r="E762">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F762" t="s">
         <v>6</v>
@@ -23236,21 +23206,21 @@
     </row>
     <row r="763" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A763">
-        <v>60066</v>
+        <v>200073</v>
       </c>
       <c r="B763" t="s">
-        <v>1383</v>
+        <v>1361</v>
       </c>
       <c r="C763" t="str">
         <f>VLOOKUP(A763,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA EASY WRING REPUESTO 1 U x1 un</v>
+        <v>TENA PANTS ULTRA LARGE X 16U x4 un</v>
       </c>
       <c r="D763">
         <f>VLOOKUP(A763,Hoja1!A:C,3,FALSE)</f>
-        <v>13385</v>
+        <v>46584.67</v>
       </c>
       <c r="E763">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F763" t="s">
         <v>6</v>
@@ -23258,21 +23228,21 @@
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A764">
-        <v>60044</v>
+        <v>200845</v>
       </c>
       <c r="B764" t="s">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="C764" t="str">
         <f>VLOOKUP(A764,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA ESPONJA CUADRITOS ULTRA 1 U (12) x12 un</v>
+        <v>TENA PANTS ULTRA LARGE X 8 U x8 un</v>
       </c>
       <c r="D764">
         <f>VLOOKUP(A764,Hoja1!A:C,3,FALSE)</f>
-        <v>1108</v>
+        <v>25539.77</v>
       </c>
       <c r="E764">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F764" t="s">
         <v>6</v>
@@ -23280,21 +23250,21 @@
     </row>
     <row r="765" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A765">
-        <v>60058</v>
+        <v>200072</v>
       </c>
       <c r="B765" t="s">
-        <v>1387</v>
+        <v>1365</v>
       </c>
       <c r="C765" t="str">
         <f>VLOOKUP(A765,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA ESPONJA DELICATTA SIN RAYAR x12 un</v>
+        <v>TENA PANTS ULTRA MEDIUM X 16U x4 un</v>
       </c>
       <c r="D765">
         <f>VLOOKUP(A765,Hoja1!A:C,3,FALSE)</f>
-        <v>1914.99</v>
+        <v>46584.67</v>
       </c>
       <c r="E765">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F765" t="s">
         <v>6</v>
@@ -23302,21 +23272,21 @@
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A766">
-        <v>60026</v>
+        <v>200846</v>
       </c>
       <c r="B766" t="s">
-        <v>1389</v>
+        <v>1367</v>
       </c>
       <c r="C766" t="str">
         <f>VLOOKUP(A766,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA ESPONJA FIBRA MULTIUSO 1 U x12 un</v>
+        <v>TENA PANTS ULTRA MEDIUM X 8 U x8 un</v>
       </c>
       <c r="D766">
         <f>VLOOKUP(A766,Hoja1!A:C,3,FALSE)</f>
-        <v>842.99</v>
+        <v>25539.77</v>
       </c>
       <c r="E766">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F766" t="s">
         <v>6</v>
@@ -23324,21 +23294,21 @@
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A767">
-        <v>60029</v>
+        <v>200850</v>
       </c>
       <c r="B767" t="s">
-        <v>1391</v>
+        <v>1369</v>
       </c>
       <c r="C767" t="str">
         <f>VLOOKUP(A767,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA ESPONJA FIBRA SALVAUÑAS 1 U x12 un</v>
+        <v>TENA PANTS CLASICO LARGE X 16U x4 un</v>
       </c>
       <c r="D767">
         <f>VLOOKUP(A767,Hoja1!A:C,3,FALSE)</f>
-        <v>1066</v>
+        <v>36394.25</v>
       </c>
       <c r="E767">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F767" t="s">
         <v>6</v>
@@ -23346,21 +23316,21 @@
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A768">
-        <v>60022</v>
+        <v>7825</v>
       </c>
       <c r="B768" t="s">
-        <v>1393</v>
+        <v>1373</v>
       </c>
       <c r="C768" t="str">
         <f>VLOOKUP(A768,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA ESPONJA FLOW PACK ACERO 3UN x12 un</v>
+        <v>VALERIA BY- VALERIA MAZA DEO X 123 ML x6 un</v>
       </c>
       <c r="D768">
         <f>VLOOKUP(A768,Hoja1!A:C,3,FALSE)</f>
-        <v>2908.01</v>
+        <v>4756.74</v>
       </c>
       <c r="E768">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F768" t="s">
         <v>6</v>
@@ -23368,21 +23338,21 @@
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A769">
-        <v>60071</v>
+        <v>7814</v>
       </c>
       <c r="B769" t="s">
-        <v>1395</v>
+        <v>1375</v>
       </c>
       <c r="C769" t="str">
         <f>VLOOKUP(A769,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA GUANTE EXTRA SENSACION CHICO x12 un</v>
+        <v>VALERIA BY- VALERIA MAZA EAU X 100 ML x3 un</v>
       </c>
       <c r="D769">
         <f>VLOOKUP(A769,Hoja1!A:C,3,FALSE)</f>
-        <v>2944.99</v>
+        <v>33094.120000000003</v>
       </c>
       <c r="E769">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F769" t="s">
         <v>6</v>
@@ -23390,21 +23360,21 @@
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A770">
-        <v>60073</v>
+        <v>7803</v>
       </c>
       <c r="B770" t="s">
-        <v>1397</v>
+        <v>1377</v>
       </c>
       <c r="C770" t="str">
         <f>VLOOKUP(A770,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA GUANTE EXTRA SENSACION GRANDE x12 un</v>
+        <v>VALERIA BY- VALERIA MAZA EAU X 60 ML x3 un</v>
       </c>
       <c r="D770">
         <f>VLOOKUP(A770,Hoja1!A:C,3,FALSE)</f>
-        <v>2944.99</v>
+        <v>27563.8</v>
       </c>
       <c r="E770">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F770" t="s">
         <v>6</v>
@@ -23412,40 +23382,37 @@
     </row>
     <row r="771" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A771">
-        <v>60072</v>
-      </c>
-      <c r="B771" t="s">
-        <v>1399</v>
+        <v>7951</v>
       </c>
       <c r="C771" t="str">
         <f>VLOOKUP(A771,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA GUANTE EXTRA SENSACION MEDIANO x12 un</v>
+        <v>VALERIA VELVET ESTUCHE (EDP60 + DEO123) x3 un</v>
       </c>
       <c r="D771">
         <f>VLOOKUP(A771,Hoja1!A:C,3,FALSE)</f>
-        <v>2944.99</v>
+        <v>35941.96</v>
       </c>
       <c r="E771">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F771" t="s">
-        <v>6</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A772">
-        <v>60061</v>
+        <v>60040</v>
       </c>
       <c r="B772" t="s">
-        <v>1401</v>
+        <v>1379</v>
       </c>
       <c r="C772" t="str">
         <f>VLOOKUP(A772,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA GUANTES FUERTES CHICO 1 U x12 un</v>
+        <v>VILEDA CABO METALICO ROJO 1 U x12 un</v>
       </c>
       <c r="D772">
         <f>VLOOKUP(A772,Hoja1!A:C,3,FALSE)</f>
-        <v>5616</v>
+        <v>4104.01</v>
       </c>
       <c r="E772">
         <v>68</v>
@@ -23456,18 +23423,18 @@
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A773">
-        <v>60063</v>
+        <v>60064</v>
       </c>
       <c r="B773" t="s">
-        <v>1403</v>
+        <v>1381</v>
       </c>
       <c r="C773" t="str">
         <f>VLOOKUP(A773,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA GUANTES FUERTES GRANDE 1 U x12 un</v>
+        <v>VILEDA EASY WRING MOP+CUBO C/ PEDAL x1 un</v>
       </c>
       <c r="D773">
         <f>VLOOKUP(A773,Hoja1!A:C,3,FALSE)</f>
-        <v>5616</v>
+        <v>102352</v>
       </c>
       <c r="E773">
         <v>68</v>
@@ -23478,18 +23445,18 @@
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A774">
-        <v>60035</v>
+        <v>60066</v>
       </c>
       <c r="B774" t="s">
-        <v>1405</v>
+        <v>1383</v>
       </c>
       <c r="C774" t="str">
         <f>VLOOKUP(A774,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA GUANTES UNIVERSAL CHICO x12 un</v>
+        <v>VILEDA EASY WRING REPUESTO 1 U x1 un</v>
       </c>
       <c r="D774">
         <f>VLOOKUP(A774,Hoja1!A:C,3,FALSE)</f>
-        <v>2840</v>
+        <v>13385</v>
       </c>
       <c r="E774">
         <v>68</v>
@@ -23500,18 +23467,18 @@
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A775">
-        <v>60030</v>
+        <v>60044</v>
       </c>
       <c r="B775" t="s">
-        <v>1407</v>
+        <v>1385</v>
       </c>
       <c r="C775" t="str">
         <f>VLOOKUP(A775,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA LANA DE ACERO 10 U x20 un</v>
+        <v>VILEDA ESPONJA CUADRITOS ULTRA 1 U (12) x12 un</v>
       </c>
       <c r="D775">
         <f>VLOOKUP(A775,Hoja1!A:C,3,FALSE)</f>
-        <v>2010</v>
+        <v>1108</v>
       </c>
       <c r="E775">
         <v>68</v>
@@ -23522,18 +23489,18 @@
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A776">
-        <v>60155</v>
+        <v>60058</v>
       </c>
       <c r="B776" t="s">
-        <v>1409</v>
+        <v>1387</v>
       </c>
       <c r="C776" t="str">
         <f>VLOOKUP(A776,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA PAÑO ESPONJA  X 3U x24 un</v>
+        <v>VILEDA ESPONJA DELICATTA SIN RAYAR x12 un</v>
       </c>
       <c r="D776">
         <f>VLOOKUP(A776,Hoja1!A:C,3,FALSE)</f>
-        <v>4525</v>
+        <v>1914.99</v>
       </c>
       <c r="E776">
         <v>68</v>
@@ -23544,18 +23511,18 @@
     </row>
     <row r="777" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A777">
-        <v>60024</v>
+        <v>60026</v>
       </c>
       <c r="B777" t="s">
-        <v>1411</v>
+        <v>1389</v>
       </c>
       <c r="C777" t="str">
         <f>VLOOKUP(A777,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA SUPER ACERO 40 G x48 un</v>
+        <v>VILEDA ESPONJA FIBRA MULTIUSO 1 U x12 un</v>
       </c>
       <c r="D777">
         <f>VLOOKUP(A777,Hoja1!A:C,3,FALSE)</f>
-        <v>2740</v>
+        <v>842.99</v>
       </c>
       <c r="E777">
         <v>68</v>
@@ -23566,18 +23533,18 @@
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A778">
-        <v>60027</v>
+        <v>60029</v>
       </c>
       <c r="B778" t="s">
-        <v>1413</v>
+        <v>1391</v>
       </c>
       <c r="C778" t="str">
         <f>VLOOKUP(A778,Hoja1!A:C,2,FALSE)</f>
-        <v>VILEDA SUPER CUBO ESCURREMAS x1 un</v>
+        <v>VILEDA ESPONJA FIBRA SALVAUÑAS 1 U x12 un</v>
       </c>
       <c r="D778">
         <f>VLOOKUP(A778,Hoja1!A:C,3,FALSE)</f>
-        <v>20095</v>
+        <v>1066</v>
       </c>
       <c r="E778">
         <v>68</v>
@@ -23588,21 +23555,21 @@
     </row>
     <row r="779" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A779">
-        <v>38881</v>
+        <v>60022</v>
       </c>
       <c r="B779" t="s">
-        <v>1415</v>
+        <v>1393</v>
       </c>
       <c r="C779" t="str">
         <f>VLOOKUP(A779,Hoja1!A:C,2,FALSE)</f>
-        <v>VN ACEITE SOLAR FPS 10 X  190ML x12 un</v>
+        <v>VILEDA ESPONJA FLOW PACK ACERO 3UN x12 un</v>
       </c>
       <c r="D779">
         <f>VLOOKUP(A779,Hoja1!A:C,3,FALSE)</f>
-        <v>10000</v>
+        <v>2908.01</v>
       </c>
       <c r="E779">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F779" t="s">
         <v>6</v>
@@ -23610,21 +23577,21 @@
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A780">
-        <v>50152</v>
+        <v>60071</v>
       </c>
       <c r="B780" t="s">
-        <v>1417</v>
+        <v>1395</v>
       </c>
       <c r="C780" t="str">
         <f>VLOOKUP(A780,Hoja1!A:C,2,FALSE)</f>
-        <v>VN AGUA MICELAR X 200ML x6 un</v>
+        <v>VILEDA GUANTE EXTRA SENSACION CHICO x12 un</v>
       </c>
       <c r="D780">
         <f>VLOOKUP(A780,Hoja1!A:C,3,FALSE)</f>
-        <v>5530.63</v>
+        <v>2944.99</v>
       </c>
       <c r="E780">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F780" t="s">
         <v>6</v>
@@ -23632,21 +23599,21 @@
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A781">
-        <v>50165</v>
+        <v>60073</v>
       </c>
       <c r="B781" t="s">
-        <v>1419</v>
+        <v>1397</v>
       </c>
       <c r="C781" t="str">
         <f>VLOOKUP(A781,Hoja1!A:C,2,FALSE)</f>
-        <v>VN AQUA GEL FACIAL C/ACIDO HIALURX 50 x6 un</v>
+        <v>VILEDA GUANTE EXTRA SENSACION GRANDE x12 un</v>
       </c>
       <c r="D781">
         <f>VLOOKUP(A781,Hoja1!A:C,3,FALSE)</f>
-        <v>10561.18</v>
+        <v>2944.99</v>
       </c>
       <c r="E781">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F781" t="s">
         <v>6</v>
@@ -23654,21 +23621,21 @@
     </row>
     <row r="782" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A782">
-        <v>43582</v>
+        <v>60072</v>
       </c>
       <c r="B782" t="s">
-        <v>1421</v>
+        <v>1399</v>
       </c>
       <c r="C782" t="str">
         <f>VLOOKUP(A782,Hoja1!A:C,2,FALSE)</f>
-        <v>VN AUTOBRONCEANTE POMO X 150ML x12 un</v>
+        <v>VILEDA GUANTE EXTRA SENSACION MEDIANO x12 un</v>
       </c>
       <c r="D782">
         <f>VLOOKUP(A782,Hoja1!A:C,3,FALSE)</f>
-        <v>10000</v>
+        <v>2944.99</v>
       </c>
       <c r="E782">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F782" t="s">
         <v>6</v>
@@ -23676,21 +23643,21 @@
     </row>
     <row r="783" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A783">
-        <v>33261</v>
+        <v>60061</v>
       </c>
       <c r="B783" t="s">
-        <v>1423</v>
+        <v>1401</v>
       </c>
       <c r="C783" t="str">
         <f>VLOOKUP(A783,Hoja1!A:C,2,FALSE)</f>
-        <v>VN CREM.CORP.PIEL EQUILIB.PALTA 400G x12 un</v>
+        <v>VILEDA GUANTES FUERTES CHICO 1 U x12 un</v>
       </c>
       <c r="D783">
         <f>VLOOKUP(A783,Hoja1!A:C,3,FALSE)</f>
-        <v>6125.94</v>
+        <v>5616</v>
       </c>
       <c r="E783">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F783" t="s">
         <v>6</v>
@@ -23698,21 +23665,21 @@
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A784">
-        <v>33262</v>
+        <v>60063</v>
       </c>
       <c r="B784" t="s">
-        <v>1425</v>
+        <v>1403</v>
       </c>
       <c r="C784" t="str">
         <f>VLOOKUP(A784,Hoja1!A:C,2,FALSE)</f>
-        <v>VN CREM.CORP.PIEL SECA COCO 250G x12 un</v>
+        <v>VILEDA GUANTES FUERTES GRANDE 1 U x12 un</v>
       </c>
       <c r="D784">
         <f>VLOOKUP(A784,Hoja1!A:C,3,FALSE)</f>
-        <v>4620.01</v>
+        <v>5616</v>
       </c>
       <c r="E784">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F784" t="s">
         <v>6</v>
@@ -23720,21 +23687,21 @@
     </row>
     <row r="785" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A785">
-        <v>33263</v>
+        <v>60035</v>
       </c>
       <c r="B785" t="s">
-        <v>1427</v>
+        <v>1405</v>
       </c>
       <c r="C785" t="str">
         <f>VLOOKUP(A785,Hoja1!A:C,2,FALSE)</f>
-        <v>VN CREM.CORP.PIEL SECA COCO 400G x12 un</v>
+        <v>VILEDA GUANTES UNIVERSAL CHICO x12 un</v>
       </c>
       <c r="D785">
         <f>VLOOKUP(A785,Hoja1!A:C,3,FALSE)</f>
-        <v>6125.94</v>
+        <v>2840</v>
       </c>
       <c r="E785">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F785" t="s">
         <v>6</v>
@@ -23742,21 +23709,21 @@
     </row>
     <row r="786" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A786">
-        <v>33275</v>
+        <v>60030</v>
       </c>
       <c r="B786" t="s">
-        <v>1429</v>
+        <v>1407</v>
       </c>
       <c r="C786" t="str">
         <f>VLOOKUP(A786,Hoja1!A:C,2,FALSE)</f>
-        <v>VN CREM.CORP.PIEL EXT.SECA ALMEN 400G x12 un</v>
+        <v>VILEDA LANA DE ACERO 10 U x20 un</v>
       </c>
       <c r="D786">
         <f>VLOOKUP(A786,Hoja1!A:C,3,FALSE)</f>
-        <v>6125.94</v>
+        <v>2010</v>
       </c>
       <c r="E786">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F786" t="s">
         <v>6</v>
@@ -23764,21 +23731,21 @@
     </row>
     <row r="787" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A787">
-        <v>33264</v>
+        <v>60155</v>
       </c>
       <c r="B787" t="s">
-        <v>1431</v>
+        <v>1409</v>
       </c>
       <c r="C787" t="str">
         <f>VLOOKUP(A787,Hoja1!A:C,2,FALSE)</f>
-        <v>VN CREM.CORP.PIEL EXT.SECA ALMEN 250G x12 un</v>
+        <v>VILEDA PAÑO ESPONJA  X 3U x24 un</v>
       </c>
       <c r="D787">
         <f>VLOOKUP(A787,Hoja1!A:C,3,FALSE)</f>
-        <v>4620.01</v>
+        <v>4525</v>
       </c>
       <c r="E787">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F787" t="s">
         <v>6</v>
@@ -23786,21 +23753,21 @@
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A788">
-        <v>50153</v>
+        <v>60024</v>
       </c>
       <c r="B788" t="s">
-        <v>1433</v>
+        <v>1411</v>
       </c>
       <c r="C788" t="str">
         <f>VLOOKUP(A788,Hoja1!A:C,2,FALSE)</f>
-        <v>VN CREMA FACIAL NUTRITIVA X 50G x6 un</v>
+        <v>VILEDA SUPER ACERO 40 G x48 un</v>
       </c>
       <c r="D788">
         <f>VLOOKUP(A788,Hoja1!A:C,3,FALSE)</f>
-        <v>6117.38</v>
+        <v>2740</v>
       </c>
       <c r="E788">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F788" t="s">
         <v>6</v>
@@ -23808,21 +23775,21 @@
     </row>
     <row r="789" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A789">
-        <v>38880</v>
+        <v>60027</v>
       </c>
       <c r="B789" t="s">
-        <v>1435</v>
+        <v>1413</v>
       </c>
       <c r="C789" t="str">
         <f>VLOOKUP(A789,Hoja1!A:C,2,FALSE)</f>
-        <v>VN CREMA SAPOLAN X 200ML x12 un</v>
+        <v>VILEDA SUPER CUBO ESCURREMAS x1 un</v>
       </c>
       <c r="D789">
         <f>VLOOKUP(A789,Hoja1!A:C,3,FALSE)</f>
-        <v>7000</v>
+        <v>20095</v>
       </c>
       <c r="E789">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F789" t="s">
         <v>6</v>
@@ -23830,18 +23797,18 @@
     </row>
     <row r="790" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A790">
-        <v>38877</v>
+        <v>38881</v>
       </c>
       <c r="B790" t="s">
-        <v>1437</v>
+        <v>1415</v>
       </c>
       <c r="C790" t="str">
         <f>VLOOKUP(A790,Hoja1!A:C,2,FALSE)</f>
-        <v>VN GEL POST SOLAR ALOE X 150G x12 un</v>
+        <v>VN ACEITE SOLAR FPS 10 X  190ML x12 un</v>
       </c>
       <c r="D790">
         <f>VLOOKUP(A790,Hoja1!A:C,3,FALSE)</f>
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="E790">
         <v>69</v>
@@ -23852,18 +23819,18 @@
     </row>
     <row r="791" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A791">
-        <v>39504</v>
+        <v>50152</v>
       </c>
       <c r="B791" t="s">
-        <v>1439</v>
+        <v>1417</v>
       </c>
       <c r="C791" t="str">
         <f>VLOOKUP(A791,Hoja1!A:C,2,FALSE)</f>
-        <v>VN JAB.LIQ. FLORAL Y QUINOA C/VAL-AZUL x12 un</v>
+        <v>VN AGUA MICELAR X 200ML x6 un</v>
       </c>
       <c r="D791">
         <f>VLOOKUP(A791,Hoja1!A:C,3,FALSE)</f>
-        <v>3565.42</v>
+        <v>5530.63</v>
       </c>
       <c r="E791">
         <v>69</v>
@@ -23874,18 +23841,18 @@
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A792">
-        <v>39509</v>
+        <v>50165</v>
       </c>
       <c r="B792" t="s">
-        <v>1441</v>
+        <v>1419</v>
       </c>
       <c r="C792" t="str">
         <f>VLOOKUP(A792,Hoja1!A:C,2,FALSE)</f>
-        <v>VN JAB.LIQ. FLORAL Y QUINOA D/P 200-AZUL x12 un</v>
+        <v>VN AQUA GEL FACIAL C/ACIDO HIALURX 50 x6 un</v>
       </c>
       <c r="D792">
         <f>VLOOKUP(A792,Hoja1!A:C,3,FALSE)</f>
-        <v>2117.94</v>
+        <v>10561.18</v>
       </c>
       <c r="E792">
         <v>69</v>
@@ -23896,18 +23863,18 @@
     </row>
     <row r="793" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A793">
-        <v>39502</v>
+        <v>43582</v>
       </c>
       <c r="B793" t="s">
-        <v>1443</v>
+        <v>1421</v>
       </c>
       <c r="C793" t="str">
         <f>VLOOKUP(A793,Hoja1!A:C,2,FALSE)</f>
-        <v>VN JAB.LIQ. JENGIBRE C/VAL-VERDE x12 un</v>
+        <v>VN AUTOBRONCEANTE POMO X 150ML x12 un</v>
       </c>
       <c r="D793">
         <f>VLOOKUP(A793,Hoja1!A:C,3,FALSE)</f>
-        <v>3565.42</v>
+        <v>10000</v>
       </c>
       <c r="E793">
         <v>69</v>
@@ -23918,18 +23885,18 @@
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A794">
-        <v>39507</v>
+        <v>33261</v>
       </c>
       <c r="B794" t="s">
-        <v>1445</v>
+        <v>1423</v>
       </c>
       <c r="C794" t="str">
         <f>VLOOKUP(A794,Hoja1!A:C,2,FALSE)</f>
-        <v>VN JAB.LIQ. JENGIBRE D/P 200-VERDE x12 un</v>
+        <v>VN CREM.CORP.PIEL EQUILIB.PALTA 400G x12 un</v>
       </c>
       <c r="D794">
         <f>VLOOKUP(A794,Hoja1!A:C,3,FALSE)</f>
-        <v>2117.94</v>
+        <v>6125.94</v>
       </c>
       <c r="E794">
         <v>69</v>
@@ -23940,18 +23907,18 @@
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A795">
-        <v>39505</v>
+        <v>33262</v>
       </c>
       <c r="B795" t="s">
-        <v>1447</v>
+        <v>1425</v>
       </c>
       <c r="C795" t="str">
         <f>VLOOKUP(A795,Hoja1!A:C,2,FALSE)</f>
-        <v>VN JAB.LIQ. BERRIES Y ARANDANOS D/P 200- x12 un</v>
+        <v>VN CREM.CORP.PIEL SECA COCO 250G x12 un</v>
       </c>
       <c r="D795">
         <f>VLOOKUP(A795,Hoja1!A:C,3,FALSE)</f>
-        <v>2117.94</v>
+        <v>4620.01</v>
       </c>
       <c r="E795">
         <v>69</v>
@@ -23962,18 +23929,18 @@
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A796">
-        <v>39501</v>
+        <v>33263</v>
       </c>
       <c r="B796" t="s">
-        <v>1449</v>
+        <v>1427</v>
       </c>
       <c r="C796" t="str">
         <f>VLOOKUP(A796,Hoja1!A:C,2,FALSE)</f>
-        <v>VN JAB.LIQ. COCO C/VAL-AMARILLO x12 un</v>
+        <v>VN CREM.CORP.PIEL SECA COCO 400G x12 un</v>
       </c>
       <c r="D796">
         <f>VLOOKUP(A796,Hoja1!A:C,3,FALSE)</f>
-        <v>3565.42</v>
+        <v>6125.94</v>
       </c>
       <c r="E796">
         <v>69</v>
@@ -23984,18 +23951,18 @@
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A797">
-        <v>39506</v>
+        <v>33275</v>
       </c>
       <c r="B797" t="s">
-        <v>1451</v>
+        <v>1429</v>
       </c>
       <c r="C797" t="str">
         <f>VLOOKUP(A797,Hoja1!A:C,2,FALSE)</f>
-        <v>VN JAB.LIQ. COCO D/P 200-AMARILLO x12 un</v>
+        <v>VN CREM.CORP.PIEL EXT.SECA ALMEN 400G x12 un</v>
       </c>
       <c r="D797">
         <f>VLOOKUP(A797,Hoja1!A:C,3,FALSE)</f>
-        <v>2117.94</v>
+        <v>6125.94</v>
       </c>
       <c r="E797">
         <v>69</v>
@@ -24006,18 +23973,18 @@
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A798">
-        <v>39500</v>
+        <v>33264</v>
       </c>
       <c r="B798" t="s">
-        <v>1453</v>
+        <v>1431</v>
       </c>
       <c r="C798" t="str">
         <f>VLOOKUP(A798,Hoja1!A:C,2,FALSE)</f>
-        <v>VN JAB.LIQ. BERRIES Y ARANDANOS C/VAL-RO x12 un</v>
+        <v>VN CREM.CORP.PIEL EXT.SECA ALMEN 250G x12 un</v>
       </c>
       <c r="D798">
         <f>VLOOKUP(A798,Hoja1!A:C,3,FALSE)</f>
-        <v>3565.42</v>
+        <v>4620.01</v>
       </c>
       <c r="E798">
         <v>69</v>
@@ -24028,18 +23995,18 @@
     </row>
     <row r="799" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A799">
-        <v>43581</v>
+        <v>50153</v>
       </c>
       <c r="B799" t="s">
-        <v>1455</v>
+        <v>1433</v>
       </c>
       <c r="C799" t="str">
         <f>VLOOKUP(A799,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. FACIAL SIN TONO FPS 50 x5 un</v>
+        <v>VN CREMA FACIAL NUTRITIVA X 50G x6 un</v>
       </c>
       <c r="D799">
         <f>VLOOKUP(A799,Hoja1!A:C,3,FALSE)</f>
-        <v>13752.63</v>
+        <v>6117.38</v>
       </c>
       <c r="E799">
         <v>69</v>
@@ -24050,18 +24017,18 @@
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A800">
-        <v>38709</v>
+        <v>38880</v>
       </c>
       <c r="B800" t="s">
-        <v>1457</v>
+        <v>1435</v>
       </c>
       <c r="C800" t="str">
         <f>VLOOKUP(A800,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR AEROMULTI-POS FPS30 X250 x12 un</v>
+        <v>VN CREMA SAPOLAN X 200ML x12 un</v>
       </c>
       <c r="D800">
         <f>VLOOKUP(A800,Hoja1!A:C,3,FALSE)</f>
-        <v>18000</v>
+        <v>7000</v>
       </c>
       <c r="E800">
         <v>69</v>
@@ -24072,18 +24039,18 @@
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A801">
-        <v>38710</v>
+        <v>38877</v>
       </c>
       <c r="B801" t="s">
-        <v>1459</v>
+        <v>1437</v>
       </c>
       <c r="C801" t="str">
         <f>VLOOKUP(A801,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR AEROMULTI-POS FPS50 X 250 x12 un</v>
+        <v>VN GEL POST SOLAR ALOE X 150G x12 un</v>
       </c>
       <c r="D801">
         <f>VLOOKUP(A801,Hoja1!A:C,3,FALSE)</f>
-        <v>20000.009999999998</v>
+        <v>9000</v>
       </c>
       <c r="E801">
         <v>69</v>
@@ -24094,18 +24061,18 @@
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A802">
-        <v>38875</v>
+        <v>39504</v>
       </c>
       <c r="B802" t="s">
-        <v>1461</v>
+        <v>1439</v>
       </c>
       <c r="C802" t="str">
         <f>VLOOKUP(A802,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR EMULSION HIDRAT. FPS30 X1 x12 un</v>
+        <v>VN JAB.LIQ. FLORAL Y QUINOA C/VAL-AZUL x12 un</v>
       </c>
       <c r="D802">
         <f>VLOOKUP(A802,Hoja1!A:C,3,FALSE)</f>
-        <v>10000</v>
+        <v>3565.42</v>
       </c>
       <c r="E802">
         <v>69</v>
@@ -24116,18 +24083,18 @@
     </row>
     <row r="803" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A803">
-        <v>38876</v>
+        <v>39509</v>
       </c>
       <c r="B803" t="s">
-        <v>1463</v>
+        <v>1441</v>
       </c>
       <c r="C803" t="str">
         <f>VLOOKUP(A803,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR EMULSION HIDRAT. FPS50 X1 x12 un</v>
+        <v>VN JAB.LIQ. FLORAL Y QUINOA D/P 200-AZUL x12 un</v>
       </c>
       <c r="D803">
         <f>VLOOKUP(A803,Hoja1!A:C,3,FALSE)</f>
-        <v>11000</v>
+        <v>2117.94</v>
       </c>
       <c r="E803">
         <v>69</v>
@@ -24138,18 +24105,18 @@
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A804">
-        <v>43580</v>
+        <v>39502</v>
       </c>
       <c r="B804" t="s">
-        <v>1465</v>
+        <v>1443</v>
       </c>
       <c r="C804" t="str">
         <f>VLOOKUP(A804,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR FACIAL TONO CLARO FPS 50 x5 un</v>
+        <v>VN JAB.LIQ. JENGIBRE C/VAL-VERDE x12 un</v>
       </c>
       <c r="D804">
         <f>VLOOKUP(A804,Hoja1!A:C,3,FALSE)</f>
-        <v>13752.63</v>
+        <v>3565.42</v>
       </c>
       <c r="E804">
         <v>69</v>
@@ -24160,18 +24127,18 @@
     </row>
     <row r="805" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A805">
-        <v>43579</v>
+        <v>39507</v>
       </c>
       <c r="B805" t="s">
-        <v>1467</v>
+        <v>1445</v>
       </c>
       <c r="C805" t="str">
         <f>VLOOKUP(A805,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR FACIAL TONO MEDIO FPS50 x5 un</v>
+        <v>VN JAB.LIQ. JENGIBRE D/P 200-VERDE x12 un</v>
       </c>
       <c r="D805">
         <f>VLOOKUP(A805,Hoja1!A:C,3,FALSE)</f>
-        <v>13752.63</v>
+        <v>2117.94</v>
       </c>
       <c r="E805">
         <v>69</v>
@@ -24182,18 +24149,18 @@
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A806">
-        <v>38866</v>
+        <v>39505</v>
       </c>
       <c r="B806" t="s">
-        <v>1469</v>
+        <v>1447</v>
       </c>
       <c r="C806" t="str">
         <f>VLOOKUP(A806,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR FPS 30 POMO X 120M x12 un</v>
+        <v>VN JAB.LIQ. BERRIES Y ARANDANOS D/P 200- x12 un</v>
       </c>
       <c r="D806">
         <f>VLOOKUP(A806,Hoja1!A:C,3,FALSE)</f>
-        <v>7000</v>
+        <v>2117.94</v>
       </c>
       <c r="E806">
         <v>69</v>
@@ -24204,18 +24171,18 @@
     </row>
     <row r="807" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A807">
-        <v>38872</v>
+        <v>39501</v>
       </c>
       <c r="B807" t="s">
-        <v>1471</v>
+        <v>1449</v>
       </c>
       <c r="C807" t="str">
         <f>VLOOKUP(A807,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR FPS 30 POMO X 50ML x12 un</v>
+        <v>VN JAB.LIQ. COCO C/VAL-AMARILLO x12 un</v>
       </c>
       <c r="D807">
         <f>VLOOKUP(A807,Hoja1!A:C,3,FALSE)</f>
-        <v>5000</v>
+        <v>3565.42</v>
       </c>
       <c r="E807">
         <v>69</v>
@@ -24226,18 +24193,18 @@
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A808">
-        <v>38867</v>
+        <v>39506</v>
       </c>
       <c r="B808" t="s">
-        <v>1473</v>
+        <v>1451</v>
       </c>
       <c r="C808" t="str">
         <f>VLOOKUP(A808,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR FPS 40 POMO X 120M x12 un</v>
+        <v>VN JAB.LIQ. COCO D/P 200-AMARILLO x12 un</v>
       </c>
       <c r="D808">
         <f>VLOOKUP(A808,Hoja1!A:C,3,FALSE)</f>
-        <v>8000</v>
+        <v>2117.94</v>
       </c>
       <c r="E808">
         <v>69</v>
@@ -24248,18 +24215,18 @@
     </row>
     <row r="809" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A809">
-        <v>38869</v>
+        <v>39500</v>
       </c>
       <c r="B809" t="s">
-        <v>1475</v>
+        <v>1453</v>
       </c>
       <c r="C809" t="str">
         <f>VLOOKUP(A809,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR FPS 50 POMO X 120M x12 un</v>
+        <v>VN JAB.LIQ. BERRIES Y ARANDANOS C/VAL-RO x12 un</v>
       </c>
       <c r="D809">
         <f>VLOOKUP(A809,Hoja1!A:C,3,FALSE)</f>
-        <v>8000</v>
+        <v>3565.42</v>
       </c>
       <c r="E809">
         <v>69</v>
@@ -24270,18 +24237,18 @@
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A810">
-        <v>38871</v>
+        <v>43581</v>
       </c>
       <c r="B810" t="s">
-        <v>1477</v>
+        <v>1455</v>
       </c>
       <c r="C810" t="str">
         <f>VLOOKUP(A810,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR FPS 50 POMO X50 ML x12 un</v>
+        <v>VN PROT. FACIAL SIN TONO FPS 50 x5 un</v>
       </c>
       <c r="D810">
         <f>VLOOKUP(A810,Hoja1!A:C,3,FALSE)</f>
-        <v>6000</v>
+        <v>13752.63</v>
       </c>
       <c r="E810">
         <v>69</v>
@@ -24292,18 +24259,18 @@
     </row>
     <row r="811" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A811">
-        <v>38870</v>
+        <v>38709</v>
       </c>
       <c r="B811" t="s">
-        <v>1479</v>
+        <v>1457</v>
       </c>
       <c r="C811" t="str">
         <f>VLOOKUP(A811,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR FPS60 BABY POMO X120 x12 un</v>
+        <v>VN PROT. SOLAR AEROMULTI-POS FPS30 X250 x12 un</v>
       </c>
       <c r="D811">
         <f>VLOOKUP(A811,Hoja1!A:C,3,FALSE)</f>
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="E811">
         <v>69</v>
@@ -24314,18 +24281,18 @@
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A812">
-        <v>38873</v>
+        <v>38710</v>
       </c>
       <c r="B812" t="s">
-        <v>1481</v>
+        <v>1459</v>
       </c>
       <c r="C812" t="str">
         <f>VLOOKUP(A812,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR POMO FAMILIAR FPS30 X 250 x12 un</v>
+        <v>VN PROT. SOLAR AEROMULTI-POS FPS50 X 250 x12 un</v>
       </c>
       <c r="D812">
         <f>VLOOKUP(A812,Hoja1!A:C,3,FALSE)</f>
-        <v>12000.01</v>
+        <v>20000.009999999998</v>
       </c>
       <c r="E812">
         <v>69</v>
@@ -24336,18 +24303,18 @@
     </row>
     <row r="813" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A813">
-        <v>38874</v>
+        <v>38875</v>
       </c>
       <c r="B813" t="s">
-        <v>1483</v>
+        <v>1461</v>
       </c>
       <c r="C813" t="str">
         <f>VLOOKUP(A813,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR POMO FAMILIAR FPS50 X250 x12 un</v>
+        <v>VN PROT. SOLAR EMULSION HIDRAT. FPS30 X1 x12 un</v>
       </c>
       <c r="D813">
         <f>VLOOKUP(A813,Hoja1!A:C,3,FALSE)</f>
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="E813">
         <v>69</v>
@@ -24358,18 +24325,18 @@
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A814">
-        <v>38490</v>
+        <v>38876</v>
       </c>
       <c r="B814" t="s">
-        <v>1485</v>
+        <v>1463</v>
       </c>
       <c r="C814" t="str">
         <f>VLOOKUP(A814,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR SPRAY EF.SECO FPS30 X 190 x12 un</v>
+        <v>VN PROT. SOLAR EMULSION HIDRAT. FPS50 X1 x12 un</v>
       </c>
       <c r="D814">
         <f>VLOOKUP(A814,Hoja1!A:C,3,FALSE)</f>
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="E814">
         <v>69</v>
@@ -24380,18 +24347,18 @@
     </row>
     <row r="815" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A815">
-        <v>38492</v>
+        <v>43580</v>
       </c>
       <c r="B815" t="s">
-        <v>1487</v>
+        <v>1465</v>
       </c>
       <c r="C815" t="str">
         <f>VLOOKUP(A815,Hoja1!A:C,2,FALSE)</f>
-        <v>VN PROT. SOLAR SPRAY EF.SECO FPS50 X190 x12 un</v>
+        <v>VN PROT. SOLAR FACIAL TONO CLARO FPS 50 x5 un</v>
       </c>
       <c r="D815">
         <f>VLOOKUP(A815,Hoja1!A:C,3,FALSE)</f>
-        <v>14000</v>
+        <v>13752.63</v>
       </c>
       <c r="E815">
         <v>69</v>
@@ -24402,18 +24369,18 @@
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A816">
-        <v>50178</v>
+        <v>43579</v>
       </c>
       <c r="B816" t="s">
-        <v>1489</v>
+        <v>1467</v>
       </c>
       <c r="C816" t="str">
         <f>VLOOKUP(A816,Hoja1!A:C,2,FALSE)</f>
-        <v>VN REPELENTE EXTRA DURACION X 170 VERDE x12 un</v>
+        <v>VN PROT. SOLAR FACIAL TONO MEDIO FPS50 x5 un</v>
       </c>
       <c r="D816">
         <f>VLOOKUP(A816,Hoja1!A:C,3,FALSE)</f>
-        <v>5883.02</v>
+        <v>13752.63</v>
       </c>
       <c r="E816">
         <v>69</v>
@@ -24424,18 +24391,18 @@
     </row>
     <row r="817" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A817">
-        <v>50177</v>
+        <v>38866</v>
       </c>
       <c r="B817" t="s">
-        <v>1491</v>
+        <v>1469</v>
       </c>
       <c r="C817" t="str">
         <f>VLOOKUP(A817,Hoja1!A:C,2,FALSE)</f>
-        <v>VN  REPELENTE FAMILIAR X 170ML NARANJA x12 un</v>
+        <v>VN PROT. SOLAR FPS 30 POMO X 120M x12 un</v>
       </c>
       <c r="D817">
         <f>VLOOKUP(A817,Hoja1!A:C,3,FALSE)</f>
-        <v>3982.76</v>
+        <v>7000</v>
       </c>
       <c r="E817">
         <v>69</v>
@@ -24446,23 +24413,265 @@
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A818">
-        <v>33260</v>
+        <v>38872</v>
       </c>
       <c r="B818" t="s">
-        <v>1493</v>
+        <v>1471</v>
       </c>
       <c r="C818" t="str">
         <f>VLOOKUP(A818,Hoja1!A:C,2,FALSE)</f>
-        <v>VN CREM.CORP.PIEL EQUILIB.PALTA 250G x12 un</v>
+        <v>VN PROT. SOLAR FPS 30 POMO X 50ML x12 un</v>
       </c>
       <c r="D818">
         <f>VLOOKUP(A818,Hoja1!A:C,3,FALSE)</f>
-        <v>4620.01</v>
+        <v>5000</v>
       </c>
       <c r="E818">
         <v>69</v>
       </c>
       <c r="F818" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="819" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A819">
+        <v>38867</v>
+      </c>
+      <c r="B819" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C819" t="str">
+        <f>VLOOKUP(A819,Hoja1!A:C,2,FALSE)</f>
+        <v>VN PROT. SOLAR FPS 40 POMO X 120M x12 un</v>
+      </c>
+      <c r="D819">
+        <f>VLOOKUP(A819,Hoja1!A:C,3,FALSE)</f>
+        <v>8000</v>
+      </c>
+      <c r="E819">
+        <v>69</v>
+      </c>
+      <c r="F819" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="820" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A820">
+        <v>38869</v>
+      </c>
+      <c r="B820" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C820" t="str">
+        <f>VLOOKUP(A820,Hoja1!A:C,2,FALSE)</f>
+        <v>VN PROT. SOLAR FPS 50 POMO X 120M x12 un</v>
+      </c>
+      <c r="D820">
+        <f>VLOOKUP(A820,Hoja1!A:C,3,FALSE)</f>
+        <v>8000</v>
+      </c>
+      <c r="E820">
+        <v>69</v>
+      </c>
+      <c r="F820" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="821" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A821">
+        <v>38871</v>
+      </c>
+      <c r="B821" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C821" t="str">
+        <f>VLOOKUP(A821,Hoja1!A:C,2,FALSE)</f>
+        <v>VN PROT. SOLAR FPS 50 POMO X50 ML x12 un</v>
+      </c>
+      <c r="D821">
+        <f>VLOOKUP(A821,Hoja1!A:C,3,FALSE)</f>
+        <v>6000</v>
+      </c>
+      <c r="E821">
+        <v>69</v>
+      </c>
+      <c r="F821" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="822" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A822">
+        <v>38870</v>
+      </c>
+      <c r="B822" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C822" t="str">
+        <f>VLOOKUP(A822,Hoja1!A:C,2,FALSE)</f>
+        <v>VN PROT. SOLAR FPS60 BABY POMO X120 x12 un</v>
+      </c>
+      <c r="D822">
+        <f>VLOOKUP(A822,Hoja1!A:C,3,FALSE)</f>
+        <v>10000</v>
+      </c>
+      <c r="E822">
+        <v>69</v>
+      </c>
+      <c r="F822" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="823" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A823">
+        <v>38873</v>
+      </c>
+      <c r="B823" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C823" t="str">
+        <f>VLOOKUP(A823,Hoja1!A:C,2,FALSE)</f>
+        <v>VN PROT. SOLAR POMO FAMILIAR FPS30 X 250 x12 un</v>
+      </c>
+      <c r="D823">
+        <f>VLOOKUP(A823,Hoja1!A:C,3,FALSE)</f>
+        <v>12000.01</v>
+      </c>
+      <c r="E823">
+        <v>69</v>
+      </c>
+      <c r="F823" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="824" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A824">
+        <v>38874</v>
+      </c>
+      <c r="B824" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C824" t="str">
+        <f>VLOOKUP(A824,Hoja1!A:C,2,FALSE)</f>
+        <v>VN PROT. SOLAR POMO FAMILIAR FPS50 X250 x12 un</v>
+      </c>
+      <c r="D824">
+        <f>VLOOKUP(A824,Hoja1!A:C,3,FALSE)</f>
+        <v>13000</v>
+      </c>
+      <c r="E824">
+        <v>69</v>
+      </c>
+      <c r="F824" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="825" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A825">
+        <v>38490</v>
+      </c>
+      <c r="B825" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C825" t="str">
+        <f>VLOOKUP(A825,Hoja1!A:C,2,FALSE)</f>
+        <v>VN PROT. SOLAR SPRAY EF.SECO FPS30 X 190 x12 un</v>
+      </c>
+      <c r="D825">
+        <f>VLOOKUP(A825,Hoja1!A:C,3,FALSE)</f>
+        <v>13000</v>
+      </c>
+      <c r="E825">
+        <v>69</v>
+      </c>
+      <c r="F825" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="826" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A826">
+        <v>38492</v>
+      </c>
+      <c r="B826" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C826" t="str">
+        <f>VLOOKUP(A826,Hoja1!A:C,2,FALSE)</f>
+        <v>VN PROT. SOLAR SPRAY EF.SECO FPS50 X190 x12 un</v>
+      </c>
+      <c r="D826">
+        <f>VLOOKUP(A826,Hoja1!A:C,3,FALSE)</f>
+        <v>14000</v>
+      </c>
+      <c r="E826">
+        <v>69</v>
+      </c>
+      <c r="F826" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="827" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A827">
+        <v>50178</v>
+      </c>
+      <c r="B827" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C827" t="str">
+        <f>VLOOKUP(A827,Hoja1!A:C,2,FALSE)</f>
+        <v>VN REPELENTE EXTRA DURACION X 170 VERDE x12 un</v>
+      </c>
+      <c r="D827">
+        <f>VLOOKUP(A827,Hoja1!A:C,3,FALSE)</f>
+        <v>5883.02</v>
+      </c>
+      <c r="E827">
+        <v>69</v>
+      </c>
+      <c r="F827" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A828">
+        <v>50177</v>
+      </c>
+      <c r="B828" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C828" t="str">
+        <f>VLOOKUP(A828,Hoja1!A:C,2,FALSE)</f>
+        <v>VN  REPELENTE FAMILIAR X 170ML NARANJA x12 un</v>
+      </c>
+      <c r="D828">
+        <f>VLOOKUP(A828,Hoja1!A:C,3,FALSE)</f>
+        <v>3982.76</v>
+      </c>
+      <c r="E828">
+        <v>69</v>
+      </c>
+      <c r="F828" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="829" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A829">
+        <v>33260</v>
+      </c>
+      <c r="B829" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C829" t="str">
+        <f>VLOOKUP(A829,Hoja1!A:C,2,FALSE)</f>
+        <v>VN CREM.CORP.PIEL EQUILIB.PALTA 250G x12 un</v>
+      </c>
+      <c r="D829">
+        <f>VLOOKUP(A829,Hoja1!A:C,3,FALSE)</f>
+        <v>4620.01</v>
+      </c>
+      <c r="E829">
+        <v>69</v>
+      </c>
+      <c r="F829" t="s">
         <v>6</v>
       </c>
     </row>

--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3039" uniqueCount="2070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2977" uniqueCount="2070">
   <si>
     <t>Código</t>
   </si>
@@ -13528,7 +13528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>122456</v>
       </c>
@@ -13547,7 +13547,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>1221323</v>
       </c>
@@ -13566,7 +13566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>1221322</v>
       </c>
@@ -13585,7 +13585,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>1221321</v>
       </c>
@@ -13604,7 +13604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>122201</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>1222064</v>
       </c>
@@ -13642,7 +13642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>122451</v>
       </c>
@@ -13661,7 +13661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>122487</v>
       </c>
@@ -13680,7 +13680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>1227503</v>
       </c>
@@ -13699,7 +13699,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>122570</v>
       </c>
@@ -13718,7 +13718,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>20216</v>
       </c>
@@ -13733,11 +13733,8 @@
       <c r="E331">
         <v>8</v>
       </c>
-      <c r="F331" t="s">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>20223</v>
       </c>
@@ -13752,11 +13749,8 @@
       <c r="E332">
         <v>8</v>
       </c>
-      <c r="F332" t="s">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>20438</v>
       </c>
@@ -13771,11 +13765,8 @@
       <c r="E333">
         <v>8</v>
       </c>
-      <c r="F333" t="s">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>20421</v>
       </c>
@@ -13790,11 +13781,8 @@
       <c r="E334">
         <v>8</v>
       </c>
-      <c r="F334" t="s">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>20452</v>
       </c>
@@ -13809,11 +13797,8 @@
       <c r="E335">
         <v>8</v>
       </c>
-      <c r="F335" t="s">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>20445</v>
       </c>
@@ -13828,9 +13813,6 @@
       <c r="E336">
         <v>8</v>
       </c>
-      <c r="F336" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337">
@@ -17325,9 +17307,6 @@
       <c r="E496">
         <v>18</v>
       </c>
-      <c r="F496" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497">
@@ -17344,9 +17323,6 @@
       <c r="E497">
         <v>18</v>
       </c>
-      <c r="F497" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498">
@@ -17363,9 +17339,6 @@
       <c r="E498">
         <v>18</v>
       </c>
-      <c r="F498" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499">
@@ -20242,9 +20215,6 @@
       <c r="E629">
         <v>43</v>
       </c>
-      <c r="F629" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630">
@@ -20261,9 +20231,6 @@
       <c r="E630">
         <v>43</v>
       </c>
-      <c r="F630" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631">
@@ -20280,9 +20247,6 @@
       <c r="E631">
         <v>43</v>
       </c>
-      <c r="F631" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632">
@@ -20302,9 +20266,6 @@
       <c r="E632">
         <v>44</v>
       </c>
-      <c r="F632" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633">
@@ -20610,9 +20571,6 @@
       <c r="E646">
         <v>46</v>
       </c>
-      <c r="F646" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647">
@@ -20629,9 +20587,6 @@
       <c r="E647">
         <v>46</v>
       </c>
-      <c r="F647" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648">
@@ -20648,9 +20603,6 @@
       <c r="E648">
         <v>46</v>
       </c>
-      <c r="F648" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649">
@@ -20667,9 +20619,6 @@
       <c r="E649">
         <v>46</v>
       </c>
-      <c r="F649" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650">
@@ -20686,9 +20635,6 @@
       <c r="E650">
         <v>46</v>
       </c>
-      <c r="F650" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651">
@@ -20708,9 +20654,6 @@
       <c r="E651">
         <v>47</v>
       </c>
-      <c r="F651" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652">
@@ -21937,9 +21880,6 @@
       <c r="E707">
         <v>52</v>
       </c>
-      <c r="F707" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A708">
@@ -21956,9 +21896,6 @@
       <c r="E708">
         <v>52</v>
       </c>
-      <c r="F708" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A709">
@@ -21975,9 +21912,6 @@
       <c r="E709">
         <v>52</v>
       </c>
-      <c r="F709" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A710">
@@ -21994,9 +21928,6 @@
       <c r="E710">
         <v>52</v>
       </c>
-      <c r="F710" t="s">
-        <v>2048</v>
-      </c>
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A711">
@@ -22016,9 +21947,6 @@
       <c r="E711">
         <v>53</v>
       </c>
-      <c r="F711" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A712">
@@ -22038,9 +21966,6 @@
       <c r="E712">
         <v>54</v>
       </c>
-      <c r="F712" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A713">
@@ -23882,9 +23807,6 @@
       </c>
       <c r="E796">
         <v>65</v>
-      </c>
-      <c r="F796" t="s">
-        <v>2048</v>
       </c>
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.25">

--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -23355,18 +23355,18 @@
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A774">
-        <v>200371</v>
+        <v>201418</v>
       </c>
       <c r="B774" t="s">
-        <v>1293</v>
+        <v>1310</v>
       </c>
       <c r="C774" t="str">
         <f>VLOOKUP(A774,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET TOALLA MAXI NOCTURNAX10 x12 un</v>
+        <v>TENA DISCREET TOALLA MAXI X10U AMARILLO x12 un</v>
       </c>
       <c r="D774">
         <f>VLOOKUP(A774,Hoja1!A:C,3,FALSE)</f>
-        <v>15073.93</v>
+        <v>13107.75</v>
       </c>
       <c r="E774">
         <v>62</v>
@@ -23377,18 +23377,18 @@
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A775">
-        <v>200372</v>
+        <v>200371</v>
       </c>
       <c r="B775" t="s">
-        <v>1308</v>
+        <v>1293</v>
       </c>
       <c r="C775" t="str">
         <f>VLOOKUP(A775,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET TOALLA MAXI NOCTURNA X30 x8 un</v>
+        <v>TENA DISCREET TOALLA MAXI NOCTURNAX10 x12 un</v>
       </c>
       <c r="D775">
         <f>VLOOKUP(A775,Hoja1!A:C,3,FALSE)</f>
-        <v>40697.19</v>
+        <v>15073.93</v>
       </c>
       <c r="E775">
         <v>62</v>
@@ -23399,18 +23399,18 @@
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A776">
-        <v>201418</v>
+        <v>200372</v>
       </c>
       <c r="B776" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C776" t="str">
         <f>VLOOKUP(A776,Hoja1!A:C,2,FALSE)</f>
-        <v>TENA DISCREET TOALLA MAXI X10U AMARILLO x12 un</v>
+        <v>TENA DISCREET TOALLA MAXI NOCTURNA X30 x8 un</v>
       </c>
       <c r="D776">
         <f>VLOOKUP(A776,Hoja1!A:C,3,FALSE)</f>
-        <v>13107.75</v>
+        <v>40697.19</v>
       </c>
       <c r="E776">
         <v>62</v>
